--- a/engine/elec_study/ELEC_Valuation_Model_05082026_public.xlsx
+++ b/engine/elec_study/ELEC_Valuation_Model_05082026_public.xlsx
@@ -76,7 +76,7 @@
     <t xml:space="preserve">year, closes to the reported net profit within 0.8% using the derived lines.</t>
   </si>
   <si>
-    <t xml:space="preserve">Discount convention. Each explicit year is discounted at its own forward WACC, gliding 22.6% -&gt; 14.1% on the</t>
+    <t xml:space="preserve">Discount convention. Each explicit year is discounted at its own forward WACC, gliding 21.4% -&gt; 13.9% on the</t>
   </si>
   <si>
     <t xml:space="preserve">same easing calendar as the interest forecast; the terminal value is capitalised at the terminal WACC and</t>
@@ -211,7 +211,7 @@
     <t xml:space="preserve">Kd pre-tax (marginal EGP)</t>
   </si>
   <si>
-    <t xml:space="preserve">Corridor + levered margin; effective-rate checks 23.4% (FY24) / 23.2% (FY25) inside 150bp</t>
+    <t xml:space="preserve">Corridor + credit margin; effective-rate checks 23.5% (FY24) / 21.7% (FY25, disclosed debt path) inside 150bp</t>
   </si>
   <si>
     <t xml:space="preserve">Kd after tax</t>
@@ -220,10 +220,10 @@
     <t xml:space="preserve">Market cap (spot × shares)</t>
   </si>
   <si>
-    <t xml:space="preserve">Total debt for weights (FY24 disclosed vintage)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simply Wall St, 22-May-2025 — the sourced debt print</t>
+    <t xml:space="preserve">Total debt for weights (FY25 disclosed facilities)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY25 results coverage: EGP 10.9bn bank facilities vs 8.96bn FY24 (matches the FY24 debt print — cross-validated)</t>
   </si>
   <si>
     <t xml:space="preserve">Equity weight E/(D+E)</t>
@@ -268,7 +268,7 @@
     <t xml:space="preserve">Net debt (FY25, derived)</t>
   </si>
   <si>
-    <t xml:space="preserve">Derived from twice-sourced FY25 assets 16,460 + FY24 anchors; FY24-vintage sourced alt: 8,172</t>
+    <t xml:space="preserve">Disclosed facilities 10,900 less estimated cash ~700; FY24-vintage sourced alt: 8,172 — worth ±EGP 0.6/sh, see Sensitivity</t>
   </si>
   <si>
     <t xml:space="preserve">Non-controlling interests</t>
@@ -346,7 +346,7 @@
     <t xml:space="preserve">EBITDA margin</t>
   </si>
   <si>
-    <t xml:space="preserve">Between the 1Q26 trough (~14%) and windfall prints (~25%)</t>
+    <t xml:space="preserve">1Q26 DISCLOSED: gross margin 5.7%, operating ~0 — the trough; windfall prints ~25% the ceiling</t>
   </si>
   <si>
     <t xml:space="preserve">D&amp;A (% of revenue)</t>
@@ -361,7 +361,7 @@
     <t xml:space="preserve">Net working capital (% of revenue)</t>
   </si>
   <si>
-    <t xml:space="preserve">From ~111% FY25e; NOT full reversion to FY24 76%</t>
+    <t xml:space="preserve">From ~117% FY25e; NOT full reversion to FY24 76%</t>
   </si>
   <si>
     <t xml:space="preserve">Forward Kd path</t>
@@ -391,7 +391,7 @@
     <t xml:space="preserve">Net working capital FY25 (derived)</t>
   </si>
   <si>
-    <t xml:space="preserve">~111% of FY25 revenue — construction in study §1.6</t>
+    <t xml:space="preserve">~117% of FY25 revenue — construction in study §1.6</t>
   </si>
   <si>
     <t xml:space="preserve">EV → equity bridge</t>
@@ -406,7 +406,7 @@
     <t xml:space="preserve">+ Surplus / non-core assets</t>
   </si>
   <si>
-    <t xml:space="preserve">− Net debt (FY25, derived; ±1,000 sensitized)</t>
+    <t xml:space="preserve">− Net debt (FY25: disclosed facilities − est. cash)</t>
   </si>
   <si>
     <t xml:space="preserve">− Non-controlling interests</t>
@@ -1734,23 +1734,23 @@
       </c>
       <c r="C6" s="17" t="n">
         <f aca="false">Assumptions!B52</f>
-        <v>12000</v>
+        <v>12640</v>
       </c>
       <c r="D6" s="24" t="n">
         <f aca="false">DCF!B13</f>
-        <v>9394.35408</v>
+        <v>9742.29312</v>
       </c>
       <c r="E6" s="24" t="n">
         <f aca="false">DCF!C13</f>
-        <v>10213.7505192</v>
+        <v>10511.2383984</v>
       </c>
       <c r="F6" s="24" t="n">
         <f aca="false">DCF!D13</f>
-        <v>10884.089873664</v>
+        <v>11106.2141568</v>
       </c>
       <c r="G6" s="24" t="n">
         <f aca="false">DCF!E13</f>
-        <v>11361.6570824064</v>
+        <v>11483.8254381312</v>
       </c>
       <c r="H6" s="24" t="n">
         <f aca="false">DCF!F13</f>
@@ -1829,23 +1829,23 @@
       </c>
       <c r="C9" s="30" t="n">
         <f aca="false">SUM(C6:C8)</f>
-        <v>15660</v>
+        <v>16300</v>
       </c>
       <c r="D9" s="19" t="n">
         <f aca="false">SUM(D6:D8)</f>
-        <v>13080.449508</v>
+        <v>13428.388548</v>
       </c>
       <c r="E9" s="19" t="n">
         <f aca="false">SUM(E6:E8)</f>
-        <v>13929.59473512</v>
+        <v>14227.08261432</v>
       </c>
       <c r="F9" s="19" t="n">
         <f aca="false">SUM(F6:F8)</f>
-        <v>14633.2527320544</v>
+        <v>14855.3770151904</v>
       </c>
       <c r="G9" s="19" t="n">
         <f aca="false">SUM(G6:G8)</f>
-        <v>15147.4704475142</v>
+        <v>15269.638803239</v>
       </c>
       <c r="H9" s="19" t="n">
         <f aca="false">SUM(H6:H8)</f>
@@ -1857,31 +1857,31 @@
         <v>195</v>
       </c>
       <c r="B11" s="17" t="n">
-        <v>8172</v>
+        <v>8172.4</v>
       </c>
       <c r="C11" s="17" t="n">
         <f aca="false">Assumptions!B28</f>
-        <v>8800</v>
+        <v>10200</v>
       </c>
       <c r="D11" s="24" t="n">
         <f aca="false">Assumptions!$B$28-'Cash Flow'!C12</f>
-        <v>7270.727816</v>
+        <v>9033.083036</v>
       </c>
       <c r="E11" s="24" t="n">
         <f aca="false">D11-'Cash Flow'!D12</f>
-        <v>8189.0352764</v>
+        <v>10379.02835424</v>
       </c>
       <c r="F11" s="24" t="n">
         <f aca="false">E11-'Cash Flow'!E12</f>
-        <v>8649.4032824488</v>
+        <v>11294.8295195952</v>
       </c>
       <c r="G11" s="24" t="n">
         <f aca="false">F11-'Cash Flow'!F12</f>
-        <v>8532.72383745838</v>
+        <v>11627.4953041941</v>
       </c>
       <c r="H11" s="24" t="n">
         <f aca="false">G11-'Cash Flow'!G12</f>
-        <v>7981.42929540173</v>
+        <v>11392.9662497003</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1898,23 +1898,23 @@
       </c>
       <c r="D12" s="24" t="n">
         <f aca="false">C12+'Income Statement'!E14</f>
-        <v>3049.721692</v>
+        <v>2395.305512</v>
       </c>
       <c r="E12" s="24" t="n">
         <f aca="false">D12+'Income Statement'!F14</f>
-        <v>2980.55945872</v>
+        <v>1848.05426008</v>
       </c>
       <c r="F12" s="24" t="n">
         <f aca="false">E12+'Income Statement'!G14</f>
-        <v>3223.8494496056</v>
+        <v>1560.5474955952</v>
       </c>
       <c r="G12" s="24" t="n">
         <f aca="false">F12+'Income Statement'!H14</f>
-        <v>3854.74661005587</v>
+        <v>1642.14349904497</v>
       </c>
       <c r="H12" s="24" t="n">
         <f aca="false">G12+'Income Statement'!I14</f>
-        <v>4694.84714504595</v>
+        <v>2043.31019074738</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1923,31 +1923,31 @@
       </c>
       <c r="B13" s="31" t="n">
         <f aca="false">B9-B11-B12</f>
-        <v>2378.31</v>
+        <v>2377.91</v>
       </c>
       <c r="C13" s="31" t="n">
         <f aca="false">C9-C11-C12</f>
-        <v>2760</v>
+        <v>2000</v>
       </c>
       <c r="D13" s="31" t="n">
         <f aca="false">$C13</f>
-        <v>2760</v>
+        <v>2000</v>
       </c>
       <c r="E13" s="31" t="n">
         <f aca="false">$C13</f>
-        <v>2760</v>
+        <v>2000</v>
       </c>
       <c r="F13" s="31" t="n">
         <f aca="false">$C13</f>
-        <v>2760</v>
+        <v>2000</v>
       </c>
       <c r="G13" s="31" t="n">
         <f aca="false">$C13</f>
-        <v>2760</v>
+        <v>2000</v>
       </c>
       <c r="H13" s="31" t="n">
         <f aca="false">$C13</f>
-        <v>2760</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1960,23 +1960,23 @@
       </c>
       <c r="C14" s="30" t="n">
         <f aca="false">C11+C12+C13</f>
-        <v>15660</v>
+        <v>16300</v>
       </c>
       <c r="D14" s="19" t="n">
         <f aca="false">D11+D12+D13</f>
-        <v>13080.449508</v>
+        <v>13428.388548</v>
       </c>
       <c r="E14" s="19" t="n">
         <f aca="false">E11+E12+E13</f>
-        <v>13929.59473512</v>
+        <v>14227.08261432</v>
       </c>
       <c r="F14" s="19" t="n">
         <f aca="false">F11+F12+F13</f>
-        <v>14633.2527320544</v>
+        <v>14855.3770151904</v>
       </c>
       <c r="G14" s="19" t="n">
         <f aca="false">G11+G12+G13</f>
-        <v>15147.4704475142</v>
+        <v>15269.638803239</v>
       </c>
       <c r="H14" s="19" t="n">
         <f aca="false">H11+H12+H13</f>
@@ -2086,23 +2086,23 @@
       </c>
       <c r="C6" s="24" t="n">
         <f aca="false">'Income Statement'!E14</f>
-        <v>-1050.278308</v>
+        <v>-1704.694488</v>
       </c>
       <c r="D6" s="24" t="n">
         <f aca="false">'Income Statement'!F14</f>
-        <v>-69.1622332799998</v>
+        <v>-547.25125192</v>
       </c>
       <c r="E6" s="24" t="n">
         <f aca="false">'Income Statement'!G14</f>
-        <v>243.2899908856</v>
+        <v>-287.5067644848</v>
       </c>
       <c r="F6" s="24" t="n">
         <f aca="false">'Income Statement'!H14</f>
-        <v>630.897160450264</v>
+        <v>81.5960034497662</v>
       </c>
       <c r="G6" s="24" t="n">
         <f aca="false">'Income Statement'!I14</f>
-        <v>840.100534990083</v>
+        <v>401.166691702412</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2136,23 +2136,23 @@
       </c>
       <c r="C8" s="24" t="n">
         <f aca="false">DCF!B14</f>
-        <v>2605.64592</v>
+        <v>2897.70688</v>
       </c>
       <c r="D8" s="24" t="n">
         <f aca="false">DCF!C14</f>
-        <v>-819.3964392</v>
+        <v>-768.945278399999</v>
       </c>
       <c r="E8" s="24" t="n">
         <f aca="false">DCF!D14</f>
-        <v>-670.339354464002</v>
+        <v>-594.975758400002</v>
       </c>
       <c r="F8" s="24" t="n">
         <f aca="false">DCF!E14</f>
-        <v>-477.567208742401</v>
+        <v>-377.611281331201</v>
       </c>
       <c r="G8" s="24" t="n">
         <f aca="false">DCF!F14</f>
-        <v>-249.223445678594</v>
+        <v>-127.055089953794</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2186,23 +2186,23 @@
       </c>
       <c r="C10" s="19" t="n">
         <f aca="false">SUM(C6:C9)</f>
-        <v>1529.272184</v>
+        <v>1166.916964</v>
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">SUM(D6:D9)</f>
-        <v>-918.3074604</v>
+        <v>-1345.94531824</v>
       </c>
       <c r="E10" s="19" t="n">
         <f aca="false">SUM(E6:E9)</f>
-        <v>-460.368006048802</v>
+        <v>-915.801165355201</v>
       </c>
       <c r="F10" s="19" t="n">
         <f aca="false">SUM(F6:F9)</f>
-        <v>116.679444990423</v>
+        <v>-332.665784598875</v>
       </c>
       <c r="G10" s="19" t="n">
         <f aca="false">SUM(G6:G9)</f>
-        <v>551.294542056654</v>
+        <v>234.529054493782</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2231,23 +2231,23 @@
       </c>
       <c r="C12" s="19" t="n">
         <f aca="false">C10+C11</f>
-        <v>1529.272184</v>
+        <v>1166.916964</v>
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">D10+D11</f>
-        <v>-918.3074604</v>
+        <v>-1345.94531824</v>
       </c>
       <c r="E12" s="19" t="n">
         <f aca="false">E10+E11</f>
-        <v>-460.368006048802</v>
+        <v>-915.801165355201</v>
       </c>
       <c r="F12" s="19" t="n">
         <f aca="false">F10+F11</f>
-        <v>116.679444990423</v>
+        <v>-332.665784598875</v>
       </c>
       <c r="G12" s="19" t="n">
         <f aca="false">G10+G11</f>
-        <v>551.294542056654</v>
+        <v>234.529054493782</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2256,23 +2256,23 @@
       </c>
       <c r="C14" s="24" t="n">
         <f aca="false">DCF!B15</f>
-        <v>3368.2848033</v>
+        <v>3289.5732238</v>
       </c>
       <c r="D14" s="24" t="n">
         <f aca="false">DCF!C15</f>
-        <v>280.564994142</v>
+        <v>177.314084022002</v>
       </c>
       <c r="E14" s="24" t="n">
         <f aca="false">DCF!D15</f>
-        <v>690.727190451838</v>
+        <v>636.981046943039</v>
       </c>
       <c r="F14" s="24" t="n">
         <f aca="false">DCF!E15</f>
-        <v>1114.28646635174</v>
+        <v>1119.56191807622</v>
       </c>
       <c r="G14" s="24" t="n">
         <f aca="false">DCF!F15</f>
-        <v>1521.10598029391</v>
+        <v>1541.01942227705</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2281,23 +2281,23 @@
       </c>
       <c r="C15" s="24" t="n">
         <f aca="false">'Balance Sheet'!D11</f>
-        <v>7270.727816</v>
+        <v>9033.083036</v>
       </c>
       <c r="D15" s="24" t="n">
         <f aca="false">'Balance Sheet'!E11</f>
-        <v>8189.0352764</v>
+        <v>10379.02835424</v>
       </c>
       <c r="E15" s="24" t="n">
         <f aca="false">'Balance Sheet'!F11</f>
-        <v>8649.4032824488</v>
+        <v>11294.8295195952</v>
       </c>
       <c r="F15" s="24" t="n">
         <f aca="false">'Balance Sheet'!G11</f>
-        <v>8532.72383745838</v>
+        <v>11627.4953041941</v>
       </c>
       <c r="G15" s="24" t="n">
         <f aca="false">'Balance Sheet'!H11</f>
-        <v>7981.42929540173</v>
+        <v>11392.9662497003</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2423,23 +2423,23 @@
       </c>
       <c r="E7" s="24" t="n">
         <f aca="false">'Income Statement'!E7</f>
-        <v>1130.80188</v>
+        <v>652.3857</v>
       </c>
       <c r="F7" s="24" t="n">
         <f aca="false">'Income Statement'!F7</f>
-        <v>1586.6020224</v>
+        <v>1388.2767696</v>
       </c>
       <c r="G7" s="24" t="n">
         <f aca="false">'Income Statement'!G7</f>
-        <v>1943.58747744</v>
+        <v>1776.994265088</v>
       </c>
       <c r="H7" s="24" t="n">
         <f aca="false">'Income Statement'!H7</f>
-        <v>2260.1145809088</v>
+        <v>2137.946225184</v>
       </c>
       <c r="I7" s="24" t="n">
         <f aca="false">'Income Statement'!I7</f>
-        <v>2506.8946594729</v>
+        <v>2374.95283529011</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2457,23 +2457,23 @@
       </c>
       <c r="E8" s="24" t="n">
         <f aca="false">'Income Statement'!E9</f>
-        <v>1017.721692</v>
+        <v>539.305512</v>
       </c>
       <c r="F8" s="24" t="n">
         <f aca="false">'Income Statement'!F9</f>
-        <v>1457.69060808</v>
+        <v>1259.36535528</v>
       </c>
       <c r="G8" s="24" t="n">
         <f aca="false">'Income Statement'!G9</f>
-        <v>1799.2066934016</v>
+        <v>1632.6134810496</v>
       </c>
       <c r="H8" s="24" t="n">
         <f aca="false">'Income Statement'!H9</f>
-        <v>2101.29571846656</v>
+        <v>1979.12736274176</v>
       </c>
       <c r="I8" s="24" t="n">
         <f aca="false">'Income Statement'!I9</f>
-        <v>2335.37028803528</v>
+        <v>2203.42846385249</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2491,23 +2491,23 @@
       </c>
       <c r="E9" s="24" t="n">
         <f aca="false">'Income Statement'!E14</f>
-        <v>-1050.278308</v>
+        <v>-1704.694488</v>
       </c>
       <c r="F9" s="24" t="n">
         <f aca="false">'Income Statement'!F14</f>
-        <v>-69.1622332799998</v>
+        <v>-547.25125192</v>
       </c>
       <c r="G9" s="24" t="n">
         <f aca="false">'Income Statement'!G14</f>
-        <v>243.2899908856</v>
+        <v>-287.5067644848</v>
       </c>
       <c r="H9" s="24" t="n">
         <f aca="false">'Income Statement'!H14</f>
-        <v>630.897160450264</v>
+        <v>81.5960034497662</v>
       </c>
       <c r="I9" s="24" t="n">
         <f aca="false">'Income Statement'!I14</f>
-        <v>840.100534990083</v>
+        <v>401.166691702412</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2516,27 +2516,27 @@
       </c>
       <c r="D10" s="24" t="n">
         <f aca="false">Assumptions!B28</f>
-        <v>8800</v>
+        <v>10200</v>
       </c>
       <c r="E10" s="24" t="n">
         <f aca="false">'Balance Sheet'!D11</f>
-        <v>7270.727816</v>
+        <v>9033.083036</v>
       </c>
       <c r="F10" s="24" t="n">
         <f aca="false">'Balance Sheet'!E11</f>
-        <v>8189.0352764</v>
+        <v>10379.02835424</v>
       </c>
       <c r="G10" s="24" t="n">
         <f aca="false">'Balance Sheet'!F11</f>
-        <v>8649.4032824488</v>
+        <v>11294.8295195952</v>
       </c>
       <c r="H10" s="24" t="n">
         <f aca="false">'Balance Sheet'!G11</f>
-        <v>8532.72383745838</v>
+        <v>11627.4953041941</v>
       </c>
       <c r="I10" s="24" t="n">
         <f aca="false">'Balance Sheet'!H11</f>
-        <v>7981.42929540173</v>
+        <v>11392.9662497003</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2549,23 +2549,23 @@
       </c>
       <c r="E11" s="24" t="n">
         <f aca="false">'Balance Sheet'!D12</f>
-        <v>3049.721692</v>
+        <v>2395.305512</v>
       </c>
       <c r="F11" s="24" t="n">
         <f aca="false">'Balance Sheet'!E12</f>
-        <v>2980.55945872</v>
+        <v>1848.05426008</v>
       </c>
       <c r="G11" s="24" t="n">
         <f aca="false">'Balance Sheet'!F12</f>
-        <v>3223.8494496056</v>
+        <v>1560.5474955952</v>
       </c>
       <c r="H11" s="24" t="n">
         <f aca="false">'Balance Sheet'!G12</f>
-        <v>3854.74661005587</v>
+        <v>1642.14349904497</v>
       </c>
       <c r="I11" s="24" t="n">
         <f aca="false">'Balance Sheet'!H12</f>
-        <v>4694.84714504595</v>
+        <v>2043.31019074738</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2574,23 +2574,23 @@
       </c>
       <c r="E12" s="24" t="n">
         <f aca="false">DCF!B15</f>
-        <v>3368.2848033</v>
+        <v>3289.5732238</v>
       </c>
       <c r="F12" s="24" t="n">
         <f aca="false">DCF!C15</f>
-        <v>280.564994142</v>
+        <v>177.314084022002</v>
       </c>
       <c r="G12" s="24" t="n">
         <f aca="false">DCF!D15</f>
-        <v>690.727190451838</v>
+        <v>636.981046943039</v>
       </c>
       <c r="H12" s="24" t="n">
         <f aca="false">DCF!E15</f>
-        <v>1114.28646635174</v>
+        <v>1119.56191807622</v>
       </c>
       <c r="I12" s="24" t="n">
         <f aca="false">DCF!F15</f>
-        <v>1521.10598029391</v>
+        <v>1541.01942227705</v>
       </c>
     </row>
   </sheetData>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="B5" s="8" t="n">
         <f aca="false">DCF!B31</f>
-        <v>0.533988597838447</v>
+        <v>0.0233762361074855</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2983,102 +2983,102 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="n">
-        <v>0.121349976678297</v>
+        <v>0.118723393761621</v>
       </c>
       <c r="B9" s="29" t="n">
-        <v>0.98</v>
+        <v>0.49</v>
       </c>
       <c r="C9" s="29" t="n">
-        <v>1.07</v>
+        <v>0.57</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>1.17</v>
+        <v>0.66</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>1.3</v>
+        <v>0.77</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>1.48</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="n">
-        <v>0.131349976678297</v>
+        <v>0.128723393761621</v>
       </c>
       <c r="B10" s="29" t="n">
-        <v>0.71</v>
+        <v>0.21</v>
       </c>
       <c r="C10" s="29" t="n">
-        <v>0.76</v>
+        <v>0.25</v>
       </c>
       <c r="D10" s="29" t="n">
-        <v>0.81</v>
+        <v>0.3</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>0.88</v>
+        <v>0.35</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>0.97</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="n">
-        <v>0.141349976678297</v>
+        <v>0.138723393761621</v>
       </c>
       <c r="B11" s="29" t="n">
-        <v>0.48</v>
+        <v>-0.01</v>
       </c>
       <c r="C11" s="29" t="n">
-        <v>0.51</v>
+        <v>0.01</v>
       </c>
       <c r="D11" s="29" t="n">
-        <v>0.53</v>
+        <v>0.02</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>0.57</v>
+        <v>0.04</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="n">
-        <v>0.151349976678297</v>
+        <v>0.148723393761621</v>
       </c>
       <c r="B12" s="29" t="n">
-        <v>0.29</v>
+        <v>-0.2</v>
       </c>
       <c r="C12" s="29" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="D12" s="29" t="n">
-        <v>0.31</v>
+        <v>-0.2</v>
       </c>
       <c r="E12" s="29" t="n">
-        <v>0.32</v>
+        <v>-0.2</v>
       </c>
       <c r="F12" s="29" t="n">
-        <v>0.32</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="n">
-        <v>0.161349976678297</v>
+        <v>0.158723393761621</v>
       </c>
       <c r="B13" s="29" t="n">
-        <v>0.13</v>
+        <v>-0.36</v>
       </c>
       <c r="C13" s="29" t="n">
-        <v>0.13</v>
+        <v>-0.37</v>
       </c>
       <c r="D13" s="29" t="n">
-        <v>0.13</v>
+        <v>-0.38</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>0.12</v>
+        <v>-0.4</v>
       </c>
       <c r="F13" s="29" t="n">
-        <v>0.11</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3091,119 +3091,119 @@
         <v>255</v>
       </c>
       <c r="B16" s="34" t="n">
-        <v>0.121349976678297</v>
+        <v>0.118723393761621</v>
       </c>
       <c r="C16" s="34" t="n">
-        <v>0.131349976678297</v>
+        <v>0.128723393761621</v>
       </c>
       <c r="D16" s="34" t="n">
-        <v>0.141349976678297</v>
+        <v>0.138723393761621</v>
       </c>
       <c r="E16" s="34" t="n">
-        <v>0.151349976678297</v>
+        <v>0.148723393761621</v>
       </c>
       <c r="F16" s="34" t="n">
-        <v>0.161349976678297</v>
+        <v>0.158723393761621</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="n">
-        <v>0.205730752476676</v>
+        <v>0.194188789049045</v>
       </c>
       <c r="B17" s="29" t="n">
-        <v>1.3</v>
+        <v>0.79</v>
       </c>
       <c r="C17" s="29" t="n">
-        <v>0.93</v>
+        <v>0.42</v>
       </c>
       <c r="D17" s="29" t="n">
-        <v>0.64</v>
+        <v>0.13</v>
       </c>
       <c r="E17" s="29" t="n">
-        <v>0.41</v>
+        <v>-0.1</v>
       </c>
       <c r="F17" s="29" t="n">
-        <v>0.21</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="n">
-        <v>0.215730752476676</v>
+        <v>0.204188789049045</v>
       </c>
       <c r="B18" s="29" t="n">
-        <v>1.23</v>
+        <v>0.72</v>
       </c>
       <c r="C18" s="29" t="n">
-        <v>0.87</v>
+        <v>0.36</v>
       </c>
       <c r="D18" s="29" t="n">
-        <v>0.59</v>
+        <v>0.08</v>
       </c>
       <c r="E18" s="29" t="n">
-        <v>0.36</v>
+        <v>-0.15</v>
       </c>
       <c r="F18" s="29" t="n">
-        <v>0.17</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="n">
-        <v>0.225730752476676</v>
+        <v>0.214188789049045</v>
       </c>
       <c r="B19" s="29" t="n">
-        <v>1.17</v>
+        <v>0.66</v>
       </c>
       <c r="C19" s="29" t="n">
-        <v>0.81</v>
+        <v>0.3</v>
       </c>
       <c r="D19" s="29" t="n">
-        <v>0.53</v>
+        <v>0.02</v>
       </c>
       <c r="E19" s="29" t="n">
-        <v>0.31</v>
+        <v>-0.2</v>
       </c>
       <c r="F19" s="29" t="n">
-        <v>0.13</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="n">
-        <v>0.235730752476676</v>
+        <v>0.224188789049045</v>
       </c>
       <c r="B20" s="29" t="n">
-        <v>1.11</v>
+        <v>0.59</v>
       </c>
       <c r="C20" s="29" t="n">
-        <v>0.76</v>
+        <v>0.24</v>
       </c>
       <c r="D20" s="29" t="n">
-        <v>0.48</v>
+        <v>-0.03</v>
       </c>
       <c r="E20" s="29" t="n">
-        <v>0.26</v>
+        <v>-0.24</v>
       </c>
       <c r="F20" s="29" t="n">
-        <v>0.08</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="n">
-        <v>0.245730752476676</v>
+        <v>0.234188789049045</v>
       </c>
       <c r="B21" s="29" t="n">
-        <v>1.04</v>
+        <v>0.53</v>
       </c>
       <c r="C21" s="29" t="n">
-        <v>0.7</v>
+        <v>0.19</v>
       </c>
       <c r="D21" s="29" t="n">
-        <v>0.43</v>
+        <v>-0.08</v>
       </c>
       <c r="E21" s="29" t="n">
-        <v>0.22</v>
+        <v>-0.29</v>
       </c>
       <c r="F21" s="29" t="n">
-        <v>0.04</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3236,19 +3236,19 @@
         <v>-0.03</v>
       </c>
       <c r="B25" s="29" t="n">
-        <v>-0.53</v>
+        <v>-1.08</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>-0.34</v>
+        <v>-0.89</v>
       </c>
       <c r="D25" s="29" t="n">
-        <v>-0.16</v>
+        <v>-0.7</v>
       </c>
       <c r="E25" s="29" t="n">
-        <v>0.03</v>
+        <v>-0.5</v>
       </c>
       <c r="F25" s="29" t="n">
-        <v>0.22</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3256,19 +3256,19 @@
         <v>-0.015</v>
       </c>
       <c r="B26" s="29" t="n">
-        <v>-0.19</v>
+        <v>-0.72</v>
       </c>
       <c r="C26" s="29" t="n">
-        <v>0</v>
+        <v>-0.53</v>
       </c>
       <c r="D26" s="29" t="n">
-        <v>0.19</v>
+        <v>-0.34</v>
       </c>
       <c r="E26" s="29" t="n">
-        <v>0.38</v>
+        <v>-0.14</v>
       </c>
       <c r="F26" s="29" t="n">
-        <v>0.56</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3276,19 +3276,19 @@
         <v>0</v>
       </c>
       <c r="B27" s="29" t="n">
-        <v>0.16</v>
+        <v>-0.36</v>
       </c>
       <c r="C27" s="29" t="n">
-        <v>0.35</v>
+        <v>-0.17</v>
       </c>
       <c r="D27" s="29" t="n">
-        <v>0.53</v>
+        <v>0.02</v>
       </c>
       <c r="E27" s="29" t="n">
-        <v>0.72</v>
+        <v>0.22</v>
       </c>
       <c r="F27" s="29" t="n">
-        <v>0.91</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3296,19 +3296,19 @@
         <v>0.015</v>
       </c>
       <c r="B28" s="29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C28" s="29" t="n">
-        <v>0.69</v>
+        <v>0.19</v>
       </c>
       <c r="D28" s="29" t="n">
-        <v>0.88</v>
+        <v>0.38</v>
       </c>
       <c r="E28" s="29" t="n">
-        <v>1.07</v>
+        <v>0.58</v>
       </c>
       <c r="F28" s="29" t="n">
-        <v>1.25</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3316,19 +3316,19 @@
         <v>0.03</v>
       </c>
       <c r="B29" s="29" t="n">
-        <v>0.85</v>
+        <v>0.36</v>
       </c>
       <c r="C29" s="29" t="n">
-        <v>1.04</v>
+        <v>0.55</v>
       </c>
       <c r="D29" s="29" t="n">
-        <v>1.22</v>
+        <v>0.74</v>
       </c>
       <c r="E29" s="29" t="n">
-        <v>1.41</v>
+        <v>0.94</v>
       </c>
       <c r="F29" s="29" t="n">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3361,13 +3361,13 @@
         <v>0.24556</v>
       </c>
       <c r="C33" s="12" t="n">
-        <v>0.210441148329856</v>
+        <v>0.200499163004575</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.129976201011162</v>
+        <v>0.128539824971898</v>
       </c>
       <c r="E33" s="29" t="n">
-        <v>0.86</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3378,13 +3378,13 @@
         <v>0.262498</v>
       </c>
       <c r="C34" s="12" t="n">
-        <v>0.218001941589273</v>
+        <v>0.207268758301291</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.135600595571833</v>
+        <v>0.133575655692091</v>
       </c>
       <c r="E34" s="29" t="n">
-        <v>0.69</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3395,13 +3395,13 @@
         <v>0.26438</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>0.218842029729208</v>
+        <v>0.208020935556482</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>0.136225528300797</v>
+        <v>0.134135192438779</v>
       </c>
       <c r="E35" s="29" t="n">
-        <v>0.67</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3412,13 +3412,13 @@
         <v>0.2798124</v>
       </c>
       <c r="C36" s="12" t="n">
-        <v>0.225730752476676</v>
+        <v>0.214188789049045</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>0.141349976678297</v>
+        <v>0.138723393761621</v>
       </c>
       <c r="E36" s="29" t="n">
-        <v>0.53</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3429,13 +3429,13 @@
         <v>0.2832</v>
       </c>
       <c r="C37" s="12" t="n">
-        <v>0.22724291112856</v>
+        <v>0.215542708108388</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>0.142474855590432</v>
+        <v>0.13973055990566</v>
       </c>
       <c r="E37" s="29" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3446,13 +3446,13 @@
         <v>0.297315</v>
       </c>
       <c r="C38" s="12" t="n">
-        <v>0.233543572178074</v>
+        <v>0.221184037522318</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>0.147161851057658</v>
+        <v>0.14392708550582</v>
       </c>
       <c r="E38" s="29" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3463,13 +3463,13 @@
         <v>0.31143</v>
       </c>
       <c r="C39" s="12" t="n">
-        <v>0.239844233227587</v>
+        <v>0.226825366936248</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>0.151848846524884</v>
+        <v>0.14812361110598</v>
       </c>
       <c r="E39" s="29" t="n">
-        <v>0.3</v>
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>
@@ -3559,23 +3559,23 @@
       </c>
       <c r="E6" s="29" t="n">
         <f aca="false">'Income Statement'!E14/Assumptions!$B$6</f>
-        <v>-0.316965598656371</v>
+        <v>-0.514463171141811</v>
       </c>
       <c r="F6" s="29" t="n">
         <f aca="false">'Income Statement'!F14/Assumptions!$B$6</f>
-        <v>-0.0208726092017952</v>
+        <v>-0.165156053742159</v>
       </c>
       <c r="G6" s="29" t="n">
         <f aca="false">'Income Statement'!G14/Assumptions!$B$6</f>
-        <v>0.0734229746732591</v>
+        <v>-0.0867672435282562</v>
       </c>
       <c r="H6" s="29" t="n">
         <f aca="false">'Income Statement'!H14/Assumptions!$B$6</f>
-        <v>0.190399720368901</v>
+        <v>0.0246250216579951</v>
       </c>
       <c r="I6" s="29" t="n">
         <f aca="false">'Income Statement'!I14/Assumptions!$B$6</f>
-        <v>0.2535356266776</v>
+        <v>0.121068901097832</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3602,17 +3602,17 @@
         <f aca="false">IF('Income Statement'!F14&gt;0,Assumptions!$B$5/('Income Statement'!F14/Assumptions!$B$6),"n.m.")</f>
         <v>n.m.</v>
       </c>
-      <c r="G7" s="26" t="n">
+      <c r="G7" s="26" t="str">
         <f aca="false">IF('Income Statement'!G14&gt;0,Assumptions!$B$5/('Income Statement'!G14/Assumptions!$B$6),"n.m.")</f>
-        <v>29.8271761631255</v>
+        <v>n.m.</v>
       </c>
       <c r="H7" s="26" t="n">
         <f aca="false">IF('Income Statement'!H14&gt;0,Assumptions!$B$5/('Income Statement'!H14/Assumptions!$B$6),"n.m.")</f>
-        <v>11.5021177329297</v>
+        <v>88.9339319337802</v>
       </c>
       <c r="I7" s="26" t="n">
         <f aca="false">IF('Income Statement'!I14&gt;0,Assumptions!$B$5/('Income Statement'!I14/Assumptions!$B$6),"n.m.")</f>
-        <v>8.63783929974008</v>
+        <v>18.0888731965141</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3633,23 +3633,23 @@
       </c>
       <c r="E8" s="12" t="n">
         <f aca="false">'Income Statement'!E7/'Income Statement'!E6</f>
-        <v>0.13</v>
+        <v>0.075</v>
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">'Income Statement'!F7/'Income Statement'!F6</f>
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">'Income Statement'!G7/'Income Statement'!G6</f>
-        <v>0.175</v>
+        <v>0.16</v>
       </c>
       <c r="H8" s="12" t="n">
         <f aca="false">'Income Statement'!H7/'Income Statement'!H6</f>
-        <v>0.185</v>
+        <v>0.175</v>
       </c>
       <c r="I8" s="12" t="n">
         <f aca="false">'Income Statement'!I7/'Income Statement'!I6</f>
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3670,23 +3670,23 @@
       </c>
       <c r="E9" s="12" t="n">
         <f aca="false">'Income Statement'!E14/'Income Statement'!E6</f>
-        <v>-0.12074279540462</v>
+        <v>-0.195976224800758</v>
       </c>
       <c r="F9" s="12" t="n">
         <f aca="false">'Income Statement'!F14/'Income Statement'!F6</f>
-        <v>-0.00697462701330789</v>
+        <v>-0.0551872486427003</v>
       </c>
       <c r="G9" s="12" t="n">
         <f aca="false">'Income Statement'!G14/'Income Statement'!G6</f>
-        <v>0.0219057536124172</v>
+        <v>-0.0258870178825759</v>
       </c>
       <c r="H9" s="12" t="n">
         <f aca="false">'Income Statement'!H14/'Income Statement'!H6</f>
-        <v>0.0516416183804128</v>
+        <v>0.00667898024538954</v>
       </c>
       <c r="I9" s="12" t="n">
         <f aca="false">'Income Statement'!I14/'Income Statement'!I6</f>
-        <v>0.0636720418406721</v>
+        <v>0.0304048162276929</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3732,23 +3732,23 @@
       </c>
       <c r="E11" s="29" t="n">
         <f aca="false">'Balance Sheet'!D12/Assumptions!$B$6</f>
-        <v>0.920381630732586</v>
+        <v>0.722884058247145</v>
       </c>
       <c r="F11" s="29" t="n">
         <f aca="false">'Balance Sheet'!E12/Assumptions!$B$6</f>
-        <v>0.899509021530791</v>
+        <v>0.557728004504987</v>
       </c>
       <c r="G11" s="29" t="n">
         <f aca="false">'Balance Sheet'!F12/Assumptions!$B$6</f>
-        <v>0.97293199620405</v>
+        <v>0.470960760976731</v>
       </c>
       <c r="H11" s="29" t="n">
         <f aca="false">'Balance Sheet'!G12/Assumptions!$B$6</f>
-        <v>1.16333171657295</v>
+        <v>0.495585782634726</v>
       </c>
       <c r="I11" s="29" t="n">
         <f aca="false">'Balance Sheet'!H12/Assumptions!$B$6</f>
-        <v>1.41686734325055</v>
+        <v>0.616654683732558</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3763,23 +3763,23 @@
       </c>
       <c r="E12" s="26" t="n">
         <f aca="false">Assumptions!$B$5/('Balance Sheet'!D12/Assumptions!$B$6)</f>
-        <v>2.37944774957846</v>
+        <v>3.02953146499084</v>
       </c>
       <c r="F12" s="26" t="n">
         <f aca="false">Assumptions!$B$5/('Balance Sheet'!E12/Assumptions!$B$6)</f>
-        <v>2.43466151820584</v>
+        <v>3.92664521471132</v>
       </c>
       <c r="G12" s="26" t="n">
         <f aca="false">Assumptions!$B$5/('Balance Sheet'!F12/Assumptions!$B$6)</f>
-        <v>2.25092813119973</v>
+        <v>4.65006892603565</v>
       </c>
       <c r="H12" s="26" t="n">
         <f aca="false">Assumptions!$B$5/('Balance Sheet'!G12/Assumptions!$B$6)</f>
-        <v>1.88252410623816</v>
+        <v>4.41901296755753</v>
       </c>
       <c r="I12" s="26" t="n">
         <f aca="false">Assumptions!$B$5/('Balance Sheet'!H12/Assumptions!$B$6)</f>
-        <v>1.5456634034459</v>
+        <v>3.55142036178841</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3790,27 +3790,27 @@
       <c r="C13" s="36"/>
       <c r="D13" s="26" t="n">
         <f aca="false">Assumptions!$B$28/'Income Statement'!D7</f>
-        <v>3.06481994188459</v>
+        <v>3.55240493263895</v>
       </c>
       <c r="E13" s="26" t="n">
         <f aca="false">'Balance Sheet'!D11/'Income Statement'!E7</f>
-        <v>6.42970969945681</v>
+        <v>13.8462308968452</v>
       </c>
       <c r="F13" s="26" t="n">
         <f aca="false">'Balance Sheet'!E11/'Income Statement'!F7</f>
-        <v>5.16136697217411</v>
+        <v>7.47619536789518</v>
       </c>
       <c r="G13" s="26" t="n">
         <f aca="false">'Balance Sheet'!F11/'Income Statement'!G7</f>
-        <v>4.45022587500995</v>
+        <v>6.35614292150564</v>
       </c>
       <c r="H13" s="26" t="n">
         <f aca="false">'Balance Sheet'!G11/'Income Statement'!H7</f>
-        <v>3.77535011257143</v>
+        <v>5.43862851517389</v>
       </c>
       <c r="I13" s="26" t="n">
         <f aca="false">'Balance Sheet'!H11/'Income Statement'!I7</f>
-        <v>3.18379125554478</v>
+        <v>4.79713368636585</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3819,27 +3819,27 @@
       </c>
       <c r="D14" s="12" t="n">
         <f aca="false">Assumptions!$B$28/Assumptions!$B$34</f>
-        <v>2.14634146341463</v>
+        <v>2.48780487804878</v>
       </c>
       <c r="E14" s="12" t="n">
         <f aca="false">'Balance Sheet'!D11/'Balance Sheet'!D12</f>
-        <v>2.38406272778021</v>
+        <v>3.77116112777517</v>
       </c>
       <c r="F14" s="12" t="n">
         <f aca="false">'Balance Sheet'!E11/'Balance Sheet'!E12</f>
-        <v>2.7474826084888</v>
+        <v>5.61619243462619</v>
       </c>
       <c r="G14" s="12" t="n">
         <f aca="false">'Balance Sheet'!F11/'Balance Sheet'!F12</f>
-        <v>2.68294268006434</v>
+        <v>7.2377351868341</v>
       </c>
       <c r="H14" s="12" t="n">
         <f aca="false">'Balance Sheet'!G11/'Balance Sheet'!G12</f>
-        <v>2.21356283580329</v>
+        <v>7.08068162797975</v>
       </c>
       <c r="I14" s="12" t="n">
         <f aca="false">'Balance Sheet'!H11/'Balance Sheet'!H12</f>
-        <v>1.70004028860105</v>
+        <v>5.57573994457157</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3848,23 +3848,23 @@
       </c>
       <c r="E15" s="12" t="n">
         <f aca="false">'Income Statement'!E14/'Balance Sheet'!D12</f>
-        <v>-0.344384968226799</v>
+        <v>-0.711681445001409</v>
       </c>
       <c r="F15" s="12" t="n">
         <f aca="false">'Income Statement'!F14/'Balance Sheet'!E12</f>
-        <v>-0.0232044467617168</v>
+        <v>-0.296122935208791</v>
       </c>
       <c r="G15" s="12" t="n">
         <f aca="false">'Income Statement'!G14/'Balance Sheet'!F12</f>
-        <v>0.0754656799855725</v>
+        <v>-0.184234549282426</v>
       </c>
       <c r="H15" s="12" t="n">
         <f aca="false">'Income Statement'!H14/'Balance Sheet'!G12</f>
-        <v>0.163667608865508</v>
+        <v>0.0496887169100755</v>
       </c>
       <c r="I15" s="12" t="n">
         <f aca="false">'Income Statement'!I14/'Balance Sheet'!H12</f>
-        <v>0.178940976997849</v>
+        <v>0.196331762802826</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4081,14 +4081,14 @@
         <v>25</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">DCF!B31</f>
-        <v>0.533988597838447</v>
+        <v>0.0233762361074855</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2.81</v>
+        <v>2.36</v>
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">Assumptions!B35</f>
@@ -4104,10 +4104,10 @@
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">'Relative &amp; Normalized'!C6</f>
-        <v>0.439283407880179</v>
+        <v>0.05</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.92</v>
+        <v>0.05</v>
       </c>
       <c r="E7" s="9" t="n">
         <f aca="false">Assumptions!B36</f>
@@ -4119,14 +4119,14 @@
         <v>27</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">'Relative &amp; Normalized'!C7</f>
-        <v>1.36704346653529</v>
+        <v>1.11377559810627</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="E8" s="9" t="n">
         <f aca="false">Assumptions!B37</f>
@@ -4158,15 +4158,15 @@
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">SUMPRODUCT(B6:B9,$E$6:$E$9)</f>
-        <v>0.302</v>
+        <v>0.246</v>
       </c>
       <c r="C10" s="11" t="n">
         <f aca="false">SUMPRODUCT(C6:C9,$E$6:$E$9)</f>
-        <v>0.756704789598169</v>
+        <v>0.423949589643946</v>
       </c>
       <c r="D10" s="11" t="n">
         <f aca="false">SUMPRODUCT(D6:D9,$E$6:$E$9)</f>
-        <v>2.046</v>
+        <v>1.624</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B13" s="12" t="n">
         <f aca="false">C10/Assumptions!B5-1</f>
-        <v>-0.654472698813621</v>
+        <v>-0.806415712491349</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4251,15 +4251,15 @@
       </c>
       <c r="B6" s="8" t="n">
         <f aca="false">Summary!B6</f>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">Summary!C6</f>
-        <v>0.533988597838447</v>
+        <v>0.0233762361074855</v>
       </c>
       <c r="D6" s="8" t="n">
         <f aca="false">Summary!D6</f>
-        <v>2.81</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4272,11 +4272,11 @@
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">Summary!C7</f>
-        <v>0.439283407880179</v>
+        <v>0.05</v>
       </c>
       <c r="D7" s="8" t="n">
         <f aca="false">Summary!D7</f>
-        <v>0.92</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4285,15 +4285,15 @@
       </c>
       <c r="B8" s="8" t="n">
         <f aca="false">Summary!B8</f>
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">Summary!C8</f>
-        <v>1.36704346653529</v>
+        <v>1.11377559810627</v>
       </c>
       <c r="D8" s="8" t="n">
         <f aca="false">Summary!D8</f>
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4319,15 +4319,15 @@
       </c>
       <c r="B10" s="15" t="n">
         <f aca="false">Summary!B10</f>
-        <v>0.302</v>
+        <v>0.246</v>
       </c>
       <c r="C10" s="15" t="n">
         <f aca="false">Summary!C10</f>
-        <v>0.756704789598169</v>
+        <v>0.423949589643946</v>
       </c>
       <c r="D10" s="15" t="n">
         <f aca="false">Summary!D10</f>
-        <v>2.046</v>
+        <v>1.624</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4494,7 +4494,7 @@
         <v>57</v>
       </c>
       <c r="B15" s="18" t="n">
-        <v>0.235</v>
+        <v>0.22</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>58</v>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B16" s="12" t="n">
         <f aca="false">B15*(1-B7)</f>
-        <v>0.182125</v>
+        <v>0.1705</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4523,7 +4523,7 @@
         <v>61</v>
       </c>
       <c r="B18" s="17" t="n">
-        <v>9000</v>
+        <v>10900</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>62</v>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="B19" s="12" t="n">
         <f aca="false">B17/(B17+B18)</f>
-        <v>0.446380520688198</v>
+        <v>0.399669104777182</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="B20" s="20" t="n">
         <f aca="false">B19*B14+(1-B19)*B16</f>
-        <v>0.225730752476676</v>
+        <v>0.214188789049045</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="B25" s="20" t="n">
         <f aca="false">B19*B23+(1-B19)*B24*(1-B7)</f>
-        <v>0.141349976678297</v>
+        <v>0.138723393761621</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4619,7 +4619,7 @@
         <v>76</v>
       </c>
       <c r="B28" s="17" t="n">
-        <v>8800</v>
+        <v>10200</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>77</v>
@@ -4770,19 +4770,19 @@
         <v>102</v>
       </c>
       <c r="C42" s="18" t="n">
-        <v>0.13</v>
+        <v>0.075</v>
       </c>
       <c r="D42" s="18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E42" s="18" t="n">
         <v>0.16</v>
       </c>
-      <c r="E42" s="18" t="n">
+      <c r="F42" s="18" t="n">
         <v>0.175</v>
       </c>
-      <c r="F42" s="18" t="n">
-        <v>0.185</v>
-      </c>
       <c r="G42" s="18" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="H42" s="13" t="s">
         <v>103</v>
@@ -4836,16 +4836,16 @@
         <v>107</v>
       </c>
       <c r="C45" s="18" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>0.93</v>
+        <v>0.94</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>0.88</v>
@@ -4859,16 +4859,16 @@
         <v>109</v>
       </c>
       <c r="C46" s="18" t="n">
-        <v>0.235</v>
+        <v>0.22</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>0.19</v>
+        <v>0.185</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>0.17</v>
+        <v>0.168</v>
       </c>
       <c r="G46" s="18" t="n">
         <v>0.155</v>
@@ -4887,15 +4887,15 @@
       </c>
       <c r="D47" s="12" t="n">
         <f aca="false">($C$46-D46)/($C$46-$G$46)</f>
-        <v>0.3125</v>
+        <v>0.307692307692308</v>
       </c>
       <c r="E47" s="12" t="n">
         <f aca="false">($C$46-E46)/($C$46-$G$46)</f>
-        <v>0.5625</v>
+        <v>0.538461538461539</v>
       </c>
       <c r="F47" s="12" t="n">
         <f aca="false">($C$46-F46)/($C$46-$G$46)</f>
-        <v>0.8125</v>
+        <v>0.8</v>
       </c>
       <c r="G47" s="12" t="n">
         <f aca="false">($C$46-G46)/($C$46-$G$46)</f>
@@ -4908,23 +4908,23 @@
       </c>
       <c r="C48" s="12" t="n">
         <f aca="false">$B$20-($B$20-$B$25)*C47</f>
-        <v>0.225730752476676</v>
+        <v>0.214188789049045</v>
       </c>
       <c r="D48" s="12" t="n">
         <f aca="false">$B$20-($B$20-$B$25)*D47</f>
-        <v>0.199361760039683</v>
+        <v>0.190968667422146</v>
       </c>
       <c r="E48" s="12" t="n">
         <f aca="false">$B$20-($B$20-$B$25)*E47</f>
-        <v>0.178266566090088</v>
+        <v>0.173553576201971</v>
       </c>
       <c r="F48" s="12" t="n">
         <f aca="false">$B$20-($B$20-$B$25)*F47</f>
-        <v>0.157171372140493</v>
+        <v>0.153816472819106</v>
       </c>
       <c r="G48" s="12" t="n">
         <f aca="false">$B$20-($B$20-$B$25)*G47</f>
-        <v>0.141349976678297</v>
+        <v>0.138723393761621</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4933,23 +4933,23 @@
       </c>
       <c r="C49" s="22" t="n">
         <f aca="false">1/(1+C48)</f>
-        <v>0.815839855514295</v>
+        <v>0.82359515177471</v>
       </c>
       <c r="D49" s="22" t="n">
         <f aca="false">C49/(1+D48)</f>
-        <v>0.6802283370176</v>
+        <v>0.691533853327463</v>
       </c>
       <c r="E49" s="22" t="n">
         <f aca="false">D49/(1+E48)</f>
-        <v>0.577312771654756</v>
+        <v>0.589264834048317</v>
       </c>
       <c r="F49" s="22" t="n">
         <f aca="false">E49/(1+F48)</f>
-        <v>0.498899977612532</v>
+        <v>0.510709326768904</v>
       </c>
       <c r="G49" s="22" t="n">
         <f aca="false">F49/(1+G48)</f>
-        <v>0.437113933330507</v>
+        <v>0.448492873305996</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4973,7 +4973,7 @@
         <v>117</v>
       </c>
       <c r="B52" s="17" t="n">
-        <v>12000</v>
+        <v>12640</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>118</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="B5" s="23" t="n">
         <f aca="false">DCF!B26</f>
-        <v>10569.3927776594</v>
+        <v>10277.4581021109</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="B7" s="24" t="n">
         <f aca="false">-Assumptions!B28</f>
-        <v>-8800</v>
+        <v>-10200</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="B9" s="23" t="n">
         <f aca="false">B5+B6+B7+B8</f>
-        <v>1769.39277765935</v>
+        <v>77.4581021109334</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="B10" s="15" t="n">
         <f aca="false">B9/Assumptions!B6</f>
-        <v>0.533988597838447</v>
+        <v>0.0233762361074855</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">B10/Assumptions!B5-1</f>
-        <v>-0.756169590028107</v>
+        <v>-0.989325919585623</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="B15" s="6" t="n">
         <f aca="false">B14+Assumptions!B28</f>
-        <v>16056.65341687</v>
+        <v>17456.65341687</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="B16" s="26" t="n">
         <f aca="false">B15/Segments!F9</f>
-        <v>10.1201518655457</v>
+        <v>12.5743322939126</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="B17" s="26" t="n">
         <f aca="false">B15/Segments!D9</f>
-        <v>5.59213086272187</v>
+        <v>6.07971585347624</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5294,23 +5294,23 @@
       </c>
       <c r="E9" s="24" t="n">
         <f aca="false">E6*Assumptions!C42</f>
-        <v>1130.80188</v>
+        <v>652.3857</v>
       </c>
       <c r="F9" s="24" t="n">
         <f aca="false">F6*Assumptions!D42</f>
-        <v>1586.6020224</v>
+        <v>1388.2767696</v>
       </c>
       <c r="G9" s="24" t="n">
         <f aca="false">G6*Assumptions!E42</f>
-        <v>1943.58747744</v>
+        <v>1776.994265088</v>
       </c>
       <c r="H9" s="24" t="n">
         <f aca="false">H6*Assumptions!F42</f>
-        <v>2260.1145809088</v>
+        <v>2137.946225184</v>
       </c>
       <c r="I9" s="24" t="n">
         <f aca="false">I6*Assumptions!G42</f>
-        <v>2506.8946594729</v>
+        <v>2374.95283529011</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5331,23 +5331,23 @@
       </c>
       <c r="E10" s="12" t="n">
         <f aca="false">E9/E6</f>
-        <v>0.13</v>
+        <v>0.075</v>
       </c>
       <c r="F10" s="12" t="n">
         <f aca="false">F9/F6</f>
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="G10" s="12" t="n">
         <f aca="false">G9/G6</f>
-        <v>0.175</v>
+        <v>0.16</v>
       </c>
       <c r="H10" s="12" t="n">
         <f aca="false">H9/H6</f>
-        <v>0.185</v>
+        <v>0.175</v>
       </c>
       <c r="I10" s="12" t="n">
         <f aca="false">I9/I6</f>
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5399,23 +5399,23 @@
       </c>
       <c r="E12" s="19" t="n">
         <f aca="false">E9-E11</f>
-        <v>1017.721692</v>
+        <v>539.305512</v>
       </c>
       <c r="F12" s="19" t="n">
         <f aca="false">F9-F11</f>
-        <v>1457.69060808</v>
+        <v>1259.36535528</v>
       </c>
       <c r="G12" s="19" t="n">
         <f aca="false">G9-G11</f>
-        <v>1799.2066934016</v>
+        <v>1632.6134810496</v>
       </c>
       <c r="H12" s="19" t="n">
         <f aca="false">H9-H11</f>
-        <v>2101.29571846656</v>
+        <v>1979.12736274176</v>
       </c>
       <c r="I12" s="19" t="n">
         <f aca="false">I9-I11</f>
-        <v>2335.37028803528</v>
+        <v>2203.42846385249</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">MAX((Assumptions!B31*Segments!F9-'Balance Sheet'!D11)/Assumptions!B6,0.05)</f>
-        <v>0.439283407880179</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">(Segments!G12-Assumptions!B24*6000)*(1-Assumptions!B7)*Assumptions!B32/Assumptions!B6</f>
-        <v>1.36704346653529</v>
+        <v>1.11377559810627</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">(Segments!G12-Assumptions!B24*6000)*(1-Assumptions!B7)/Assumptions!B6</f>
-        <v>0.210314379466968</v>
+        <v>0.17135009201635</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5616,23 +5616,23 @@
       </c>
       <c r="B7" s="24" t="n">
         <f aca="false">Segments!E9</f>
-        <v>1130.80188</v>
+        <v>652.3857</v>
       </c>
       <c r="C7" s="24" t="n">
         <f aca="false">Segments!F9</f>
-        <v>1586.6020224</v>
+        <v>1388.2767696</v>
       </c>
       <c r="D7" s="24" t="n">
         <f aca="false">Segments!G9</f>
-        <v>1943.58747744</v>
+        <v>1776.994265088</v>
       </c>
       <c r="E7" s="24" t="n">
         <f aca="false">Segments!H9</f>
-        <v>2260.1145809088</v>
+        <v>2137.946225184</v>
       </c>
       <c r="F7" s="24" t="n">
         <f aca="false">Segments!I9</f>
-        <v>2506.8946594729</v>
+        <v>2374.95283529011</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5666,23 +5666,23 @@
       </c>
       <c r="B9" s="24" t="n">
         <f aca="false">Segments!E12</f>
-        <v>1017.721692</v>
+        <v>539.305512</v>
       </c>
       <c r="C9" s="24" t="n">
         <f aca="false">Segments!F12</f>
-        <v>1457.69060808</v>
+        <v>1259.36535528</v>
       </c>
       <c r="D9" s="24" t="n">
         <f aca="false">Segments!G12</f>
-        <v>1799.2066934016</v>
+        <v>1632.6134810496</v>
       </c>
       <c r="E9" s="24" t="n">
         <f aca="false">Segments!H12</f>
-        <v>2101.29571846656</v>
+        <v>1979.12736274176</v>
       </c>
       <c r="F9" s="24" t="n">
         <f aca="false">Segments!I12</f>
-        <v>2335.37028803528</v>
+        <v>2203.42846385249</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5691,23 +5691,23 @@
       </c>
       <c r="B10" s="24" t="n">
         <f aca="false">B9*(1-Assumptions!$B$7)</f>
-        <v>788.7343113</v>
+        <v>417.9617718</v>
       </c>
       <c r="C10" s="24" t="n">
         <f aca="false">C9*(1-Assumptions!$B$7)</f>
-        <v>1129.710221262</v>
+        <v>976.008150342</v>
       </c>
       <c r="D10" s="24" t="n">
         <f aca="false">D9*(1-Assumptions!$B$7)</f>
-        <v>1394.38518738624</v>
+        <v>1265.27544781344</v>
       </c>
       <c r="E10" s="24" t="n">
         <f aca="false">E9*(1-Assumptions!$B$7)</f>
-        <v>1628.50418181158</v>
+        <v>1533.82370612486</v>
       </c>
       <c r="F10" s="24" t="n">
         <f aca="false">F9*(1-Assumptions!$B$7)</f>
-        <v>1809.91197322734</v>
+        <v>1707.65705948568</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5766,19 +5766,19 @@
       </c>
       <c r="B13" s="24" t="n">
         <f aca="false">B6*Assumptions!C45</f>
-        <v>9394.35408</v>
+        <v>9742.29312</v>
       </c>
       <c r="C13" s="24" t="n">
         <f aca="false">C6*Assumptions!D45</f>
-        <v>10213.7505192</v>
+        <v>10511.2383984</v>
       </c>
       <c r="D13" s="24" t="n">
         <f aca="false">D6*Assumptions!E45</f>
-        <v>10884.089873664</v>
+        <v>11106.2141568</v>
       </c>
       <c r="E13" s="24" t="n">
         <f aca="false">E6*Assumptions!F45</f>
-        <v>11361.6570824064</v>
+        <v>11483.8254381312</v>
       </c>
       <c r="F13" s="24" t="n">
         <f aca="false">F6*Assumptions!G45</f>
@@ -5791,23 +5791,23 @@
       </c>
       <c r="B14" s="24" t="n">
         <f aca="false">-(B13-Assumptions!$B$52)</f>
-        <v>2605.64592</v>
+        <v>2897.70688</v>
       </c>
       <c r="C14" s="6" t="n">
         <f aca="false">-(C13-B13)</f>
-        <v>-819.3964392</v>
+        <v>-768.945278399999</v>
       </c>
       <c r="D14" s="6" t="n">
         <f aca="false">-(D13-C13)</f>
-        <v>-670.339354464002</v>
+        <v>-594.975758400002</v>
       </c>
       <c r="E14" s="6" t="n">
         <f aca="false">-(E13-D13)</f>
-        <v>-477.567208742401</v>
+        <v>-377.611281331201</v>
       </c>
       <c r="F14" s="6" t="n">
         <f aca="false">-(F13-E13)</f>
-        <v>-249.223445678594</v>
+        <v>-127.055089953794</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5816,23 +5816,23 @@
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">B10+B11+B12+B14</f>
-        <v>3368.2848033</v>
+        <v>3289.5732238</v>
       </c>
       <c r="C15" s="19" t="n">
         <f aca="false">C10+C11+C12+C14</f>
-        <v>280.564994142</v>
+        <v>177.314084022002</v>
       </c>
       <c r="D15" s="19" t="n">
         <f aca="false">D10+D11+D12+D14</f>
-        <v>690.727190451838</v>
+        <v>636.981046943039</v>
       </c>
       <c r="E15" s="19" t="n">
         <f aca="false">E10+E11+E12+E14</f>
-        <v>1114.28646635174</v>
+        <v>1119.56191807622</v>
       </c>
       <c r="F15" s="19" t="n">
         <f aca="false">F10+F11+F12+F14</f>
-        <v>1521.10598029391</v>
+        <v>1541.01942227705</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5841,23 +5841,23 @@
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">Assumptions!C48</f>
-        <v>0.225730752476676</v>
+        <v>0.214188789049045</v>
       </c>
       <c r="C16" s="9" t="n">
         <f aca="false">Assumptions!D48</f>
-        <v>0.199361760039683</v>
+        <v>0.190968667422146</v>
       </c>
       <c r="D16" s="9" t="n">
         <f aca="false">Assumptions!E48</f>
-        <v>0.178266566090088</v>
+        <v>0.173553576201971</v>
       </c>
       <c r="E16" s="9" t="n">
         <f aca="false">Assumptions!F48</f>
-        <v>0.157171372140493</v>
+        <v>0.153816472819106</v>
       </c>
       <c r="F16" s="9" t="n">
         <f aca="false">Assumptions!G48</f>
-        <v>0.141349976678297</v>
+        <v>0.138723393761621</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5866,23 +5866,23 @@
       </c>
       <c r="B17" s="28" t="n">
         <f aca="false">Assumptions!C49</f>
-        <v>0.815839855514295</v>
+        <v>0.82359515177471</v>
       </c>
       <c r="C17" s="28" t="n">
         <f aca="false">Assumptions!D49</f>
-        <v>0.6802283370176</v>
+        <v>0.691533853327463</v>
       </c>
       <c r="D17" s="28" t="n">
         <f aca="false">Assumptions!E49</f>
-        <v>0.577312771654756</v>
+        <v>0.589264834048317</v>
       </c>
       <c r="E17" s="28" t="n">
         <f aca="false">Assumptions!F49</f>
-        <v>0.498899977612532</v>
+        <v>0.510709326768904</v>
       </c>
       <c r="F17" s="28" t="n">
         <f aca="false">Assumptions!G49</f>
-        <v>0.437113933330507</v>
+        <v>0.448492873305996</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5891,23 +5891,23 @@
       </c>
       <c r="B18" s="19" t="n">
         <f aca="false">B15*B17</f>
-        <v>2747.98098725527</v>
+        <v>2709.27655852958</v>
       </c>
       <c r="C18" s="19" t="n">
         <f aca="false">C15*C17</f>
-        <v>190.848259390566</v>
+        <v>122.618691772964</v>
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">D15*D17</f>
-        <v>398.765628777053</v>
+        <v>375.350530918813</v>
       </c>
       <c r="E18" s="19" t="n">
         <f aca="false">E15*E17</f>
-        <v>555.917493116833</v>
+        <v>571.770713456811</v>
       </c>
       <c r="F18" s="19" t="n">
         <f aca="false">F15*F17</f>
-        <v>664.896618058828</v>
+        <v>691.136228517381</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="B20" s="19" t="n">
         <f aca="false">SUM(B18:F18)</f>
-        <v>4558.40898659855</v>
+        <v>4470.15272319555</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="B21" s="12" t="n">
         <f aca="false">F10/(F13+0.05*F6)</f>
-        <v>0.1475</v>
+        <v>0.139166666666667</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="B22" s="12" t="n">
         <f aca="false">Assumptions!$B$26/B21</f>
-        <v>0.338983050847458</v>
+        <v>0.359281437125749</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="B23" s="6" t="n">
         <f aca="false">F10*(1+Assumptions!$B$26)*(1-B22)</f>
-        <v>1256.20161531626</v>
+        <v>1148.83395588752</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B24" s="6" t="n">
         <f aca="false">B23/(Assumptions!$B$25-Assumptions!$B$26)</f>
-        <v>13751.5263932707</v>
+        <v>12948.4897632993</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="B25" s="6" t="n">
         <f aca="false">B24*F17</f>
-        <v>6010.98379106081</v>
+        <v>5807.30537891538</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="B26" s="19" t="n">
         <f aca="false">B20+B25</f>
-        <v>10569.3927776594</v>
+        <v>10277.4581021109</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="B27" s="12" t="n">
         <f aca="false">B25/B26</f>
-        <v>0.568716095381212</v>
+        <v>0.565052693109261</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="B28" s="24" t="n">
         <f aca="false">-Assumptions!$B$28</f>
-        <v>-8800</v>
+        <v>-10200</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="B30" s="19" t="n">
         <f aca="false">B26-Assumptions!$B$28-Assumptions!$B$29</f>
-        <v>1769.39277765935</v>
+        <v>77.4581021109334</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="B31" s="11" t="n">
         <f aca="false">B30/Assumptions!$B$6</f>
-        <v>0.533988597838447</v>
+        <v>0.0233762361074855</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="B32" s="20" t="n">
         <f aca="false">B31/Assumptions!$B$5-1</f>
-        <v>-0.756169590028107</v>
+        <v>-0.989325919585623</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6150,23 +6150,23 @@
       </c>
       <c r="E7" s="24" t="n">
         <f aca="false">Segments!E9</f>
-        <v>1130.80188</v>
+        <v>652.3857</v>
       </c>
       <c r="F7" s="24" t="n">
         <f aca="false">Segments!F9</f>
-        <v>1586.6020224</v>
+        <v>1388.2767696</v>
       </c>
       <c r="G7" s="24" t="n">
         <f aca="false">Segments!G9</f>
-        <v>1943.58747744</v>
+        <v>1776.994265088</v>
       </c>
       <c r="H7" s="24" t="n">
         <f aca="false">Segments!H9</f>
-        <v>2260.1145809088</v>
+        <v>2137.946225184</v>
       </c>
       <c r="I7" s="24" t="n">
         <f aca="false">Segments!I9</f>
-        <v>2506.8946594729</v>
+        <v>2374.95283529011</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6218,23 +6218,23 @@
       </c>
       <c r="E9" s="23" t="n">
         <f aca="false">Segments!E12</f>
-        <v>1017.721692</v>
+        <v>539.305512</v>
       </c>
       <c r="F9" s="23" t="n">
         <f aca="false">Segments!F12</f>
-        <v>1457.69060808</v>
+        <v>1259.36535528</v>
       </c>
       <c r="G9" s="23" t="n">
         <f aca="false">Segments!G12</f>
-        <v>1799.2066934016</v>
+        <v>1632.6134810496</v>
       </c>
       <c r="H9" s="23" t="n">
         <f aca="false">Segments!H12</f>
-        <v>2101.29571846656</v>
+        <v>1979.12736274176</v>
       </c>
       <c r="I9" s="23" t="n">
         <f aca="false">Segments!I12</f>
-        <v>2335.37028803528</v>
+        <v>2203.42846385249</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6252,23 +6252,23 @@
       </c>
       <c r="E10" s="24" t="n">
         <f aca="false">-Assumptions!C46*Assumptions!$B$28</f>
-        <v>-2068</v>
+        <v>-2244</v>
       </c>
       <c r="F10" s="24" t="n">
         <f aca="false">-Assumptions!D46*'Balance Sheet'!D11</f>
-        <v>-1526.85284136</v>
+        <v>-1806.6166072</v>
       </c>
       <c r="G10" s="24" t="n">
         <f aca="false">-Assumptions!E46*'Balance Sheet'!E11</f>
-        <v>-1555.916702516</v>
+        <v>-1920.1202455344</v>
       </c>
       <c r="H10" s="24" t="n">
         <f aca="false">-Assumptions!F46*'Balance Sheet'!F11</f>
-        <v>-1470.3985580163</v>
+        <v>-1897.53135929199</v>
       </c>
       <c r="I10" s="24" t="n">
         <f aca="false">-Assumptions!G46*'Balance Sheet'!G11</f>
-        <v>-1322.57219480605</v>
+        <v>-1802.26177215008</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6286,23 +6286,23 @@
       </c>
       <c r="E11" s="19" t="n">
         <f aca="false">E9+E10</f>
-        <v>-1050.278308</v>
+        <v>-1704.694488</v>
       </c>
       <c r="F11" s="19" t="n">
         <f aca="false">F9+F10</f>
-        <v>-69.1622332799998</v>
+        <v>-547.25125192</v>
       </c>
       <c r="G11" s="19" t="n">
         <f aca="false">G9+G10</f>
-        <v>243.2899908856</v>
+        <v>-287.5067644848</v>
       </c>
       <c r="H11" s="19" t="n">
         <f aca="false">H9+H10</f>
-        <v>630.897160450264</v>
+        <v>81.5960034497662</v>
       </c>
       <c r="I11" s="19" t="n">
         <f aca="false">I9+I10</f>
-        <v>1012.79809322923</v>
+        <v>401.166691702412</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6311,23 +6311,23 @@
       </c>
       <c r="E12" s="6" t="n">
         <f aca="false">SUM($E$11:E11)</f>
-        <v>-1050.278308</v>
+        <v>-1704.694488</v>
       </c>
       <c r="F12" s="6" t="n">
         <f aca="false">SUM($E$11:F11)</f>
-        <v>-1119.44054128</v>
+        <v>-2251.94573992</v>
       </c>
       <c r="G12" s="6" t="n">
         <f aca="false">SUM($E$11:G11)</f>
-        <v>-876.150550394399</v>
+        <v>-2539.4525044048</v>
       </c>
       <c r="H12" s="6" t="n">
         <f aca="false">SUM($E$11:H11)</f>
-        <v>-245.253389944135</v>
+        <v>-2457.85650095503</v>
       </c>
       <c r="I12" s="6" t="n">
         <f aca="false">SUM($E$11:I11)</f>
-        <v>767.544703285094</v>
+        <v>-2056.68980925262</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="I13" s="24" t="n">
         <f aca="false">-(Assumptions!$B$7*MAX(0,I12)-Assumptions!$B$7*MAX(0,F12))</f>
-        <v>-172.697558239146</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6379,23 +6379,23 @@
       </c>
       <c r="E14" s="19" t="n">
         <f aca="false">E11+E13</f>
-        <v>-1050.278308</v>
+        <v>-1704.694488</v>
       </c>
       <c r="F14" s="19" t="n">
         <f aca="false">F11+F13</f>
-        <v>-69.1622332799998</v>
+        <v>-547.25125192</v>
       </c>
       <c r="G14" s="19" t="n">
         <f aca="false">G11+G13</f>
-        <v>243.2899908856</v>
+        <v>-287.5067644848</v>
       </c>
       <c r="H14" s="19" t="n">
         <f aca="false">H11+H13</f>
-        <v>630.897160450264</v>
+        <v>81.5960034497662</v>
       </c>
       <c r="I14" s="19" t="n">
         <f aca="false">I11+I13</f>
-        <v>840.100534990083</v>
+        <v>401.166691702412</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6416,23 +6416,23 @@
       </c>
       <c r="E15" s="8" t="n">
         <f aca="false">E14/Assumptions!$B$6</f>
-        <v>-0.316965598656371</v>
+        <v>-0.514463171141811</v>
       </c>
       <c r="F15" s="8" t="n">
         <f aca="false">F14/Assumptions!$B$6</f>
-        <v>-0.0208726092017952</v>
+        <v>-0.165156053742159</v>
       </c>
       <c r="G15" s="8" t="n">
         <f aca="false">G14/Assumptions!$B$6</f>
-        <v>0.0734229746732591</v>
+        <v>-0.0867672435282562</v>
       </c>
       <c r="H15" s="8" t="n">
         <f aca="false">H14/Assumptions!$B$6</f>
-        <v>0.190399720368901</v>
+        <v>0.0246250216579951</v>
       </c>
       <c r="I15" s="8" t="n">
         <f aca="false">I14/Assumptions!$B$6</f>
-        <v>0.2535356266776</v>
+        <v>0.121068901097832</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/engine/elec_study/ELEC_Valuation_Model_05082026_public.xlsx
+++ b/engine/elec_study/ELEC_Valuation_Model_05082026_public.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="330">
   <si>
     <t xml:space="preserve">Testahil — Electro Cable Egypt Co. S.A.E. (EGX: ELEC)</t>
   </si>
@@ -49,10 +49,13 @@
     <t xml:space="preserve">black cell is a formula; green cells link across sheets. All inputs live on the Assumptions sheet — change one</t>
   </si>
   <si>
-    <t xml:space="preserve">(the EBITDA margin path, the working-capital intensity, the terminal WACC, the net-debt anchor) and the whole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">model reprices.</t>
+    <t xml:space="preserve">(volumes, copper, the EGP path, conversion EBITDA per tonne, the working-capital intensity, the net-debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anchor) and the whole model reprices. The forecast is a bottom-up TONNAGE build: revenue = volume x (LME x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGP x 1.387 fabrication uplift); EBITDA = volume x conversion EBITDA/t. Margins are outputs, not inputs.</t>
   </si>
   <si>
     <t xml:space="preserve">What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
@@ -76,7 +79,7 @@
     <t xml:space="preserve">year, closes to the reported net profit within 0.8% using the derived lines.</t>
   </si>
   <si>
-    <t xml:space="preserve">Discount convention. Each explicit year is discounted at its own forward WACC, gliding 21.4% -&gt; 13.9% on the</t>
+    <t xml:space="preserve">Discount convention. Each explicit year is discounted at its own forward WACC, gliding 21.4% -&gt; 15.0% on the</t>
   </si>
   <si>
     <t xml:space="preserve">same easing calendar as the interest forecast; the terminal value is capitalised at the terminal WACC and</t>
@@ -253,7 +256,7 @@
     <t xml:space="preserve">Egyptian long-run corporate norm 14-16%, midpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">WACC — terminal</t>
+    <t xml:space="preserve">WACC — terminal (normalized structure, see B56)</t>
   </si>
   <si>
     <t xml:space="preserve">Terminal growth g</t>
@@ -337,505 +340,574 @@
     <t xml:space="preserve">FY30E</t>
   </si>
   <si>
-    <t xml:space="preserve">Revenue growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY26E on Q1-26 -44%; recovery on the grid-capex cycle</t>
+    <t xml:space="preserve">Volume (kt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1-26 implied ~2.4kt/qtr sets FY26E (~42% util.); recovery to 64% by FY30E on the grid-capex cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LME copper (USD/t)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flat at the 2026 consensus avg — no house commodity view; bull/bear move it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGP/USD (avg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~3%/yr crawl; inflation differential narrows as CBE targets bite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conversion EBITDA per tonne (k EGP/t)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hist: 111 (FY23), 146 (FY24), 182 (FY25, copper-gain inflated), 11 (Q1-26). FY30E 13.7% of price = pre-windfall 2022 norm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capex (EGP mn)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintenance ~EGP 9k per tonne of 25kt capacity, escalated ~8%/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D&amp;A (% of revenue)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net working capital (% of revenue)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From ~117% FY25e; NOT full reversion to FY24 76%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forward Kd path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBE easing resumption; sets the WACC glide shape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glide fraction (from the Kd path)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forward WACC (that year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative discount factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASE-YEAR ANCHORS (FY2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue FY25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arab Finance/Zawya FY2025 results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net working capital FY25 (derived)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~117% of FY25 revenue — construction in study §1.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabrication uplift k (price/t ÷ copper cost/t)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copper ~72% of cable price (industry norm); FY24 back-solves to 24.0kt = 96% of capacity — the validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminal debt weight D/(D+E)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORMALIZED structure — not today’s ~60% distress weight (circular into perpetuity); conservative direction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacity (kt/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company profile via IATF page — single-sourced, possibly parent-only; utilization indicative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV → equity bridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-business company: the bridge is the DCF EV less net claims. Links to DCF / Assumptions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core enterprise value (DCF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ Surplus / non-core assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">− Net debt (FY25: disclosed facilities − est. cash)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">− Non-controlling interests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity value — intrinsic (may be negative)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity value — floored (limited liability)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per share (EGP) — floored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upside / (downside) vs spot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market-implied read (the same bridge run backwards)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market cap at spot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ Net debt = market-implied EV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market-implied EV / FY27E EBITDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market-implied EV / FY25 EBITDA (windfall-vintage)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The market pays a peer-level multiple on windfall-vintage EBITDA — the study’s central observation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segment view — the revenue and margin build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-segment build (power ~2/3, telecom ~1/3 of revenue — memo estimate; no segment disclosure). Forecast links to Assumptions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume (kt) — implied hist / driver fwd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilization (÷ 25 kt capacity)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LME copper (USD/t, avg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price per tonne (EGP, = Cu × EGP × k)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue (= volume × price/t)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  memo: power cables (~2/3, est.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  memo: telecom &amp; other (~1/3, est.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA (= volume × EBITDA/t)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA margin — OUTPUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTTOM-UP TONNAGE BUILD. Historical volumes are IMPLIED (revenue ÷ [LME × EGP × k]; k = 1.387 from the industry copper-share norm; FY24 back-solves to 24.0kt = 96% of stated capacity — the validation). Historical conversion EBITDA/t: 111 (FY23) / 146 (FY24) / 182 (FY25, copper-gain inflated) / 11 (Q1-26 annualized ~9.5kt, 38% utilization). Q1-26 disclosed: GM 5.7%, operating profit ~0. Forecast volumes/copper/EGP/EBITDA-per-t are Assumptions drivers; margins are outputs. Capacity single-sourced, possibly parent-only — utilization indicative.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY23 note: at the 2023 parallel rate (~38 vs official 30.7) implied volume is 19.4kt (78%) — the honest range for that year.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relative &amp; normalized-earnings lenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Links to Assumptions / Segments / Balance Sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGP/share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relative EV/EBITDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY27E EBITDA × multiple − net debt end-FY26E, /sh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normalized earnings power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY28E EBIT − 15% money on 6,000 mid-cycle ND, × (1−t), × P/E, /sh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  normalized EPS (EGP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book lens: justified P/B × BVPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(ROE−g)/(Ke_term−g) × FY25e book/sh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P/B at spot (memo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCF — explicit 5-year FCFF on the forward-WACC schedule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue -&gt; EBITDA -&gt; D&amp;A -&gt; EBIT -&gt; NOPAT -&gt; +D&amp;A -&gt; -Capex -&gt; -dWC -&gt; FCFF -&gt; forward WACC -&gt; cumulative DF -&gt; PV. Terminal is ROIC-consistent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">− D&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOPAT = EBIT × (1 − tax)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ D&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">− Capex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net working capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">− Δ working capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free cash flow to firm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PV of FCFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Σ PV of explicit FCFF (FY26–30E)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminal ROIC (NOPAT ÷ [NWC + 5% of revenue])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminal reinvestment rate = g ÷ ROIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminal FCFF = NOPAT × (1+g) × (1 − RR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminal value (at terminal WACC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PV of terminal value (year-5 factor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enterprise value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminal value as % of EV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">less: net debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">less: non-controlling interests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity value — INTRINSIC (may be negative)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity value — floored at zero (limited liability)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intrinsic per share (EGP, unfloored)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fair value per share (EGP) — floored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The glide: each year at its own forward WACC (22.6% -&gt; 14.1%), shape from the forward Kd path; the terminal is capitalised at the terminal WACC and discounted at the identical year-5 cumulative factor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income statement (EGP mn, consolidated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY23–FY25 as sourced/derived (blue; (d)-flagged in the study); FY26E–FY30E formulas. Interest on OPENING net debt at that year’s forward Kd; tax on positive EBT net of loss carryforward.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net finance cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnings before tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative EBT since FY26E (memo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income tax (22.5% of positive cumulative EBT, incremental)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net profit (attributable)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPS (EGP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historical net finance cost is (d)-derived (FY24 via the disclosed 2.0x coverage; FY23/FY25 back-solved to the reported NP). Loss carryforward per Egyptian tax law (5yr) modelled via cumulative-EBT tax.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance sheet — condensed invested-capital layout (EGP mn)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC = NWC + PP&amp;E + other assets; financed by net debt + equity + flat non-debt liabilities. Check row is zero by construction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY25e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PP&amp;E (roll: + capex - D&amp;A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other assets (held flat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invested capital (net of payables)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net debt (schedule: opening − equity FCF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity (roll: + net profit, no dividends)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-debt liabilities &amp; other (flat plug at FY25e)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total financing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance check (IC − financing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY24 column: SWS-sourced anchors (debt 9,000/cash 828/equity 3,600); FY25e column: derived (study §1.6). The forecast check row is zero by construction: PP&amp;E rolls with capex − D&amp;A, NWC with its driver, net debt with the cash-flow sheet, equity with net profit, and the non-debt-liabilities plug is held flat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash flow (EGP mn, forecast)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity free cash flow feeds the net-debt schedule (surplus repays debt; deficit is drawn). FCFF memo ties to the DCF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net profit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating − investing cash flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dividends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity free cash flow (repays / draws net debt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">memo: FCFF (ties to DCF row)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">memo: net debt, closing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No dividends modelled — the company has never paid one and the balance sheet argues against a first.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary financials (EGP mn)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every forecast cell links to the statement sheets; history as sourced/derived.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net debt (closing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity (attributable)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FCFF (forecast)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monte Carlo — engine outputs (carry-anchored YZ-HAR-t)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50,000 paths · Student-t(6) · width calibrated on the 30-name Egyptian panel · drift = local carry (19.50%) · values computed by the engine, not a sheet simulation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The probability read (3 months)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(price above spot)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(+10%) vs P(−10%) — odds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37% vs 18% · 2.1:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median level (EGP) and % move</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29 (+4.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50% band (25th–75th)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06 – 2.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Touch(+10%) / touch(−10%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60% / 39%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentile map (EGP/share)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level-touch ladder (probability of touching by horizon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level (EGP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probability zones (3 months)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deep downside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt; 1.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lower band</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80–2.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Around spot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05–2.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upper band</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35–2.70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong upside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt; 2.70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensitivity — engine grids (values) + the live base cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grids are engine outputs under the full glide re-computation; the base cell reprices live off Assumptions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live base DCF (links to the DCF sheet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminal WACC × terminal g (EGP/share)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminal WACC \ g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explicit-window WACC × terminal WACC (EGP/share)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explicit \ terminal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA-margin shift × terminal NWC intensity (EGP/share)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margin shift \ NWC %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beta grid (Ke / WACCs / DCF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WACC explicit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WACC terminal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCF (EGP/sh)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-share &amp; ratios — the standing dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Links to statements / Assumptions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P/E at spot (×)</t>
   </si>
   <si>
     <t xml:space="preserve">EBITDA margin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1Q26 DISCLOSED: gross margin 5.7%, operating ~0 — the trough; windfall prints ~25% the ceiling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D&amp;A (% of revenue)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capex (% of revenue)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No disclosed capex any year — flagged derivation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net working capital (% of revenue)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">From ~117% FY25e; NOT full reversion to FY24 76%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forward Kd path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CBE easing resumption; sets the WACC glide shape</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glide fraction (from the Kd path)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forward WACC (that year)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative discount factor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASE-YEAR ANCHORS (FY2025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue FY25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arab Finance/Zawya FY2025 results</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net working capital FY25 (derived)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~117% of FY25 revenue — construction in study §1.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EV → equity bridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single-business company: the bridge is the DCF EV less net claims. Links to DCF / Assumptions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core enterprise value (DCF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+ Surplus / non-core assets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">− Net debt (FY25: disclosed facilities − est. cash)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">− Non-controlling interests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per share (EGP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upside / (downside) vs spot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market-implied read (the same bridge run backwards)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market cap at spot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+ Net debt = market-implied EV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market-implied EV / FY27E EBITDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market-implied EV / FY25 EBITDA (windfall-vintage)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The market pays a peer-level multiple on windfall-vintage EBITDA — the study’s central observation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segment view — the revenue and margin build</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single-segment build (power ~2/3, telecom ~1/3 of revenue — memo estimate; no segment disclosure). Forecast links to Assumptions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  memo: power cables (~2/3, est.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  memo: telecom &amp; other (~1/3, est.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EBITDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D&amp;A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EBIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Historical EBITDA/D&amp;A/EBIT: FY24 aggregator-sourced (EBIT 3,400, SWS; EBITDA 3,490, Investing.com); FY23/FY25 derived by closing the P&amp;L to the reported net profit — flagged (d) in the study.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relative &amp; normalized-earnings lenses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Links to Assumptions / Segments / Balance Sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EGP/share</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relative EV/EBITDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY27E EBITDA × multiple − net debt end-FY26E, /sh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Normalized earnings power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY28E EBIT − 15% money on 6,000 mid-cycle ND, × (1−t), × P/E, /sh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  normalized EPS (EGP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book lens: justified P/B × BVPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(ROE−g)/(Ke_term−g) × FY25e book/sh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P/B at spot (memo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCF — explicit 5-year FCFF on the forward-WACC schedule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue -&gt; EBITDA -&gt; D&amp;A -&gt; EBIT -&gt; NOPAT -&gt; +D&amp;A -&gt; -Capex -&gt; -dWC -&gt; FCFF -&gt; forward WACC -&gt; cumulative DF -&gt; PV. Terminal is ROIC-consistent.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">− D&amp;A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOPAT = EBIT × (1 − tax)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+ D&amp;A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">− Capex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net working capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">− Δ working capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free cash flow to firm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PV of FCFF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Σ PV of explicit FCFF (FY26–30E)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminal ROIC (NOPAT ÷ [NWC + 5% of revenue])</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminal reinvestment rate = g ÷ ROIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminal FCFF = NOPAT × (1+g) × (1 − RR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminal value (at terminal WACC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PV of terminal value (year-5 factor)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enterprise value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminal value as % of EV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">less: net debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">less: non-controlling interests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fair value per share (EGP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The glide: each year at its own forward WACC (22.6% -&gt; 14.1%), shape from the forward Kd path; the terminal is capitalised at the terminal WACC and discounted at the identical year-5 cumulative factor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Income statement (EGP mn, consolidated)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY23–FY25 as sourced/derived (blue; (d)-flagged in the study); FY26E–FY30E formulas. Interest on OPENING net debt at that year’s forward Kd; tax on positive EBT net of loss carryforward.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net finance cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earnings before tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative EBT since FY26E (memo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Income tax (22.5% of positive cumulative EBT, incremental)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net profit (attributable)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPS (EGP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Historical net finance cost is (d)-derived (FY24 via the disclosed 2.0x coverage; FY23/FY25 back-solved to the reported NP). Loss carryforward per Egyptian tax law (5yr) modelled via cumulative-EBT tax.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balance sheet — condensed invested-capital layout (EGP mn)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IC = NWC + PP&amp;E + other assets; financed by net debt + equity + flat non-debt liabilities. Check row is zero by construction.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY25e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PP&amp;E (roll: + capex - D&amp;A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other assets (held flat)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invested capital (net of payables)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net debt (schedule: opening − equity FCF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity (roll: + net profit, no dividends)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-debt liabilities &amp; other (flat plug at FY25e)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total financing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balance check (IC − financing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY24 column: SWS-sourced anchors (debt 9,000/cash 828/equity 3,600); FY25e column: derived (study §1.6). The forecast check row is zero by construction: PP&amp;E rolls with capex − D&amp;A, NWC with its driver, net debt with the cash-flow sheet, equity with net profit, and the non-debt-liabilities plug is held flat.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash flow (EGP mn, forecast)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity free cash flow feeds the net-debt schedule (surplus repays debt; deficit is drawn). FCFF memo ties to the DCF.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net profit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operating − investing cash flow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dividends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity free cash flow (repays / draws net debt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">memo: FCFF (ties to DCF row)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">memo: net debt, closing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No dividends modelled — the company has never paid one and the balance sheet argues against a first.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary financials (EGP mn)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every forecast cell links to the statement sheets; history as sourced/derived.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net debt (closing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity (attributable)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FCFF (forecast)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monte Carlo — engine outputs (carry-anchored YZ-HAR-t)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50,000 paths · Student-t(6) · width calibrated on the 30-name Egyptian panel · drift = local carry (19.50%) · values computed by the engine, not a sheet simulation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The probability read (3 months)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P(price above spot)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P(+10%) vs P(−10%) — odds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37% vs 18% · 2.1:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median level (EGP) and % move</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29 (+4.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50% band (25th–75th)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06 – 2.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Touch(+10%) / touch(−10%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60% / 39%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percentile map (EGP/share)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level-touch ladder (probability of touching by horizon)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level (EGP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Probability zones (3 months)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deep downside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt; 1.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lower band</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80–2.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Around spot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05–2.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upper band</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35–2.70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strong upside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt; 2.70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensitivity — engine grids (values) + the live base cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grids are engine outputs under the full glide re-computation; the base cell reprices live off Assumptions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live base DCF (links to the DCF sheet)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminal WACC × terminal g (EGP/share)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminal WACC \ g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explicit-window WACC × terminal WACC (EGP/share)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explicit \ terminal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EBITDA-margin shift × terminal NWC intensity (EGP/share)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margin shift \ NWC %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beta grid (Ke / WACCs / DCF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WACC explicit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WACC terminal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCF (EGP/sh)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per-share &amp; ratios — the standing dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Links to statements / Assumptions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P/E at spot (×)</t>
   </si>
   <si>
     <t xml:space="preserve">Net margin</t>
@@ -959,15 +1031,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.00;\(0.00\);\-"/>
     <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="168" formatCode="0.00\x"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="@"/>
-    <numFmt numFmtId="171" formatCode="\+0.0%;\-0.0%;&quot;base&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="#,##0"/>
+    <numFmt numFmtId="171" formatCode="0"/>
+    <numFmt numFmtId="172" formatCode="0.000"/>
+    <numFmt numFmtId="173" formatCode="@"/>
+    <numFmt numFmtId="174" formatCode="\+0.0%;\-0.0%;&quot;base&quot;"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -1133,7 +1208,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="47">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1222,7 +1297,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1242,11 +1333,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1266,7 +1381,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1274,7 +1389,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1534,7 +1649,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="118"/>
@@ -1583,12 +1698,12 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
+      <c r="A9" s="3" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="A10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
@@ -1596,12 +1711,12 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
+      <c r="A12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="A13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
@@ -1624,12 +1739,12 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
+      <c r="A18" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="A19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
@@ -1642,12 +1757,12 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
+      <c r="A22" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
@@ -1657,6 +1772,11 @@
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1684,7 +1804,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1698,68 +1818,68 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>10500</v>
       </c>
       <c r="C6" s="17" t="n">
-        <f aca="false">Assumptions!B52</f>
+        <f aca="false">Assumptions!B54</f>
         <v>12640</v>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="28" t="n">
         <f aca="false">DCF!B13</f>
-        <v>9742.29312</v>
-      </c>
-      <c r="E6" s="24" t="n">
+        <v>10259.56399104</v>
+      </c>
+      <c r="E6" s="28" t="n">
         <f aca="false">DCF!C13</f>
-        <v>10511.2383984</v>
-      </c>
-      <c r="F6" s="24" t="n">
+        <v>11463.1289136</v>
+      </c>
+      <c r="F6" s="28" t="n">
         <f aca="false">DCF!D13</f>
-        <v>11106.2141568</v>
-      </c>
-      <c r="G6" s="24" t="n">
+        <v>12528.68778</v>
+      </c>
+      <c r="G6" s="28" t="n">
         <f aca="false">DCF!E13</f>
-        <v>11483.8254381312</v>
-      </c>
-      <c r="H6" s="24" t="n">
+        <v>13372.089192</v>
+      </c>
+      <c r="H6" s="28" t="n">
         <f aca="false">DCF!F13</f>
-        <v>11610.880528085</v>
+        <v>13902.666624</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>650</v>
@@ -1767,30 +1887,30 @@
       <c r="C7" s="17" t="n">
         <v>680</v>
       </c>
-      <c r="D7" s="24" t="n">
-        <f aca="false">C7-DCF!B12-Segments!E11</f>
-        <v>706.095428</v>
-      </c>
-      <c r="E7" s="24" t="n">
-        <f aca="false">D7-DCF!C12-Segments!F11</f>
-        <v>735.84421592</v>
-      </c>
-      <c r="F7" s="24" t="n">
-        <f aca="false">E7-DCF!D12-Segments!G11</f>
-        <v>769.1628583904</v>
-      </c>
-      <c r="G7" s="24" t="n">
-        <f aca="false">F7-DCF!E12-Segments!H11</f>
-        <v>805.81336510784</v>
-      </c>
-      <c r="H7" s="24" t="n">
-        <f aca="false">G7-DCF!F12-Segments!I11</f>
-        <v>845.395912362675</v>
+      <c r="D7" s="28" t="n">
+        <f aca="false">C7-DCF!B12-Segments!E17</f>
+        <v>785.915775104</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <f aca="false">D7-DCF!C12-Segments!F17</f>
+        <v>888.330231824</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <f aca="false">E7-DCF!D12-Segments!G17</f>
+        <v>987.457290684</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <f aca="false">F7-DCF!E12-Segments!H17</f>
+        <v>1085.524142284</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <f aca="false">G7-DCF!F12-Segments!I17</f>
+        <v>1186.143839884</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="B8" s="17" t="n">
         <v>3000</v>
@@ -1821,40 +1941,40 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="B9" s="30" t="n">
+        <v>217</v>
+      </c>
+      <c r="B9" s="40" t="n">
         <f aca="false">SUM(B6:B8)</f>
         <v>14150</v>
       </c>
-      <c r="C9" s="30" t="n">
+      <c r="C9" s="40" t="n">
         <f aca="false">SUM(C6:C8)</f>
         <v>16300</v>
       </c>
       <c r="D9" s="19" t="n">
         <f aca="false">SUM(D6:D8)</f>
-        <v>13428.388548</v>
+        <v>14025.479766144</v>
       </c>
       <c r="E9" s="19" t="n">
         <f aca="false">SUM(E6:E8)</f>
-        <v>14227.08261432</v>
+        <v>15331.459145424</v>
       </c>
       <c r="F9" s="19" t="n">
         <f aca="false">SUM(F6:F8)</f>
-        <v>14855.3770151904</v>
+        <v>16496.145070684</v>
       </c>
       <c r="G9" s="19" t="n">
         <f aca="false">SUM(G6:G8)</f>
-        <v>15269.638803239</v>
+        <v>17437.613334284</v>
       </c>
       <c r="H9" s="19" t="n">
         <f aca="false">SUM(H6:H8)</f>
-        <v>15436.2764404477</v>
+        <v>18068.810463884</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="B11" s="17" t="n">
         <v>8172.4</v>
@@ -1863,30 +1983,30 @@
         <f aca="false">Assumptions!B28</f>
         <v>10200</v>
       </c>
-      <c r="D11" s="24" t="n">
+      <c r="D11" s="28" t="n">
         <f aca="false">Assumptions!$B$28-'Cash Flow'!C12</f>
-        <v>9033.083036</v>
-      </c>
-      <c r="E11" s="24" t="n">
+        <v>9872.56399104</v>
+      </c>
+      <c r="E11" s="28" t="n">
         <f aca="false">D11-'Cash Flow'!D12</f>
-        <v>10379.02835424</v>
-      </c>
-      <c r="F11" s="24" t="n">
+        <v>12222.641711808</v>
+      </c>
+      <c r="F11" s="28" t="n">
         <f aca="false">E11-'Cash Flow'!E12</f>
-        <v>11294.8295195952</v>
-      </c>
-      <c r="G11" s="24" t="n">
+        <v>14270.3892948925</v>
+      </c>
+      <c r="G11" s="28" t="n">
         <f aca="false">F11-'Cash Flow'!F12</f>
-        <v>11627.4953041941</v>
-      </c>
-      <c r="H11" s="24" t="n">
+        <v>15899.8161084344</v>
+      </c>
+      <c r="H11" s="28" t="n">
         <f aca="false">G11-'Cash Flow'!G12</f>
-        <v>11392.9662497003</v>
+        <v>17040.8650372418</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">Assumptions!B34-500.31</f>
@@ -1896,102 +2016,102 @@
         <f aca="false">Assumptions!B34</f>
         <v>4100</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="28" t="n">
         <f aca="false">C12+'Income Statement'!E14</f>
-        <v>2395.305512</v>
-      </c>
-      <c r="E12" s="24" t="n">
+        <v>2152.915775104</v>
+      </c>
+      <c r="E12" s="28" t="n">
         <f aca="false">D12+'Income Statement'!F14</f>
-        <v>1848.05426008</v>
-      </c>
-      <c r="F12" s="24" t="n">
+        <v>1108.817433616</v>
+      </c>
+      <c r="F12" s="28" t="n">
         <f aca="false">E12+'Income Statement'!G14</f>
-        <v>1560.5474955952</v>
-      </c>
-      <c r="G12" s="24" t="n">
+        <v>225.75577579152</v>
+      </c>
+      <c r="G12" s="28" t="n">
         <f aca="false">F12+'Income Statement'!H14</f>
-        <v>1642.14349904497</v>
-      </c>
-      <c r="H12" s="24" t="n">
+        <v>-462.202774150417</v>
+      </c>
+      <c r="H12" s="28" t="n">
         <f aca="false">G12+'Income Statement'!I14</f>
-        <v>2043.31019074738</v>
+        <v>-972.054573357752</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="B13" s="31" t="n">
+        <v>220</v>
+      </c>
+      <c r="B13" s="41" t="n">
         <f aca="false">B9-B11-B12</f>
         <v>2377.91</v>
       </c>
-      <c r="C13" s="31" t="n">
+      <c r="C13" s="41" t="n">
         <f aca="false">C9-C11-C12</f>
         <v>2000</v>
       </c>
-      <c r="D13" s="31" t="n">
+      <c r="D13" s="41" t="n">
         <f aca="false">$C13</f>
         <v>2000</v>
       </c>
-      <c r="E13" s="31" t="n">
+      <c r="E13" s="41" t="n">
         <f aca="false">$C13</f>
         <v>2000</v>
       </c>
-      <c r="F13" s="31" t="n">
+      <c r="F13" s="41" t="n">
         <f aca="false">$C13</f>
         <v>2000</v>
       </c>
-      <c r="G13" s="31" t="n">
+      <c r="G13" s="41" t="n">
         <f aca="false">$C13</f>
         <v>2000</v>
       </c>
-      <c r="H13" s="31" t="n">
+      <c r="H13" s="41" t="n">
         <f aca="false">$C13</f>
         <v>2000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="B14" s="30" t="n">
+        <v>221</v>
+      </c>
+      <c r="B14" s="40" t="n">
         <f aca="false">B11+B12+B13</f>
         <v>14150</v>
       </c>
-      <c r="C14" s="30" t="n">
+      <c r="C14" s="40" t="n">
         <f aca="false">C11+C12+C13</f>
         <v>16300</v>
       </c>
       <c r="D14" s="19" t="n">
         <f aca="false">D11+D12+D13</f>
-        <v>13428.388548</v>
+        <v>14025.479766144</v>
       </c>
       <c r="E14" s="19" t="n">
         <f aca="false">E11+E12+E13</f>
-        <v>14227.08261432</v>
+        <v>15331.459145424</v>
       </c>
       <c r="F14" s="19" t="n">
         <f aca="false">F11+F12+F13</f>
-        <v>14855.3770151904</v>
+        <v>16496.145070684</v>
       </c>
       <c r="G14" s="19" t="n">
         <f aca="false">G11+G12+G13</f>
-        <v>15269.638803239</v>
+        <v>17437.613334284</v>
       </c>
       <c r="H14" s="19" t="n">
         <f aca="false">H11+H12+H13</f>
-        <v>15436.2764404477</v>
+        <v>18068.810463884</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="B15" s="31" t="n">
+        <v>222</v>
+      </c>
+      <c r="B15" s="41" t="n">
         <f aca="false">B9-B14</f>
         <v>0</v>
       </c>
-      <c r="C15" s="31" t="n">
+      <c r="C15" s="41" t="n">
         <f aca="false">C9-C14</f>
         <v>0</v>
       </c>
@@ -2018,7 +2138,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -2046,7 +2166,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2059,155 +2179,155 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="5"/>
       <c r="C4" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="C6" s="24" t="n">
+        <v>226</v>
+      </c>
+      <c r="C6" s="28" t="n">
         <f aca="false">'Income Statement'!E14</f>
-        <v>-1704.694488</v>
-      </c>
-      <c r="D6" s="24" t="n">
+        <v>-1947.084224896</v>
+      </c>
+      <c r="D6" s="28" t="n">
         <f aca="false">'Income Statement'!F14</f>
-        <v>-547.25125192</v>
-      </c>
-      <c r="E6" s="24" t="n">
+        <v>-1044.098341488</v>
+      </c>
+      <c r="E6" s="28" t="n">
         <f aca="false">'Income Statement'!G14</f>
-        <v>-287.5067644848</v>
-      </c>
-      <c r="F6" s="24" t="n">
+        <v>-883.06165782448</v>
+      </c>
+      <c r="F6" s="28" t="n">
         <f aca="false">'Income Statement'!H14</f>
-        <v>81.5960034497662</v>
-      </c>
-      <c r="G6" s="24" t="n">
+        <v>-687.958549941937</v>
+      </c>
+      <c r="G6" s="28" t="n">
         <f aca="false">'Income Statement'!I14</f>
-        <v>401.166691702412</v>
+        <v>-509.851799207334</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="C7" s="24" t="n">
-        <f aca="false">Segments!E11</f>
-        <v>113.080188</v>
-      </c>
-      <c r="D7" s="24" t="n">
-        <f aca="false">Segments!F11</f>
-        <v>128.91141432</v>
-      </c>
-      <c r="E7" s="24" t="n">
-        <f aca="false">Segments!G11</f>
-        <v>144.3807840384</v>
-      </c>
-      <c r="F7" s="24" t="n">
-        <f aca="false">Segments!H11</f>
-        <v>158.81886244224</v>
-      </c>
-      <c r="G7" s="24" t="n">
-        <f aca="false">Segments!I11</f>
-        <v>171.524371437619</v>
+        <v>182</v>
+      </c>
+      <c r="C7" s="28" t="n">
+        <f aca="false">Segments!E17</f>
+        <v>119.084224896</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <f aca="false">Segments!F17</f>
+        <v>140.58554328</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <f aca="false">Segments!G17</f>
+        <v>162.87294114</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <f aca="false">Segments!H17</f>
+        <v>184.9331484</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <f aca="false">Segments!I17</f>
+        <v>205.3803024</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C8" s="24" t="n">
+        <v>185</v>
+      </c>
+      <c r="C8" s="28" t="n">
         <f aca="false">DCF!B14</f>
-        <v>2897.70688</v>
-      </c>
-      <c r="D8" s="24" t="n">
+        <v>2380.43600896</v>
+      </c>
+      <c r="D8" s="28" t="n">
         <f aca="false">DCF!C14</f>
-        <v>-768.945278399999</v>
-      </c>
-      <c r="E8" s="24" t="n">
+        <v>-1203.56492256</v>
+      </c>
+      <c r="E8" s="28" t="n">
         <f aca="false">DCF!D14</f>
-        <v>-594.975758400002</v>
-      </c>
-      <c r="F8" s="24" t="n">
+        <v>-1065.5588664</v>
+      </c>
+      <c r="F8" s="28" t="n">
         <f aca="false">DCF!E14</f>
-        <v>-377.611281331201</v>
-      </c>
-      <c r="G8" s="24" t="n">
+        <v>-843.401411999999</v>
+      </c>
+      <c r="G8" s="28" t="n">
         <f aca="false">DCF!F14</f>
-        <v>-127.055089953794</v>
+        <v>-530.577432</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="C9" s="24" t="n">
+        <v>183</v>
+      </c>
+      <c r="C9" s="28" t="n">
         <f aca="false">DCF!B12</f>
-        <v>-139.175616</v>
-      </c>
-      <c r="D9" s="24" t="n">
+        <v>-225</v>
+      </c>
+      <c r="D9" s="28" t="n">
         <f aca="false">DCF!C12</f>
-        <v>-158.66020224</v>
-      </c>
-      <c r="E9" s="24" t="n">
+        <v>-243</v>
+      </c>
+      <c r="E9" s="28" t="n">
         <f aca="false">DCF!D12</f>
-        <v>-177.6994265088</v>
-      </c>
-      <c r="F9" s="24" t="n">
+        <v>-262</v>
+      </c>
+      <c r="F9" s="28" t="n">
         <f aca="false">DCF!E12</f>
-        <v>-195.46936915968</v>
-      </c>
-      <c r="G9" s="24" t="n">
+        <v>-283</v>
+      </c>
+      <c r="G9" s="28" t="n">
         <f aca="false">DCF!F12</f>
-        <v>-211.106918692454</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C10" s="19" t="n">
         <f aca="false">SUM(C6:C9)</f>
-        <v>1166.916964</v>
+        <v>327.43600896</v>
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">SUM(D6:D9)</f>
-        <v>-1345.94531824</v>
+        <v>-2350.077720768</v>
       </c>
       <c r="E10" s="19" t="n">
         <f aca="false">SUM(E6:E9)</f>
-        <v>-915.801165355201</v>
+        <v>-2047.74758308448</v>
       </c>
       <c r="F10" s="19" t="n">
         <f aca="false">SUM(F6:F9)</f>
-        <v>-332.665784598875</v>
+        <v>-1629.42681354194</v>
       </c>
       <c r="G10" s="19" t="n">
         <f aca="false">SUM(G6:G9)</f>
-        <v>234.529054493782</v>
+        <v>-1141.04892880733</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>0</v>
@@ -2227,82 +2347,82 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="C12" s="19" t="n">
         <f aca="false">C10+C11</f>
-        <v>1166.916964</v>
+        <v>327.43600896</v>
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">D10+D11</f>
-        <v>-1345.94531824</v>
+        <v>-2350.077720768</v>
       </c>
       <c r="E12" s="19" t="n">
         <f aca="false">E10+E11</f>
-        <v>-915.801165355201</v>
+        <v>-2047.74758308448</v>
       </c>
       <c r="F12" s="19" t="n">
         <f aca="false">F10+F11</f>
-        <v>-332.665784598875</v>
+        <v>-1629.42681354194</v>
       </c>
       <c r="G12" s="19" t="n">
         <f aca="false">G10+G11</f>
-        <v>234.529054493782</v>
+        <v>-1141.04892880733</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="C14" s="24" t="n">
+        <v>230</v>
+      </c>
+      <c r="C14" s="28" t="n">
         <f aca="false">DCF!B15</f>
-        <v>3289.5732238</v>
-      </c>
-      <c r="D14" s="24" t="n">
+        <v>2504.6299595616</v>
+      </c>
+      <c r="D14" s="28" t="n">
         <f aca="false">DCF!C15</f>
-        <v>177.314084022002</v>
-      </c>
-      <c r="E14" s="24" t="n">
+        <v>-584.908175322001</v>
+      </c>
+      <c r="E14" s="28" t="n">
         <f aca="false">DCF!D15</f>
-        <v>636.981046943039</v>
-      </c>
-      <c r="F14" s="24" t="n">
+        <v>-96.6374546434988</v>
+      </c>
+      <c r="F14" s="28" t="n">
         <f aca="false">DCF!E15</f>
-        <v>1119.56191807622</v>
-      </c>
-      <c r="G14" s="24" t="n">
+        <v>383.368546390001</v>
+      </c>
+      <c r="G14" s="28" t="n">
         <f aca="false">DCF!F15</f>
-        <v>1541.01942227705</v>
+        <v>883.63313604</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="C15" s="24" t="n">
+        <v>231</v>
+      </c>
+      <c r="C15" s="28" t="n">
         <f aca="false">'Balance Sheet'!D11</f>
-        <v>9033.083036</v>
-      </c>
-      <c r="D15" s="24" t="n">
+        <v>9872.56399104</v>
+      </c>
+      <c r="D15" s="28" t="n">
         <f aca="false">'Balance Sheet'!E11</f>
-        <v>10379.02835424</v>
-      </c>
-      <c r="E15" s="24" t="n">
+        <v>12222.641711808</v>
+      </c>
+      <c r="E15" s="28" t="n">
         <f aca="false">'Balance Sheet'!F11</f>
-        <v>11294.8295195952</v>
-      </c>
-      <c r="F15" s="24" t="n">
+        <v>14270.3892948925</v>
+      </c>
+      <c r="F15" s="28" t="n">
         <f aca="false">'Balance Sheet'!G11</f>
-        <v>11627.4953041941</v>
-      </c>
-      <c r="G15" s="24" t="n">
+        <v>15899.8161084344</v>
+      </c>
+      <c r="G15" s="28" t="n">
         <f aca="false">'Balance Sheet'!H11</f>
-        <v>11392.9662497003</v>
+        <v>17040.8650372418</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2330,7 +2450,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2344,39 +2464,39 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>8673.4</v>
@@ -2387,30 +2507,30 @@
       <c r="D6" s="17" t="n">
         <v>10819</v>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="E6" s="28" t="n">
         <f aca="false">'Income Statement'!E6</f>
-        <v>8698.476</v>
-      </c>
-      <c r="F6" s="24" t="n">
+        <v>9160.324992</v>
+      </c>
+      <c r="F6" s="28" t="n">
         <f aca="false">'Income Statement'!F6</f>
-        <v>9916.26264</v>
-      </c>
-      <c r="G6" s="24" t="n">
+        <v>10814.27256</v>
+      </c>
+      <c r="G6" s="28" t="n">
         <f aca="false">'Income Statement'!G6</f>
-        <v>11106.2141568</v>
-      </c>
-      <c r="H6" s="24" t="n">
+        <v>12528.68778</v>
+      </c>
+      <c r="H6" s="28" t="n">
         <f aca="false">'Income Statement'!H6</f>
-        <v>12216.83557248</v>
-      </c>
-      <c r="I6" s="24" t="n">
+        <v>14225.6268</v>
+      </c>
+      <c r="I6" s="28" t="n">
         <f aca="false">'Income Statement'!I6</f>
-        <v>13194.1824182784</v>
+        <v>15798.4848</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>2661.03638064516</v>
@@ -2421,30 +2541,30 @@
       <c r="D7" s="17" t="n">
         <v>2871.29429032258</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="28" t="n">
         <f aca="false">'Income Statement'!E7</f>
-        <v>652.3857</v>
-      </c>
-      <c r="F7" s="24" t="n">
+        <v>416</v>
+      </c>
+      <c r="F7" s="28" t="n">
         <f aca="false">'Income Statement'!F7</f>
-        <v>1388.2767696</v>
-      </c>
-      <c r="G7" s="24" t="n">
+        <v>1071</v>
+      </c>
+      <c r="G7" s="28" t="n">
         <f aca="false">'Income Statement'!G7</f>
-        <v>1776.994265088</v>
-      </c>
-      <c r="H7" s="24" t="n">
+        <v>1541</v>
+      </c>
+      <c r="H7" s="28" t="n">
         <f aca="false">'Income Statement'!H7</f>
-        <v>2137.946225184</v>
-      </c>
-      <c r="I7" s="24" t="n">
+        <v>1894.4</v>
+      </c>
+      <c r="I7" s="28" t="n">
         <f aca="false">'Income Statement'!I7</f>
-        <v>2374.95283529011</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B8" s="17" t="n">
         <v>2600.32258064516</v>
@@ -2455,30 +2575,30 @@
       <c r="D8" s="17" t="n">
         <v>2795.56129032258</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="28" t="n">
         <f aca="false">'Income Statement'!E9</f>
-        <v>539.305512</v>
-      </c>
-      <c r="F8" s="24" t="n">
+        <v>296.915775104</v>
+      </c>
+      <c r="F8" s="28" t="n">
         <f aca="false">'Income Statement'!F9</f>
-        <v>1259.36535528</v>
-      </c>
-      <c r="G8" s="24" t="n">
+        <v>930.41445672</v>
+      </c>
+      <c r="G8" s="28" t="n">
         <f aca="false">'Income Statement'!G9</f>
-        <v>1632.6134810496</v>
-      </c>
-      <c r="H8" s="24" t="n">
+        <v>1378.12705886</v>
+      </c>
+      <c r="H8" s="28" t="n">
         <f aca="false">'Income Statement'!H9</f>
-        <v>1979.12736274176</v>
-      </c>
-      <c r="I8" s="24" t="n">
+        <v>1709.4668516</v>
+      </c>
+      <c r="I8" s="28" t="n">
         <f aca="false">'Income Statement'!I9</f>
-        <v>2203.42846385249</v>
+        <v>1954.6196976</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="B9" s="17" t="n">
         <v>1248</v>
@@ -2489,108 +2609,108 @@
       <c r="D9" s="17" t="n">
         <v>500.31</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="28" t="n">
         <f aca="false">'Income Statement'!E14</f>
-        <v>-1704.694488</v>
-      </c>
-      <c r="F9" s="24" t="n">
+        <v>-1947.084224896</v>
+      </c>
+      <c r="F9" s="28" t="n">
         <f aca="false">'Income Statement'!F14</f>
-        <v>-547.25125192</v>
-      </c>
-      <c r="G9" s="24" t="n">
+        <v>-1044.098341488</v>
+      </c>
+      <c r="G9" s="28" t="n">
         <f aca="false">'Income Statement'!G14</f>
-        <v>-287.5067644848</v>
-      </c>
-      <c r="H9" s="24" t="n">
+        <v>-883.06165782448</v>
+      </c>
+      <c r="H9" s="28" t="n">
         <f aca="false">'Income Statement'!H14</f>
-        <v>81.5960034497662</v>
-      </c>
-      <c r="I9" s="24" t="n">
+        <v>-687.958549941937</v>
+      </c>
+      <c r="I9" s="28" t="n">
         <f aca="false">'Income Statement'!I14</f>
-        <v>401.166691702412</v>
+        <v>-509.851799207334</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D10" s="24" t="n">
+        <v>235</v>
+      </c>
+      <c r="D10" s="28" t="n">
         <f aca="false">Assumptions!B28</f>
         <v>10200</v>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="28" t="n">
         <f aca="false">'Balance Sheet'!D11</f>
-        <v>9033.083036</v>
-      </c>
-      <c r="F10" s="24" t="n">
+        <v>9872.56399104</v>
+      </c>
+      <c r="F10" s="28" t="n">
         <f aca="false">'Balance Sheet'!E11</f>
-        <v>10379.02835424</v>
-      </c>
-      <c r="G10" s="24" t="n">
+        <v>12222.641711808</v>
+      </c>
+      <c r="G10" s="28" t="n">
         <f aca="false">'Balance Sheet'!F11</f>
-        <v>11294.8295195952</v>
-      </c>
-      <c r="H10" s="24" t="n">
+        <v>14270.3892948925</v>
+      </c>
+      <c r="H10" s="28" t="n">
         <f aca="false">'Balance Sheet'!G11</f>
-        <v>11627.4953041941</v>
-      </c>
-      <c r="I10" s="24" t="n">
+        <v>15899.8161084344</v>
+      </c>
+      <c r="I10" s="28" t="n">
         <f aca="false">'Balance Sheet'!H11</f>
-        <v>11392.9662497003</v>
+        <v>17040.8650372418</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D11" s="24" t="n">
+        <v>236</v>
+      </c>
+      <c r="D11" s="28" t="n">
         <f aca="false">Assumptions!B34</f>
         <v>4100</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="28" t="n">
         <f aca="false">'Balance Sheet'!D12</f>
-        <v>2395.305512</v>
-      </c>
-      <c r="F11" s="24" t="n">
+        <v>2152.915775104</v>
+      </c>
+      <c r="F11" s="28" t="n">
         <f aca="false">'Balance Sheet'!E12</f>
-        <v>1848.05426008</v>
-      </c>
-      <c r="G11" s="24" t="n">
+        <v>1108.817433616</v>
+      </c>
+      <c r="G11" s="28" t="n">
         <f aca="false">'Balance Sheet'!F12</f>
-        <v>1560.5474955952</v>
-      </c>
-      <c r="H11" s="24" t="n">
+        <v>225.75577579152</v>
+      </c>
+      <c r="H11" s="28" t="n">
         <f aca="false">'Balance Sheet'!G12</f>
-        <v>1642.14349904497</v>
-      </c>
-      <c r="I11" s="24" t="n">
+        <v>-462.202774150417</v>
+      </c>
+      <c r="I11" s="28" t="n">
         <f aca="false">'Balance Sheet'!H12</f>
-        <v>2043.31019074738</v>
+        <v>-972.054573357752</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="E12" s="24" t="n">
+        <v>237</v>
+      </c>
+      <c r="E12" s="28" t="n">
         <f aca="false">DCF!B15</f>
-        <v>3289.5732238</v>
-      </c>
-      <c r="F12" s="24" t="n">
+        <v>2504.6299595616</v>
+      </c>
+      <c r="F12" s="28" t="n">
         <f aca="false">DCF!C15</f>
-        <v>177.314084022002</v>
-      </c>
-      <c r="G12" s="24" t="n">
+        <v>-584.908175322001</v>
+      </c>
+      <c r="G12" s="28" t="n">
         <f aca="false">DCF!D15</f>
-        <v>636.981046943039</v>
-      </c>
-      <c r="H12" s="24" t="n">
+        <v>-96.6374546434988</v>
+      </c>
+      <c r="H12" s="28" t="n">
         <f aca="false">DCF!E15</f>
-        <v>1119.56191807622</v>
-      </c>
-      <c r="I12" s="24" t="n">
+        <v>383.368546390001</v>
+      </c>
+      <c r="I12" s="28" t="n">
         <f aca="false">DCF!F15</f>
-        <v>1541.01942227705</v>
+        <v>883.63313604</v>
       </c>
     </row>
   </sheetData>
@@ -2618,7 +2738,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2630,17 +2750,17 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="32" t="s">
-        <v>217</v>
+      <c r="A5" s="42" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>0.6135</v>
@@ -2648,119 +2768,119 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>220</v>
+        <v>242</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>222</v>
+        <v>244</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>224</v>
+        <v>246</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>226</v>
+        <v>248</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="B14" s="29" t="n">
+        <v>257</v>
+      </c>
+      <c r="B14" s="39" t="n">
         <v>1.91</v>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="39" t="n">
         <v>2.1</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="39" t="n">
         <v>2.22</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="39" t="n">
         <v>2.35</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="39" t="n">
         <v>2.59</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="B15" s="29" t="n">
+        <v>258</v>
+      </c>
+      <c r="B15" s="39" t="n">
         <v>1.71</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="39" t="n">
         <v>2.06</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="39" t="n">
         <v>2.29</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="39" t="n">
         <v>2.55</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="39" t="n">
         <v>3.07</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="29" t="n">
+      <c r="A19" s="39" t="n">
         <v>3</v>
       </c>
       <c r="B19" s="12" t="n">
@@ -2771,7 +2891,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="29" t="n">
+      <c r="A20" s="39" t="n">
         <v>2.75</v>
       </c>
       <c r="B20" s="12" t="n">
@@ -2782,7 +2902,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="29" t="n">
+      <c r="A21" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="B21" s="12" t="n">
@@ -2793,7 +2913,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="29" t="n">
+      <c r="A22" s="39" t="n">
         <v>2.35</v>
       </c>
       <c r="B22" s="12" t="n">
@@ -2804,7 +2924,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="29" t="n">
+      <c r="A23" s="39" t="n">
         <v>2.19</v>
       </c>
       <c r="B23" s="12" t="n">
@@ -2815,7 +2935,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="29" t="n">
+      <c r="A24" s="39" t="n">
         <v>2.05</v>
       </c>
       <c r="B24" s="12" t="n">
@@ -2826,7 +2946,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="29" t="n">
+      <c r="A25" s="39" t="n">
         <v>1.9</v>
       </c>
       <c r="B25" s="12" t="n">
@@ -2837,7 +2957,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="29" t="n">
+      <c r="A26" s="39" t="n">
         <v>1.7</v>
       </c>
       <c r="B26" s="12" t="n">
@@ -2849,15 +2969,15 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="B29" s="33" t="s">
-        <v>240</v>
+        <v>262</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>263</v>
       </c>
       <c r="C29" s="12" t="n">
         <v>0.0814</v>
@@ -2865,10 +2985,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="B30" s="33" t="s">
-        <v>242</v>
+        <v>264</v>
+      </c>
+      <c r="B30" s="43" t="s">
+        <v>265</v>
       </c>
       <c r="C30" s="12" t="n">
         <v>0.1618</v>
@@ -2876,10 +2996,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="B31" s="33" t="s">
-        <v>244</v>
+        <v>266</v>
+      </c>
+      <c r="B31" s="43" t="s">
+        <v>267</v>
       </c>
       <c r="C31" s="12" t="n">
         <v>0.32145</v>
@@ -2887,10 +3007,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="B32" s="33" t="s">
-        <v>246</v>
+        <v>268</v>
+      </c>
+      <c r="B32" s="43" t="s">
+        <v>269</v>
       </c>
       <c r="C32" s="12" t="n">
         <v>0.27745</v>
@@ -2898,10 +3018,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="B33" s="33" t="s">
-        <v>248</v>
+        <v>270</v>
+      </c>
+      <c r="B33" s="43" t="s">
+        <v>271</v>
       </c>
       <c r="C33" s="12" t="n">
         <v>0.1579</v>
@@ -2932,7 +3052,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2944,417 +3064,417 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="B5" s="8" t="n">
-        <f aca="false">DCF!B31</f>
-        <v>0.0233762361074855</v>
+        <f aca="false">DCF!B33</f>
+        <v>0.01</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="B8" s="34" t="n">
+        <v>276</v>
+      </c>
+      <c r="B8" s="44" t="n">
         <v>0.03</v>
       </c>
-      <c r="C8" s="34" t="n">
+      <c r="C8" s="44" t="n">
         <v>0.04</v>
       </c>
-      <c r="D8" s="34" t="n">
+      <c r="D8" s="44" t="n">
         <v>0.05</v>
       </c>
-      <c r="E8" s="34" t="n">
+      <c r="E8" s="44" t="n">
         <v>0.06</v>
       </c>
-      <c r="F8" s="34" t="n">
+      <c r="F8" s="44" t="n">
         <v>0.07</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="n">
-        <v>0.118723393761621</v>
-      </c>
-      <c r="B9" s="29" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="C9" s="29" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="D9" s="29" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="F9" s="29" t="n">
-        <v>0.93</v>
+        <v>0.129988</v>
+      </c>
+      <c r="B9" s="39" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="C9" s="39" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="D9" s="39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E9" s="39" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="F9" s="39" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="n">
-        <v>0.128723393761621</v>
-      </c>
-      <c r="B10" s="29" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="C10" s="29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D10" s="29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F10" s="29" t="n">
-        <v>0.42</v>
+        <v>0.139988</v>
+      </c>
+      <c r="B10" s="39" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="C10" s="39" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="D10" s="39" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="E10" s="39" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F10" s="39" t="n">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="n">
-        <v>0.138723393761621</v>
-      </c>
-      <c r="B11" s="29" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="C11" s="29" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D11" s="29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F11" s="29" t="n">
-        <v>0.06</v>
+        <v>0.149988</v>
+      </c>
+      <c r="B11" s="39" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="C11" s="39" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="D11" s="39" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="E11" s="39" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="F11" s="39" t="n">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="n">
-        <v>0.148723393761621</v>
-      </c>
-      <c r="B12" s="29" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C12" s="29" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="D12" s="29" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="E12" s="29" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="F12" s="29" t="n">
-        <v>-0.21</v>
+        <v>0.159988</v>
+      </c>
+      <c r="B12" s="39" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="C12" s="39" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="D12" s="39" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="E12" s="39" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="F12" s="39" t="n">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="n">
-        <v>0.158723393761621</v>
-      </c>
-      <c r="B13" s="29" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="C13" s="29" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="D13" s="29" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="E13" s="29" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="F13" s="29" t="n">
-        <v>-0.42</v>
+        <v>0.169988</v>
+      </c>
+      <c r="B13" s="39" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="C13" s="39" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="D13" s="39" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="E13" s="39" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="F13" s="39" t="n">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B16" s="34" t="n">
-        <v>0.118723393761621</v>
-      </c>
-      <c r="C16" s="34" t="n">
-        <v>0.128723393761621</v>
-      </c>
-      <c r="D16" s="34" t="n">
-        <v>0.138723393761621</v>
-      </c>
-      <c r="E16" s="34" t="n">
-        <v>0.148723393761621</v>
-      </c>
-      <c r="F16" s="34" t="n">
-        <v>0.158723393761621</v>
+        <v>278</v>
+      </c>
+      <c r="B16" s="44" t="n">
+        <v>0.129988</v>
+      </c>
+      <c r="C16" s="44" t="n">
+        <v>0.139988</v>
+      </c>
+      <c r="D16" s="44" t="n">
+        <v>0.149988</v>
+      </c>
+      <c r="E16" s="44" t="n">
+        <v>0.159988</v>
+      </c>
+      <c r="F16" s="44" t="n">
+        <v>0.169988</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="n">
         <v>0.194188789049045</v>
       </c>
-      <c r="B17" s="29" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="F17" s="29" t="n">
-        <v>-0.29</v>
+      <c r="B17" s="39" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="C17" s="39" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="D17" s="39" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="E17" s="39" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="F17" s="39" t="n">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="n">
         <v>0.204188789049045</v>
       </c>
-      <c r="B18" s="29" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>-0.33</v>
+      <c r="B18" s="39" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="C18" s="39" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="D18" s="39" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="E18" s="39" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="F18" s="39" t="n">
+        <v>-1.54</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="n">
         <v>0.214188789049045</v>
       </c>
-      <c r="B19" s="29" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="C19" s="29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D19" s="29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E19" s="29" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="F19" s="29" t="n">
-        <v>-0.38</v>
+      <c r="B19" s="39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C19" s="39" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="D19" s="39" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="E19" s="39" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="F19" s="39" t="n">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="n">
         <v>0.224188789049045</v>
       </c>
-      <c r="B20" s="29" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="C20" s="29" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>-0.42</v>
+      <c r="B20" s="39" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="C20" s="39" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="D20" s="39" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="E20" s="39" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="F20" s="39" t="n">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="n">
         <v>0.234188789049045</v>
       </c>
-      <c r="B21" s="29" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="C21" s="29" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="D21" s="29" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="E21" s="29" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="F21" s="29" t="n">
-        <v>-0.46</v>
+      <c r="B21" s="39" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="C21" s="39" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="D21" s="39" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="E21" s="39" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="F21" s="39" t="n">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B24" s="34" t="n">
+        <v>280</v>
+      </c>
+      <c r="B24" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="34" t="n">
+      <c r="C24" s="44" t="n">
         <v>0.94</v>
       </c>
-      <c r="D24" s="34" t="n">
+      <c r="D24" s="44" t="n">
         <v>0.88</v>
       </c>
-      <c r="E24" s="34" t="n">
+      <c r="E24" s="44" t="n">
         <v>0.82</v>
       </c>
-      <c r="F24" s="34" t="n">
+      <c r="F24" s="44" t="n">
         <v>0.76</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="35" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="B25" s="29" t="n">
-        <v>-1.08</v>
-      </c>
-      <c r="C25" s="29" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="D25" s="29" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="E25" s="29" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="F25" s="29" t="n">
-        <v>-0.31</v>
+      <c r="A25" s="45" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="B25" s="39" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="C25" s="39" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="D25" s="39" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="E25" s="39" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="F25" s="39" t="n">
+        <v>-1.87</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="35" t="n">
-        <v>-0.015</v>
-      </c>
-      <c r="B26" s="29" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="C26" s="29" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="D26" s="29" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="E26" s="29" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="F26" s="29" t="n">
-        <v>0.05</v>
+      <c r="A26" s="45" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="B26" s="39" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="C26" s="39" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="D26" s="39" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="E26" s="39" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="F26" s="39" t="n">
+        <v>-1.39</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="35" t="n">
+      <c r="A27" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="B27" s="29" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="C27" s="29" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="D27" s="29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E27" s="29" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="F27" s="29" t="n">
-        <v>0.41</v>
+      <c r="B27" s="39" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="C27" s="39" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="D27" s="39" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="E27" s="39" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="F27" s="39" t="n">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="35" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="B28" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="29" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="D28" s="29" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E28" s="29" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F28" s="29" t="n">
-        <v>0.77</v>
+      <c r="A28" s="45" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="B28" s="39" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="C28" s="39" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="D28" s="39" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="E28" s="39" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="F28" s="39" t="n">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="35" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="B29" s="29" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="C29" s="29" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D29" s="29" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E29" s="29" t="n">
-        <v>0.94</v>
-      </c>
-      <c r="F29" s="29" t="n">
-        <v>1.13</v>
+      <c r="A29" s="45" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B29" s="39" t="n">
+        <v>-0.81</v>
+      </c>
+      <c r="C29" s="39" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="D29" s="39" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="E29" s="39" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F29" s="39" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="29" t="n">
+      <c r="A33" s="39" t="n">
         <v>0.6</v>
       </c>
       <c r="B33" s="12" t="n">
@@ -3364,14 +3484,14 @@
         <v>0.200499163004575</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.128539824971898</v>
-      </c>
-      <c r="E33" s="29" t="n">
-        <v>0.31</v>
+        <v>0.1347</v>
+      </c>
+      <c r="E33" s="39" t="n">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="29" t="n">
+      <c r="A34" s="39" t="n">
         <v>0.78</v>
       </c>
       <c r="B34" s="12" t="n">
@@ -3381,14 +3501,14 @@
         <v>0.207268758301291</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.133575655692091</v>
-      </c>
-      <c r="E34" s="29" t="n">
-        <v>0.16</v>
+        <v>0.14226</v>
+      </c>
+      <c r="E34" s="39" t="n">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="29" t="n">
+      <c r="A35" s="39" t="n">
         <v>0.8</v>
       </c>
       <c r="B35" s="12" t="n">
@@ -3398,14 +3518,14 @@
         <v>0.208020935556482</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>0.134135192438779</v>
-      </c>
-      <c r="E35" s="29" t="n">
-        <v>0.14</v>
+        <v>0.1431</v>
+      </c>
+      <c r="E35" s="39" t="n">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="29" t="n">
+      <c r="A36" s="39" t="n">
         <v>0.964</v>
       </c>
       <c r="B36" s="12" t="n">
@@ -3415,14 +3535,14 @@
         <v>0.214188789049045</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>0.138723393761621</v>
-      </c>
-      <c r="E36" s="29" t="n">
-        <v>0.02</v>
+        <v>0.149988</v>
+      </c>
+      <c r="E36" s="39" t="n">
+        <v>-1.34</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="29" t="n">
+      <c r="A37" s="39" t="n">
         <v>1</v>
       </c>
       <c r="B37" s="12" t="n">
@@ -3432,14 +3552,14 @@
         <v>0.215542708108388</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>0.13973055990566</v>
-      </c>
-      <c r="E37" s="29" t="n">
-        <v>0</v>
+        <v>0.1515</v>
+      </c>
+      <c r="E37" s="39" t="n">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="29" t="n">
+      <c r="A38" s="39" t="n">
         <v>1.15</v>
       </c>
       <c r="B38" s="12" t="n">
@@ -3449,14 +3569,14 @@
         <v>0.221184037522318</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>0.14392708550582</v>
-      </c>
-      <c r="E38" s="29" t="n">
-        <v>-0.1</v>
+        <v>0.1578</v>
+      </c>
+      <c r="E38" s="39" t="n">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="29" t="n">
+      <c r="A39" s="39" t="n">
         <v>1.3</v>
       </c>
       <c r="B39" s="12" t="n">
@@ -3466,10 +3586,10 @@
         <v>0.226825366936248</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>0.14812361110598</v>
-      </c>
-      <c r="E39" s="29" t="n">
-        <v>-0.19</v>
+        <v>0.1641</v>
+      </c>
+      <c r="E39" s="39" t="n">
+        <v>-1.51</v>
       </c>
     </row>
   </sheetData>
@@ -3497,7 +3617,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3511,113 +3631,113 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="B6" s="29" t="n">
+        <v>210</v>
+      </c>
+      <c r="B6" s="39" t="n">
         <f aca="false">'Income Statement'!B14/Assumptions!$B$6</f>
         <v>0.376636424945712</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="39" t="n">
         <f aca="false">'Income Statement'!C14/Assumptions!$B$6</f>
         <v>0.400719427117721</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="39" t="n">
         <f aca="false">'Income Statement'!D14/Assumptions!$B$6</f>
         <v>0.150989559106241</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="39" t="n">
         <f aca="false">'Income Statement'!E14/Assumptions!$B$6</f>
-        <v>-0.514463171141811</v>
-      </c>
-      <c r="F6" s="29" t="n">
+        <v>-0.587614456356588</v>
+      </c>
+      <c r="F6" s="39" t="n">
         <f aca="false">'Income Statement'!F14/Assumptions!$B$6</f>
-        <v>-0.165156053742159</v>
-      </c>
-      <c r="G6" s="29" t="n">
+        <v>-0.315100534158483</v>
+      </c>
+      <c r="G6" s="39" t="n">
         <f aca="false">'Income Statement'!G14/Assumptions!$B$6</f>
-        <v>-0.0867672435282562</v>
-      </c>
-      <c r="H6" s="29" t="n">
+        <v>-0.266500950167985</v>
+      </c>
+      <c r="H6" s="39" t="n">
         <f aca="false">'Income Statement'!H14/Assumptions!$B$6</f>
-        <v>0.0246250216579951</v>
-      </c>
-      <c r="I6" s="29" t="n">
+        <v>-0.20762039163539</v>
+      </c>
+      <c r="I6" s="39" t="n">
         <f aca="false">'Income Statement'!I14/Assumptions!$B$6</f>
-        <v>0.121068901097832</v>
+        <v>-0.153869197841017</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="B7" s="26" t="n">
+        <v>289</v>
+      </c>
+      <c r="B7" s="30" t="n">
         <f aca="false">IF('Income Statement'!B14&gt;0,Assumptions!$B$5/('Income Statement'!B14/Assumptions!$B$6),"n.m.")</f>
         <v>5.8146261353125</v>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="30" t="n">
         <f aca="false">IF('Income Statement'!C14&gt;0,Assumptions!$B$5/('Income Statement'!C14/Assumptions!$B$6),"n.m.")</f>
         <v>5.46517052031179</v>
       </c>
-      <c r="D7" s="26" t="n">
+      <c r="D7" s="30" t="n">
         <f aca="false">IF('Income Statement'!D14&gt;0,Assumptions!$B$5/('Income Statement'!D14/Assumptions!$B$6),"n.m.")</f>
         <v>14.5043141589614</v>
       </c>
-      <c r="E7" s="26" t="str">
+      <c r="E7" s="30" t="str">
         <f aca="false">IF('Income Statement'!E14&gt;0,Assumptions!$B$5/('Income Statement'!E14/Assumptions!$B$6),"n.m.")</f>
         <v>n.m.</v>
       </c>
-      <c r="F7" s="26" t="str">
+      <c r="F7" s="30" t="str">
         <f aca="false">IF('Income Statement'!F14&gt;0,Assumptions!$B$5/('Income Statement'!F14/Assumptions!$B$6),"n.m.")</f>
         <v>n.m.</v>
       </c>
-      <c r="G7" s="26" t="str">
+      <c r="G7" s="30" t="str">
         <f aca="false">IF('Income Statement'!G14&gt;0,Assumptions!$B$5/('Income Statement'!G14/Assumptions!$B$6),"n.m.")</f>
         <v>n.m.</v>
       </c>
-      <c r="H7" s="26" t="n">
+      <c r="H7" s="30" t="str">
         <f aca="false">IF('Income Statement'!H14&gt;0,Assumptions!$B$5/('Income Statement'!H14/Assumptions!$B$6),"n.m.")</f>
-        <v>88.9339319337802</v>
-      </c>
-      <c r="I7" s="26" t="n">
+        <v>n.m.</v>
+      </c>
+      <c r="I7" s="30" t="str">
         <f aca="false">IF('Income Statement'!I14&gt;0,Assumptions!$B$5/('Income Statement'!I14/Assumptions!$B$6),"n.m.")</f>
-        <v>18.0888731965141</v>
+        <v>n.m.</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>102</v>
+        <v>290</v>
       </c>
       <c r="B8" s="12" t="n">
         <f aca="false">'Income Statement'!B7/'Income Statement'!B6</f>
@@ -3633,28 +3753,28 @@
       </c>
       <c r="E8" s="12" t="n">
         <f aca="false">'Income Statement'!E7/'Income Statement'!E6</f>
-        <v>0.075</v>
+        <v>0.0454132359237588</v>
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">'Income Statement'!F7/'Income Statement'!F6</f>
-        <v>0.14</v>
+        <v>0.0990357875721971</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">'Income Statement'!G7/'Income Statement'!G6</f>
-        <v>0.16</v>
+        <v>0.122997717483227</v>
       </c>
       <c r="H8" s="12" t="n">
         <f aca="false">'Income Statement'!H7/'Income Statement'!H6</f>
-        <v>0.175</v>
+        <v>0.133168121632433</v>
       </c>
       <c r="I8" s="12" t="n">
         <f aca="false">'Income Statement'!I7/'Income Statement'!I6</f>
-        <v>0.18</v>
+        <v>0.136721972223564</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="B9" s="12" t="n">
         <f aca="false">'Income Statement'!B14/'Income Statement'!B6</f>
@@ -3670,28 +3790,28 @@
       </c>
       <c r="E9" s="12" t="n">
         <f aca="false">'Income Statement'!E14/'Income Statement'!E6</f>
-        <v>-0.195976224800758</v>
+        <v>-0.212556238626517</v>
       </c>
       <c r="F9" s="12" t="n">
         <f aca="false">'Income Statement'!F14/'Income Statement'!F6</f>
-        <v>-0.0551872486427003</v>
+        <v>-0.0965481807209046</v>
       </c>
       <c r="G9" s="12" t="n">
         <f aca="false">'Income Statement'!G14/'Income Statement'!G6</f>
-        <v>-0.0258870178825759</v>
+        <v>-0.0704831721670121</v>
       </c>
       <c r="H9" s="12" t="n">
         <f aca="false">'Income Statement'!H14/'Income Statement'!H6</f>
-        <v>0.00667898024538954</v>
+        <v>-0.0483605087926204</v>
       </c>
       <c r="I9" s="12" t="n">
         <f aca="false">'Income Statement'!I14/'Income Statement'!I6</f>
-        <v>0.0304048162276929</v>
+        <v>-0.0322721960784071</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="C10" s="12" t="n">
         <f aca="false">'Income Statement'!C6/'Income Statement'!B6-1</f>
@@ -3703,119 +3823,119 @@
       </c>
       <c r="E10" s="12" t="n">
         <f aca="false">'Income Statement'!E6/'Income Statement'!D6-1</f>
-        <v>-0.196</v>
+        <v>-0.153311304926518</v>
       </c>
       <c r="F10" s="12" t="n">
         <f aca="false">'Income Statement'!F6/'Income Statement'!E6-1</f>
-        <v>0.14</v>
+        <v>0.180555555555556</v>
       </c>
       <c r="G10" s="12" t="n">
         <f aca="false">'Income Statement'!G6/'Income Statement'!F6-1</f>
-        <v>0.12</v>
+        <v>0.158532643826761</v>
       </c>
       <c r="H10" s="12" t="n">
         <f aca="false">'Income Statement'!H6/'Income Statement'!G6-1</f>
-        <v>0.1</v>
+        <v>0.135444273957316</v>
       </c>
       <c r="I10" s="12" t="n">
         <f aca="false">'Income Statement'!I6/'Income Statement'!H6-1</f>
-        <v>0.0800000000000001</v>
+        <v>0.110565110565111</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="D11" s="29" t="n">
+        <v>293</v>
+      </c>
+      <c r="D11" s="39" t="n">
         <f aca="false">Assumptions!$B$34/Assumptions!$B$6</f>
         <v>1.23734722938896</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="39" t="n">
         <f aca="false">'Balance Sheet'!D12/Assumptions!$B$6</f>
-        <v>0.722884058247145</v>
-      </c>
-      <c r="F11" s="29" t="n">
+        <v>0.649732773032369</v>
+      </c>
+      <c r="F11" s="39" t="n">
         <f aca="false">'Balance Sheet'!E12/Assumptions!$B$6</f>
-        <v>0.557728004504987</v>
-      </c>
-      <c r="G11" s="29" t="n">
+        <v>0.334632238873886</v>
+      </c>
+      <c r="G11" s="39" t="n">
         <f aca="false">'Balance Sheet'!F12/Assumptions!$B$6</f>
-        <v>0.470960760976731</v>
-      </c>
-      <c r="H11" s="29" t="n">
+        <v>0.0681312887059003</v>
+      </c>
+      <c r="H11" s="39" t="n">
         <f aca="false">'Balance Sheet'!G12/Assumptions!$B$6</f>
-        <v>0.495585782634726</v>
-      </c>
-      <c r="I11" s="29" t="n">
+        <v>-0.13948910292949</v>
+      </c>
+      <c r="I11" s="39" t="n">
         <f aca="false">'Balance Sheet'!H12/Assumptions!$B$6</f>
-        <v>0.616654683732558</v>
+        <v>-0.293358300770507</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="26" t="n">
+        <v>294</v>
+      </c>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="30" t="n">
         <f aca="false">Assumptions!$B$5/(Assumptions!$B$34/Assumptions!$B$6)</f>
         <v>1.76991546752927</v>
       </c>
-      <c r="E12" s="26" t="n">
+      <c r="E12" s="30" t="n">
         <f aca="false">Assumptions!$B$5/('Balance Sheet'!D12/Assumptions!$B$6)</f>
-        <v>3.02953146499084</v>
-      </c>
-      <c r="F12" s="26" t="n">
+        <v>3.37061649172943</v>
+      </c>
+      <c r="F12" s="30" t="n">
         <f aca="false">Assumptions!$B$5/('Balance Sheet'!E12/Assumptions!$B$6)</f>
-        <v>3.92664521471132</v>
-      </c>
-      <c r="G12" s="26" t="n">
+        <v>6.54449794607314</v>
+      </c>
+      <c r="G12" s="30" t="n">
         <f aca="false">Assumptions!$B$5/('Balance Sheet'!F12/Assumptions!$B$6)</f>
-        <v>4.65006892603565</v>
-      </c>
-      <c r="H12" s="26" t="n">
+        <v>32.143821753519</v>
+      </c>
+      <c r="H12" s="30" t="n">
         <f aca="false">Assumptions!$B$5/('Balance Sheet'!G12/Assumptions!$B$6)</f>
-        <v>4.41901296755753</v>
-      </c>
-      <c r="I12" s="26" t="n">
+        <v>-15.7001511516424</v>
+      </c>
+      <c r="I12" s="30" t="n">
         <f aca="false">Assumptions!$B$5/('Balance Sheet'!H12/Assumptions!$B$6)</f>
-        <v>3.55142036178841</v>
+        <v>-7.46527367471094</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="26" t="n">
+        <v>295</v>
+      </c>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="30" t="n">
         <f aca="false">Assumptions!$B$28/'Income Statement'!D7</f>
         <v>3.55240493263895</v>
       </c>
-      <c r="E13" s="26" t="n">
+      <c r="E13" s="30" t="n">
         <f aca="false">'Balance Sheet'!D11/'Income Statement'!E7</f>
-        <v>13.8462308968452</v>
-      </c>
-      <c r="F13" s="26" t="n">
+        <v>23.7321249784615</v>
+      </c>
+      <c r="F13" s="30" t="n">
         <f aca="false">'Balance Sheet'!E11/'Income Statement'!F7</f>
-        <v>7.47619536789518</v>
-      </c>
-      <c r="G13" s="26" t="n">
+        <v>11.4123638765714</v>
+      </c>
+      <c r="G13" s="30" t="n">
         <f aca="false">'Balance Sheet'!F11/'Income Statement'!G7</f>
-        <v>6.35614292150564</v>
-      </c>
-      <c r="H13" s="26" t="n">
+        <v>9.26047326079979</v>
+      </c>
+      <c r="H13" s="30" t="n">
         <f aca="false">'Balance Sheet'!G11/'Income Statement'!H7</f>
-        <v>5.43862851517389</v>
-      </c>
-      <c r="I13" s="26" t="n">
+        <v>8.39306171264486</v>
+      </c>
+      <c r="I13" s="30" t="n">
         <f aca="false">'Balance Sheet'!H11/'Income Statement'!I7</f>
-        <v>4.79713368636585</v>
+        <v>7.8892893690934</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="D14" s="12" t="n">
         <f aca="false">Assumptions!$B$28/Assumptions!$B$34</f>
@@ -3823,53 +3943,53 @@
       </c>
       <c r="E14" s="12" t="n">
         <f aca="false">'Balance Sheet'!D11/'Balance Sheet'!D12</f>
-        <v>3.77116112777517</v>
+        <v>4.58567125811649</v>
       </c>
       <c r="F14" s="12" t="n">
         <f aca="false">'Balance Sheet'!E11/'Balance Sheet'!E12</f>
-        <v>5.61619243462619</v>
+        <v>11.0231327008887</v>
       </c>
       <c r="G14" s="12" t="n">
         <f aca="false">'Balance Sheet'!F11/'Balance Sheet'!F12</f>
-        <v>7.2377351868341</v>
+        <v>63.2116243531721</v>
       </c>
       <c r="H14" s="12" t="n">
         <f aca="false">'Balance Sheet'!G11/'Balance Sheet'!G12</f>
-        <v>7.08068162797975</v>
+        <v>-34.400088008256</v>
       </c>
       <c r="I14" s="12" t="n">
         <f aca="false">'Balance Sheet'!H11/'Balance Sheet'!H12</f>
-        <v>5.57573994457157</v>
+        <v>-17.5307698809315</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="E15" s="12" t="n">
         <f aca="false">'Income Statement'!E14/'Balance Sheet'!D12</f>
-        <v>-0.711681445001409</v>
+        <v>-0.904394053595498</v>
       </c>
       <c r="F15" s="12" t="n">
         <f aca="false">'Income Statement'!F14/'Balance Sheet'!E12</f>
-        <v>-0.296122935208791</v>
+        <v>-0.941632328130933</v>
       </c>
       <c r="G15" s="12" t="n">
         <f aca="false">'Income Statement'!G14/'Balance Sheet'!F12</f>
-        <v>-0.184234549282426</v>
+        <v>-3.91157947001971</v>
       </c>
       <c r="H15" s="12" t="n">
         <f aca="false">'Income Statement'!H14/'Balance Sheet'!G12</f>
-        <v>0.0496887169100755</v>
+        <v>1.4884344889675</v>
       </c>
       <c r="I15" s="12" t="n">
         <f aca="false">'Income Statement'!I14/'Balance Sheet'!H12</f>
-        <v>0.196331762802826</v>
+        <v>0.524509439265495</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -3899,7 +4019,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3910,117 +4030,117 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>276</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>282</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>294</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>297</v>
+        <v>321</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>300</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>303</v>
+        <v>327</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>304</v>
+        <v>328</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>305</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -4048,7 +4168,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4059,36 +4179,36 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>0.01</v>
       </c>
       <c r="C6" s="8" t="n">
-        <f aca="false">DCF!B31</f>
-        <v>0.0233762361074855</v>
+        <f aca="false">DCF!B33</f>
+        <v>0.01</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2.36</v>
+        <v>1.53</v>
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">Assumptions!B35</f>
@@ -4097,7 +4217,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>0.05</v>
@@ -4116,17 +4236,17 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.55</v>
+        <v>0.26</v>
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">'Relative &amp; Normalized'!C7</f>
-        <v>1.11377559810627</v>
+        <v>0.726885683552602</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1.92</v>
+        <v>1.4</v>
       </c>
       <c r="E8" s="9" t="n">
         <f aca="false">Assumptions!B37</f>
@@ -4135,7 +4255,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>0.61</v>
@@ -4154,24 +4274,24 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">SUMPRODUCT(B6:B9,$E$6:$E$9)</f>
-        <v>0.246</v>
+        <v>0.188</v>
       </c>
       <c r="C10" s="11" t="n">
         <f aca="false">SUMPRODUCT(C6:C9,$E$6:$E$9)</f>
-        <v>0.423949589643946</v>
+        <v>0.341221112290217</v>
       </c>
       <c r="D10" s="11" t="n">
         <f aca="false">SUMPRODUCT(D6:D9,$E$6:$E$9)</f>
-        <v>1.624</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="8" t="n">
         <f aca="false">Assumptions!B5</f>
@@ -4180,16 +4300,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="12" t="n">
         <f aca="false">C10/Assumptions!B5-1</f>
-        <v>-0.806415712491349</v>
+        <v>-0.844191272926842</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4217,7 +4337,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4228,26 +4348,26 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="8" t="n">
         <f aca="false">Summary!B6</f>
@@ -4255,16 +4375,16 @@
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">Summary!C6</f>
-        <v>0.0233762361074855</v>
+        <v>0.01</v>
       </c>
       <c r="D6" s="8" t="n">
         <f aca="false">Summary!D6</f>
-        <v>2.36</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="8" t="n">
         <f aca="false">Summary!B7</f>
@@ -4281,24 +4401,24 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="8" t="n">
         <f aca="false">Summary!B8</f>
-        <v>0.55</v>
+        <v>0.26</v>
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">Summary!C8</f>
-        <v>1.11377559810627</v>
+        <v>0.726885683552602</v>
       </c>
       <c r="D8" s="8" t="n">
         <f aca="false">Summary!D8</f>
-        <v>1.92</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">Summary!B9</f>
@@ -4315,24 +4435,24 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="15" t="n">
         <f aca="false">Summary!B10</f>
-        <v>0.246</v>
+        <v>0.188</v>
       </c>
       <c r="C10" s="15" t="n">
         <f aca="false">Summary!C10</f>
-        <v>0.423949589643946</v>
+        <v>0.341221112290217</v>
       </c>
       <c r="D10" s="15" t="n">
         <f aca="false">Summary!D10</f>
-        <v>1.624</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="8" t="n">
         <f aca="false">Assumptions!B5</f>
@@ -4355,7 +4475,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -4368,7 +4488,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4381,77 +4501,77 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>2.19</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>3313.540373</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" s="18" t="n">
         <v>0.225</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>0.2231</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>0.034</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B11" s="12" t="n">
         <f aca="false">B9-B10</f>
@@ -4460,29 +4580,29 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>0.0941</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>0.964</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="12" t="n">
         <f aca="false">B11+B13*B12</f>
@@ -4491,18 +4611,18 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" s="18" t="n">
         <v>0.22</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B16" s="12" t="n">
         <f aca="false">B15*(1-B7)</f>
@@ -4511,7 +4631,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B17" s="6" t="n">
         <f aca="false">B5*B6</f>
@@ -4520,18 +4640,18 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B18" s="17" t="n">
         <v>10900</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B19" s="12" t="n">
         <f aca="false">B17/(B17+B18)</f>
@@ -4540,7 +4660,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B20" s="20" t="n">
         <f aca="false">B19*B14+(1-B19)*B16</f>
@@ -4549,29 +4669,29 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B21" s="18" t="n">
         <v>0.105</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" s="18" t="n">
         <v>0.07</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" s="12" t="n">
         <f aca="false">B21+B13*B22</f>
@@ -4580,114 +4700,114 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B24" s="18" t="n">
         <v>0.15</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B25" s="20" t="n">
-        <f aca="false">B19*B23+(1-B19)*B24*(1-B7)</f>
-        <v>0.138723393761621</v>
+        <f aca="false">(1-$B$56)*B23+$B$56*B24*(1-B7)</f>
+        <v>0.149988</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B26" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B28" s="17" t="n">
         <v>10200</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B29" s="17" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B31" s="21" t="n">
         <v>5.5</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B32" s="21" t="n">
         <v>6.5</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B33" s="18" t="n">
         <v>0.14</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B34" s="17" t="n">
         <v>4100</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B35" s="18" t="n">
         <v>0.4</v>
@@ -4695,7 +4815,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B36" s="18" t="n">
         <v>0.2</v>
@@ -4703,7 +4823,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B37" s="18" t="n">
         <v>0.2</v>
@@ -4711,7 +4831,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B38" s="18" t="n">
         <v>0.2</v>
@@ -4719,264 +4839,343 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C41" s="18" t="n">
-        <v>-0.196</v>
-      </c>
-      <c r="D41" s="18" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="F41" s="18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G41" s="18" t="n">
-        <v>0.08</v>
+        <v>101</v>
+      </c>
+      <c r="C41" s="22" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D41" s="22" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="E41" s="22" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F41" s="22" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G41" s="22" t="n">
+        <v>16</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C42" s="18" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="D42" s="18" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E42" s="18" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F42" s="18" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="G42" s="18" t="n">
-        <v>0.18</v>
+        <v>103</v>
+      </c>
+      <c r="C42" s="23" t="n">
+        <v>12600</v>
+      </c>
+      <c r="D42" s="23" t="n">
+        <v>12600</v>
+      </c>
+      <c r="E42" s="23" t="n">
+        <v>12600</v>
+      </c>
+      <c r="F42" s="23" t="n">
+        <v>12600</v>
+      </c>
+      <c r="G42" s="23" t="n">
+        <v>12600</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C43" s="18" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="D43" s="18" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="E43" s="18" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="F43" s="18" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="G43" s="18" t="n">
-        <v>0.013</v>
+        <v>105</v>
+      </c>
+      <c r="C43" s="22" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="D43" s="22" t="n">
+        <v>52</v>
+      </c>
+      <c r="E43" s="22" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="F43" s="22" t="n">
+        <v>55</v>
+      </c>
+      <c r="G43" s="22" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C44" s="18" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="D44" s="18" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="E44" s="18" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="F44" s="18" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="G44" s="18" t="n">
-        <v>0.016</v>
+        <v>107</v>
+      </c>
+      <c r="C44" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="D44" s="24" t="n">
+        <v>90</v>
+      </c>
+      <c r="E44" s="24" t="n">
+        <v>115</v>
+      </c>
+      <c r="F44" s="24" t="n">
+        <v>128</v>
+      </c>
+      <c r="G44" s="24" t="n">
+        <v>135</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C45" s="18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="D45" s="18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="18" t="n">
-        <v>0.94</v>
-      </c>
-      <c r="G45" s="18" t="n">
-        <v>0.88</v>
+        <v>109</v>
+      </c>
+      <c r="C45" s="23" t="n">
+        <v>225</v>
+      </c>
+      <c r="D45" s="23" t="n">
+        <v>243</v>
+      </c>
+      <c r="E45" s="23" t="n">
+        <v>262</v>
+      </c>
+      <c r="F45" s="23" t="n">
+        <v>283</v>
+      </c>
+      <c r="G45" s="23" t="n">
+        <v>306</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C46" s="18" t="n">
-        <v>0.22</v>
+        <v>0.013</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>0.2</v>
+        <v>0.013</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>0.185</v>
+        <v>0.013</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>0.168</v>
+        <v>0.013</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="H46" s="13" t="s">
-        <v>110</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C47" s="12" t="n">
-        <f aca="false">($C$46-C46)/($C$46-$G$46)</f>
-        <v>0</v>
-      </c>
-      <c r="D47" s="12" t="n">
-        <f aca="false">($C$46-D46)/($C$46-$G$46)</f>
-        <v>0.307692307692308</v>
-      </c>
-      <c r="E47" s="12" t="n">
-        <f aca="false">($C$46-E46)/($C$46-$G$46)</f>
-        <v>0.538461538461539</v>
-      </c>
-      <c r="F47" s="12" t="n">
-        <f aca="false">($C$46-F46)/($C$46-$G$46)</f>
-        <v>0.8</v>
-      </c>
-      <c r="G47" s="12" t="n">
-        <f aca="false">($C$46-G46)/($C$46-$G$46)</f>
+        <v>112</v>
+      </c>
+      <c r="C47" s="18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="D47" s="18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E47" s="18" t="n">
         <v>1</v>
+      </c>
+      <c r="F47" s="18" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="G47" s="18" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H47" s="13" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C48" s="12" t="n">
-        <f aca="false">$B$20-($B$20-$B$25)*C47</f>
-        <v>0.214188789049045</v>
-      </c>
-      <c r="D48" s="12" t="n">
-        <f aca="false">$B$20-($B$20-$B$25)*D47</f>
-        <v>0.190968667422146</v>
-      </c>
-      <c r="E48" s="12" t="n">
-        <f aca="false">$B$20-($B$20-$B$25)*E47</f>
-        <v>0.173553576201971</v>
-      </c>
-      <c r="F48" s="12" t="n">
-        <f aca="false">$B$20-($B$20-$B$25)*F47</f>
-        <v>0.153816472819106</v>
-      </c>
-      <c r="G48" s="12" t="n">
-        <f aca="false">$B$20-($B$20-$B$25)*G47</f>
-        <v>0.138723393761621</v>
+        <v>114</v>
+      </c>
+      <c r="C48" s="18" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D48" s="18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E48" s="18" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="F48" s="18" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="G48" s="18" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C49" s="22" t="n">
-        <f aca="false">1/(1+C48)</f>
-        <v>0.82359515177471</v>
-      </c>
-      <c r="D49" s="22" t="n">
-        <f aca="false">C49/(1+D48)</f>
-        <v>0.691533853327463</v>
-      </c>
-      <c r="E49" s="22" t="n">
-        <f aca="false">D49/(1+E48)</f>
-        <v>0.589264834048317</v>
-      </c>
-      <c r="F49" s="22" t="n">
-        <f aca="false">E49/(1+F48)</f>
-        <v>0.510709326768904</v>
-      </c>
-      <c r="G49" s="22" t="n">
-        <f aca="false">F49/(1+G48)</f>
-        <v>0.448492873305996</v>
+        <v>116</v>
+      </c>
+      <c r="C49" s="12" t="n">
+        <f aca="false">($C$48-C48)/($C$48-$G$48)</f>
+        <v>0</v>
+      </c>
+      <c r="D49" s="12" t="n">
+        <f aca="false">($C$48-D48)/($C$48-$G$48)</f>
+        <v>0.307692307692308</v>
+      </c>
+      <c r="E49" s="12" t="n">
+        <f aca="false">($C$48-E48)/($C$48-$G$48)</f>
+        <v>0.538461538461539</v>
+      </c>
+      <c r="F49" s="12" t="n">
+        <f aca="false">($C$48-F48)/($C$48-$G$48)</f>
+        <v>0.8</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <f aca="false">($C$48-G48)/($C$48-$G$48)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="16" t="s">
-        <v>114</v>
+      <c r="A50" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" s="12" t="n">
+        <f aca="false">$B$20-($B$20-$B$25)*C49</f>
+        <v>0.214188789049045</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <f aca="false">$B$20-($B$20-$B$25)*D49</f>
+        <v>0.194434700110878</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <f aca="false">$B$20-($B$20-$B$25)*E49</f>
+        <v>0.179619133407252</v>
+      </c>
+      <c r="F50" s="12" t="n">
+        <f aca="false">$B$20-($B$20-$B$25)*F49</f>
+        <v>0.162828157809809</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <f aca="false">$B$20-($B$20-$B$25)*G49</f>
+        <v>0.149988</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B51" s="17" t="n">
+        <v>118</v>
+      </c>
+      <c r="C51" s="25" t="n">
+        <f aca="false">1/(1+C50)</f>
+        <v>0.82359515177471</v>
+      </c>
+      <c r="D51" s="25" t="n">
+        <f aca="false">C51/(1+D50)</f>
+        <v>0.689527147610713</v>
+      </c>
+      <c r="E51" s="25" t="n">
+        <f aca="false">D51/(1+E50)</f>
+        <v>0.584533709299085</v>
+      </c>
+      <c r="F51" s="25" t="n">
+        <f aca="false">E51/(1+F50)</f>
+        <v>0.502682795710809</v>
+      </c>
+      <c r="G51" s="25" t="n">
+        <f aca="false">F51/(1+G50)</f>
+        <v>0.437120035783686</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" s="17" t="n">
         <v>10819</v>
       </c>
-      <c r="C51" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B52" s="17" t="n">
+      <c r="C53" s="13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B54" s="17" t="n">
         <v>12640</v>
       </c>
-      <c r="C52" s="13" t="s">
-        <v>118</v>
+      <c r="C54" s="13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" s="26" t="n">
+        <v>1.387</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B57" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -4995,7 +5194,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -5004,7 +5203,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5015,21 +5214,21 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="B5" s="23" t="n">
+        <v>132</v>
+      </c>
+      <c r="B5" s="27" t="n">
         <f aca="false">DCF!B26</f>
-        <v>10277.4581021109</v>
+        <v>5763.33382151802</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>0</v>
@@ -5037,93 +5236,102 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="B7" s="24" t="n">
+        <v>134</v>
+      </c>
+      <c r="B7" s="28" t="n">
         <f aca="false">-Assumptions!B28</f>
         <v>-10200</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="B8" s="24" t="n">
+        <v>135</v>
+      </c>
+      <c r="B8" s="28" t="n">
         <f aca="false">-Assumptions!B29</f>
         <v>-0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="B9" s="23" t="n">
+        <v>136</v>
+      </c>
+      <c r="B9" s="27" t="n">
         <f aca="false">B5+B6+B7+B8</f>
-        <v>77.4581021109334</v>
+        <v>-4436.66617848198</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="B10" s="15" t="n">
-        <f aca="false">B9/Assumptions!B6</f>
-        <v>0.0233762361074855</v>
+        <v>137</v>
+      </c>
+      <c r="B10" s="27" t="n">
+        <f aca="false">MAX(B9,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B11" s="25" t="n">
-        <f aca="false">B10/Assumptions!B5-1</f>
-        <v>-0.989325919585623</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>128</v>
+        <v>138</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <f aca="false">MAX(B10/Assumptions!B6,0.01)</f>
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" s="29" t="n">
+        <f aca="false">B11/Assumptions!B5-1</f>
+        <v>-0.995433789954338</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="24" t="n">
+      <c r="A14" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="28" t="n">
         <f aca="false">Assumptions!B17</f>
         <v>7256.65341687</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" s="6" t="n">
-        <f aca="false">B14+Assumptions!B28</f>
-        <v>17456.65341687</v>
-      </c>
-    </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B16" s="26" t="n">
-        <f aca="false">B15/Segments!F9</f>
-        <v>12.5743322939126</v>
+        <v>142</v>
+      </c>
+      <c r="B16" s="6" t="n">
+        <f aca="false">B15+Assumptions!B28</f>
+        <v>17456.65341687</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B17" s="26" t="n">
-        <f aca="false">B15/Segments!D9</f>
+        <v>143</v>
+      </c>
+      <c r="B17" s="30" t="n">
+        <f aca="false">B16/Segments!F15</f>
+        <v>16.2993962809244</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18" s="30" t="n">
+        <f aca="false">B16/Segments!D15</f>
         <v>6.07971585347624</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
-        <v>133</v>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -5142,7 +5350,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -5151,7 +5359,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5165,262 +5373,477 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="B6" s="27" t="n">
-        <v>8673.4</v>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>13778.2</v>
-      </c>
-      <c r="D6" s="27" t="n">
-        <v>10819</v>
-      </c>
-      <c r="E6" s="23" t="n">
-        <f aca="false">Assumptions!$B$51*(1+Assumptions!C41)</f>
-        <v>8698.476</v>
-      </c>
-      <c r="F6" s="23" t="n">
-        <f aca="false">E6*(1+Assumptions!D41)</f>
-        <v>9916.26264</v>
-      </c>
-      <c r="G6" s="23" t="n">
-        <f aca="false">F6*(1+Assumptions!E41)</f>
-        <v>11106.2141568</v>
-      </c>
-      <c r="H6" s="23" t="n">
-        <f aca="false">G6*(1+Assumptions!F41)</f>
-        <v>12216.83557248</v>
-      </c>
-      <c r="I6" s="23" t="n">
-        <f aca="false">H6*(1+Assumptions!G41)</f>
-        <v>13194.1824182784</v>
+      <c r="A6" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="31" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>24</v>
+      </c>
+      <c r="D6" s="31" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="E6" s="32" t="n">
+        <f aca="false">Assumptions!C41</f>
+        <v>10.4</v>
+      </c>
+      <c r="F6" s="32" t="n">
+        <f aca="false">Assumptions!D41</f>
+        <v>11.9</v>
+      </c>
+      <c r="G6" s="32" t="n">
+        <f aca="false">Assumptions!E41</f>
+        <v>13.4</v>
+      </c>
+      <c r="H6" s="32" t="n">
+        <f aca="false">Assumptions!F41</f>
+        <v>14.8</v>
+      </c>
+      <c r="I6" s="32" t="n">
+        <f aca="false">Assumptions!G41</f>
+        <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <f aca="false">E6*2/3</f>
-        <v>5798.984</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <f aca="false">F6*2/3</f>
-        <v>6610.84176</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <f aca="false">G6*2/3</f>
-        <v>7404.1427712</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <f aca="false">H6*2/3</f>
-        <v>8144.55704832</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <f aca="false">I6*2/3</f>
-        <v>8796.1216121856</v>
+        <v>152</v>
+      </c>
+      <c r="B7" s="12" t="n">
+        <f aca="false">B6/Assumptions!$B$57</f>
+        <v>0.96</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <f aca="false">C6/Assumptions!$B$57</f>
+        <v>0.96</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <f aca="false">D6/Assumptions!$B$57</f>
+        <v>0.632</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <f aca="false">E6/Assumptions!$B$57</f>
+        <v>0.416</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <f aca="false">F6/Assumptions!$B$57</f>
+        <v>0.476</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <f aca="false">G6/Assumptions!$B$57</f>
+        <v>0.536</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <f aca="false">H6/Assumptions!$B$57</f>
+        <v>0.592</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <f aca="false">I6/Assumptions!$B$57</f>
+        <v>0.64</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <f aca="false">E6/3</f>
-        <v>2899.492</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <f aca="false">F6/3</f>
-        <v>3305.42088</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <f aca="false">G6/3</f>
-        <v>3702.0713856</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <f aca="false">H6/3</f>
-        <v>4072.27852416</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <f aca="false">I6/3</f>
-        <v>4398.0608060928</v>
+        <v>153</v>
+      </c>
+      <c r="B8" s="23" t="n">
+        <v>8478</v>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>9147</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <f aca="false">Assumptions!C42</f>
+        <v>12600</v>
+      </c>
+      <c r="F8" s="33" t="n">
+        <f aca="false">Assumptions!D42</f>
+        <v>12600</v>
+      </c>
+      <c r="G8" s="33" t="n">
+        <f aca="false">Assumptions!E42</f>
+        <v>12600</v>
+      </c>
+      <c r="H8" s="33" t="n">
+        <f aca="false">Assumptions!F42</f>
+        <v>12600</v>
+      </c>
+      <c r="I8" s="33" t="n">
+        <f aca="false">Assumptions!G42</f>
+        <v>12600</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="B9" s="17" t="n">
-        <v>2661.03638064516</v>
-      </c>
-      <c r="C9" s="17" t="n">
-        <v>3490</v>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>2871.29429032258</v>
-      </c>
-      <c r="E9" s="24" t="n">
-        <f aca="false">E6*Assumptions!C42</f>
-        <v>652.3857</v>
-      </c>
-      <c r="F9" s="24" t="n">
-        <f aca="false">F6*Assumptions!D42</f>
-        <v>1388.2767696</v>
-      </c>
-      <c r="G9" s="24" t="n">
-        <f aca="false">G6*Assumptions!E42</f>
-        <v>1776.994265088</v>
-      </c>
-      <c r="H9" s="24" t="n">
-        <f aca="false">H6*Assumptions!F42</f>
-        <v>2137.946225184</v>
-      </c>
-      <c r="I9" s="24" t="n">
-        <f aca="false">I6*Assumptions!G42</f>
-        <v>2374.95283529011</v>
+        <v>105</v>
+      </c>
+      <c r="B9" s="22" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="C9" s="22" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="D9" s="22" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <f aca="false">Assumptions!C43</f>
+        <v>50.4</v>
+      </c>
+      <c r="F9" s="32" t="n">
+        <f aca="false">Assumptions!D43</f>
+        <v>52</v>
+      </c>
+      <c r="G9" s="32" t="n">
+        <f aca="false">Assumptions!E43</f>
+        <v>53.5</v>
+      </c>
+      <c r="H9" s="32" t="n">
+        <f aca="false">Assumptions!F43</f>
+        <v>55</v>
+      </c>
+      <c r="I9" s="32" t="n">
+        <f aca="false">Assumptions!G43</f>
+        <v>56.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" s="12" t="n">
-        <f aca="false">B9/B6</f>
+        <v>154</v>
+      </c>
+      <c r="B10" s="34" t="n">
+        <f aca="false">B8*B9*Assumptions!$B$55</f>
+        <v>361000.8702</v>
+      </c>
+      <c r="C10" s="34" t="n">
+        <f aca="false">C8*C9*Assumptions!$B$55</f>
+        <v>574716.0717</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <f aca="false">D8*D9*Assumptions!$B$55</f>
+        <v>686565</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <f aca="false">E8*E9*Assumptions!$B$55</f>
+        <v>880800.48</v>
+      </c>
+      <c r="F10" s="33" t="n">
+        <f aca="false">F8*F9*Assumptions!$B$55</f>
+        <v>908762.4</v>
+      </c>
+      <c r="G10" s="33" t="n">
+        <f aca="false">G8*G9*Assumptions!$B$55</f>
+        <v>934976.7</v>
+      </c>
+      <c r="H10" s="33" t="n">
+        <f aca="false">H8*H9*Assumptions!$B$55</f>
+        <v>961191</v>
+      </c>
+      <c r="I10" s="33" t="n">
+        <f aca="false">I8*I9*Assumptions!$B$55</f>
+        <v>987405.3</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" s="35" t="n">
+        <v>8673.4</v>
+      </c>
+      <c r="C11" s="35" t="n">
+        <v>13778.2</v>
+      </c>
+      <c r="D11" s="35" t="n">
+        <v>10819</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <f aca="false">E6*E10/1000</f>
+        <v>9160.324992</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <f aca="false">F6*F10/1000</f>
+        <v>10814.27256</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <f aca="false">G6*G10/1000</f>
+        <v>12528.68778</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <f aca="false">H6*H10/1000</f>
+        <v>14225.6268</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <f aca="false">I6*I10/1000</f>
+        <v>15798.4848</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <f aca="false">E11*2/3</f>
+        <v>6106.883328</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <f aca="false">F11*2/3</f>
+        <v>7209.51504</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <f aca="false">G11*2/3</f>
+        <v>8352.45852</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <f aca="false">H11*2/3</f>
+        <v>9483.7512</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <f aca="false">I11*2/3</f>
+        <v>10532.3232</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <f aca="false">E11/3</f>
+        <v>3053.441664</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <f aca="false">F11/3</f>
+        <v>3604.75752</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <f aca="false">G11/3</f>
+        <v>4176.22926</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <f aca="false">H11/3</f>
+        <v>4741.8756</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <f aca="false">I11/3</f>
+        <v>5266.1616</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="B14" s="36" t="n">
+        <v>111</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>146</v>
+      </c>
+      <c r="D14" s="36" t="n">
+        <v>182</v>
+      </c>
+      <c r="E14" s="37" t="n">
+        <f aca="false">Assumptions!C44</f>
+        <v>40</v>
+      </c>
+      <c r="F14" s="37" t="n">
+        <f aca="false">Assumptions!D44</f>
+        <v>90</v>
+      </c>
+      <c r="G14" s="37" t="n">
+        <f aca="false">Assumptions!E44</f>
+        <v>115</v>
+      </c>
+      <c r="H14" s="37" t="n">
+        <f aca="false">Assumptions!F44</f>
+        <v>128</v>
+      </c>
+      <c r="I14" s="37" t="n">
+        <f aca="false">Assumptions!G44</f>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="35" t="n">
+        <v>2661.03638064516</v>
+      </c>
+      <c r="C15" s="35" t="n">
+        <v>3490</v>
+      </c>
+      <c r="D15" s="35" t="n">
+        <v>2871.29429032258</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <f aca="false">E6*E14</f>
+        <v>416</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <f aca="false">F6*F14</f>
+        <v>1071</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <f aca="false">G6*G14</f>
+        <v>1541</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <f aca="false">H6*H14</f>
+        <v>1894.4</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <f aca="false">I6*I14</f>
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" s="12" t="n">
+        <f aca="false">B15/B11</f>
         <v>0.306804295967575</v>
       </c>
-      <c r="C10" s="12" t="n">
-        <f aca="false">C9/C6</f>
+      <c r="C16" s="12" t="n">
+        <f aca="false">C15/C11</f>
         <v>0.253298689233717</v>
       </c>
-      <c r="D10" s="12" t="n">
-        <f aca="false">D9/D6</f>
+      <c r="D16" s="12" t="n">
+        <f aca="false">D15/D11</f>
         <v>0.26539368613759</v>
       </c>
-      <c r="E10" s="12" t="n">
-        <f aca="false">E9/E6</f>
-        <v>0.075</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <f aca="false">F9/F6</f>
-        <v>0.14</v>
-      </c>
-      <c r="G10" s="12" t="n">
-        <f aca="false">G9/G6</f>
-        <v>0.16</v>
-      </c>
-      <c r="H10" s="12" t="n">
-        <f aca="false">H9/H6</f>
-        <v>0.175</v>
-      </c>
-      <c r="I10" s="12" t="n">
-        <f aca="false">I9/I6</f>
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="B11" s="17" t="n">
+      <c r="E16" s="12" t="n">
+        <f aca="false">E15/E11</f>
+        <v>0.0454132359237588</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <f aca="false">F15/F11</f>
+        <v>0.0990357875721971</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <f aca="false">G15/G11</f>
+        <v>0.122997717483227</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <f aca="false">H15/H11</f>
+        <v>0.133168121632433</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <f aca="false">I15/I11</f>
+        <v>0.136721972223564</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="B17" s="17" t="n">
         <v>60.7138</v>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C17" s="17" t="n">
         <v>90</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D17" s="17" t="n">
         <v>75.733</v>
       </c>
-      <c r="E11" s="24" t="n">
-        <f aca="false">E6*Assumptions!C43</f>
-        <v>113.080188</v>
-      </c>
-      <c r="F11" s="24" t="n">
-        <f aca="false">F6*Assumptions!D43</f>
-        <v>128.91141432</v>
-      </c>
-      <c r="G11" s="24" t="n">
-        <f aca="false">G6*Assumptions!E43</f>
-        <v>144.3807840384</v>
-      </c>
-      <c r="H11" s="24" t="n">
-        <f aca="false">H6*Assumptions!F43</f>
-        <v>158.81886244224</v>
-      </c>
-      <c r="I11" s="24" t="n">
-        <f aca="false">I6*Assumptions!G43</f>
-        <v>171.524371437619</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="B12" s="27" t="n">
+      <c r="E17" s="28" t="n">
+        <f aca="false">E11*Assumptions!C46</f>
+        <v>119.084224896</v>
+      </c>
+      <c r="F17" s="28" t="n">
+        <f aca="false">F11*Assumptions!D46</f>
+        <v>140.58554328</v>
+      </c>
+      <c r="G17" s="28" t="n">
+        <f aca="false">G11*Assumptions!E46</f>
+        <v>162.87294114</v>
+      </c>
+      <c r="H17" s="28" t="n">
+        <f aca="false">H11*Assumptions!F46</f>
+        <v>184.9331484</v>
+      </c>
+      <c r="I17" s="28" t="n">
+        <f aca="false">I11*Assumptions!G46</f>
+        <v>205.3803024</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B18" s="35" t="n">
         <v>2600.32258064516</v>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C18" s="35" t="n">
         <v>3400</v>
       </c>
-      <c r="D12" s="27" t="n">
+      <c r="D18" s="35" t="n">
         <v>2795.56129032258</v>
       </c>
-      <c r="E12" s="19" t="n">
-        <f aca="false">E9-E11</f>
-        <v>539.305512</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <f aca="false">F9-F11</f>
-        <v>1259.36535528</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <f aca="false">G9-G11</f>
-        <v>1632.6134810496</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <f aca="false">H9-H11</f>
-        <v>1979.12736274176</v>
-      </c>
-      <c r="I12" s="19" t="n">
-        <f aca="false">I9-I11</f>
-        <v>2203.42846385249</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>145</v>
+      <c r="E18" s="19" t="n">
+        <f aca="false">E15-E17</f>
+        <v>296.915775104</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <f aca="false">F15-F17</f>
+        <v>930.41445672</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <f aca="false">G15-G17</f>
+        <v>1378.12705886</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <f aca="false">H15-H17</f>
+        <v>1709.4668516</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <f aca="false">I15-I17</f>
+        <v>1954.6196976</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -5449,7 +5872,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5460,59 +5883,59 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C6" s="8" t="n">
-        <f aca="false">MAX((Assumptions!B31*Segments!F9-'Balance Sheet'!D11)/Assumptions!B6,0.05)</f>
+        <f aca="false">MAX((Assumptions!B31*Segments!F15-'Balance Sheet'!D11)/Assumptions!B6,0.05)</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="C7" s="8" t="n">
-        <f aca="false">(Segments!G12-Assumptions!B24*6000)*(1-Assumptions!B7)*Assumptions!B32/Assumptions!B6</f>
-        <v>1.11377559810627</v>
+        <f aca="false">(Segments!G18-Assumptions!B24*6000)*(1-Assumptions!B7)*Assumptions!B32/Assumptions!B6</f>
+        <v>0.726885683552602</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="C8" s="8" t="n">
-        <f aca="false">(Segments!G12-Assumptions!B24*6000)*(1-Assumptions!B7)/Assumptions!B6</f>
-        <v>0.17135009201635</v>
+        <f aca="false">(Segments!G18-Assumptions!B24*6000)*(1-Assumptions!B7)/Assumptions!B6</f>
+        <v>0.1118285667004</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="C9" s="8" t="n">
         <f aca="false">MAX((Assumptions!B33-Assumptions!B26)/(Assumptions!B23-Assumptions!B26),0.1)*Assumptions!B34/Assumptions!B6</f>
@@ -5521,9 +5944,9 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C11" s="26" t="n">
+        <v>175</v>
+      </c>
+      <c r="C11" s="30" t="n">
         <f aca="false">Assumptions!B5/(Assumptions!B34/Assumptions!B6)</f>
         <v>1.76991546752927</v>
       </c>
@@ -5544,7 +5967,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -5553,7 +5976,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5565,471 +5988,489 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="B6" s="24" t="n">
-        <f aca="false">Segments!E6</f>
-        <v>8698.476</v>
-      </c>
-      <c r="C6" s="24" t="n">
-        <f aca="false">Segments!F6</f>
-        <v>9916.26264</v>
-      </c>
-      <c r="D6" s="24" t="n">
-        <f aca="false">Segments!G6</f>
-        <v>11106.2141568</v>
-      </c>
-      <c r="E6" s="24" t="n">
-        <f aca="false">Segments!H6</f>
-        <v>12216.83557248</v>
-      </c>
-      <c r="F6" s="24" t="n">
-        <f aca="false">Segments!I6</f>
-        <v>13194.1824182784</v>
+        <v>178</v>
+      </c>
+      <c r="B6" s="28" t="n">
+        <f aca="false">Segments!E11</f>
+        <v>9160.324992</v>
+      </c>
+      <c r="C6" s="28" t="n">
+        <f aca="false">Segments!F11</f>
+        <v>10814.27256</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <f aca="false">Segments!G11</f>
+        <v>12528.68778</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <f aca="false">Segments!H11</f>
+        <v>14225.6268</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <f aca="false">Segments!I11</f>
+        <v>15798.4848</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="B7" s="24" t="n">
-        <f aca="false">Segments!E9</f>
-        <v>652.3857</v>
-      </c>
-      <c r="C7" s="24" t="n">
-        <f aca="false">Segments!F9</f>
-        <v>1388.2767696</v>
-      </c>
-      <c r="D7" s="24" t="n">
-        <f aca="false">Segments!G9</f>
-        <v>1776.994265088</v>
-      </c>
-      <c r="E7" s="24" t="n">
-        <f aca="false">Segments!H9</f>
-        <v>2137.946225184</v>
-      </c>
-      <c r="F7" s="24" t="n">
-        <f aca="false">Segments!I9</f>
-        <v>2374.95283529011</v>
+        <v>179</v>
+      </c>
+      <c r="B7" s="28" t="n">
+        <f aca="false">Segments!E15</f>
+        <v>416</v>
+      </c>
+      <c r="C7" s="28" t="n">
+        <f aca="false">Segments!F15</f>
+        <v>1071</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <f aca="false">Segments!G15</f>
+        <v>1541</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <f aca="false">Segments!H15</f>
+        <v>1894.4</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <f aca="false">Segments!I15</f>
+        <v>2160</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="B8" s="24" t="n">
-        <f aca="false">-Segments!E11</f>
-        <v>-113.080188</v>
-      </c>
-      <c r="C8" s="24" t="n">
-        <f aca="false">-Segments!F11</f>
-        <v>-128.91141432</v>
-      </c>
-      <c r="D8" s="24" t="n">
-        <f aca="false">-Segments!G11</f>
-        <v>-144.3807840384</v>
-      </c>
-      <c r="E8" s="24" t="n">
-        <f aca="false">-Segments!H11</f>
-        <v>-158.81886244224</v>
-      </c>
-      <c r="F8" s="24" t="n">
-        <f aca="false">-Segments!I11</f>
-        <v>-171.524371437619</v>
+        <v>180</v>
+      </c>
+      <c r="B8" s="28" t="n">
+        <f aca="false">-Segments!E17</f>
+        <v>-119.084224896</v>
+      </c>
+      <c r="C8" s="28" t="n">
+        <f aca="false">-Segments!F17</f>
+        <v>-140.58554328</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <f aca="false">-Segments!G17</f>
+        <v>-162.87294114</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <f aca="false">-Segments!H17</f>
+        <v>-184.9331484</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <f aca="false">-Segments!I17</f>
+        <v>-205.3803024</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="B9" s="24" t="n">
-        <f aca="false">Segments!E12</f>
-        <v>539.305512</v>
-      </c>
-      <c r="C9" s="24" t="n">
-        <f aca="false">Segments!F12</f>
-        <v>1259.36535528</v>
-      </c>
-      <c r="D9" s="24" t="n">
-        <f aca="false">Segments!G12</f>
-        <v>1632.6134810496</v>
-      </c>
-      <c r="E9" s="24" t="n">
-        <f aca="false">Segments!H12</f>
-        <v>1979.12736274176</v>
-      </c>
-      <c r="F9" s="24" t="n">
-        <f aca="false">Segments!I12</f>
-        <v>2203.42846385249</v>
+        <v>161</v>
+      </c>
+      <c r="B9" s="28" t="n">
+        <f aca="false">Segments!E18</f>
+        <v>296.915775104</v>
+      </c>
+      <c r="C9" s="28" t="n">
+        <f aca="false">Segments!F18</f>
+        <v>930.41445672</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <f aca="false">Segments!G18</f>
+        <v>1378.12705886</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <f aca="false">Segments!H18</f>
+        <v>1709.4668516</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <f aca="false">Segments!I18</f>
+        <v>1954.6196976</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="B10" s="24" t="n">
+        <v>181</v>
+      </c>
+      <c r="B10" s="28" t="n">
         <f aca="false">B9*(1-Assumptions!$B$7)</f>
-        <v>417.9617718</v>
-      </c>
-      <c r="C10" s="24" t="n">
+        <v>230.1097257056</v>
+      </c>
+      <c r="C10" s="28" t="n">
         <f aca="false">C9*(1-Assumptions!$B$7)</f>
-        <v>976.008150342</v>
-      </c>
-      <c r="D10" s="24" t="n">
+        <v>721.071203958</v>
+      </c>
+      <c r="D10" s="28" t="n">
         <f aca="false">D9*(1-Assumptions!$B$7)</f>
-        <v>1265.27544781344</v>
-      </c>
-      <c r="E10" s="24" t="n">
+        <v>1068.0484706165</v>
+      </c>
+      <c r="E10" s="28" t="n">
         <f aca="false">E9*(1-Assumptions!$B$7)</f>
-        <v>1533.82370612486</v>
-      </c>
-      <c r="F10" s="24" t="n">
+        <v>1324.83680999</v>
+      </c>
+      <c r="F10" s="28" t="n">
         <f aca="false">F9*(1-Assumptions!$B$7)</f>
-        <v>1707.65705948568</v>
+        <v>1514.83026564</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="B11" s="24" t="n">
-        <f aca="false">Segments!E11</f>
-        <v>113.080188</v>
-      </c>
-      <c r="C11" s="24" t="n">
-        <f aca="false">Segments!F11</f>
-        <v>128.91141432</v>
-      </c>
-      <c r="D11" s="24" t="n">
-        <f aca="false">Segments!G11</f>
-        <v>144.3807840384</v>
-      </c>
-      <c r="E11" s="24" t="n">
-        <f aca="false">Segments!H11</f>
-        <v>158.81886244224</v>
-      </c>
-      <c r="F11" s="24" t="n">
-        <f aca="false">Segments!I11</f>
-        <v>171.524371437619</v>
+        <v>182</v>
+      </c>
+      <c r="B11" s="28" t="n">
+        <f aca="false">Segments!E17</f>
+        <v>119.084224896</v>
+      </c>
+      <c r="C11" s="28" t="n">
+        <f aca="false">Segments!F17</f>
+        <v>140.58554328</v>
+      </c>
+      <c r="D11" s="28" t="n">
+        <f aca="false">Segments!G17</f>
+        <v>162.87294114</v>
+      </c>
+      <c r="E11" s="28" t="n">
+        <f aca="false">Segments!H17</f>
+        <v>184.9331484</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <f aca="false">Segments!I17</f>
+        <v>205.3803024</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="B12" s="24" t="n">
-        <f aca="false">-B6*Assumptions!C44</f>
-        <v>-139.175616</v>
-      </c>
-      <c r="C12" s="24" t="n">
-        <f aca="false">-C6*Assumptions!D44</f>
-        <v>-158.66020224</v>
-      </c>
-      <c r="D12" s="24" t="n">
-        <f aca="false">-D6*Assumptions!E44</f>
-        <v>-177.6994265088</v>
-      </c>
-      <c r="E12" s="24" t="n">
-        <f aca="false">-E6*Assumptions!F44</f>
-        <v>-195.46936915968</v>
-      </c>
-      <c r="F12" s="24" t="n">
-        <f aca="false">-F6*Assumptions!G44</f>
-        <v>-211.106918692454</v>
+        <v>183</v>
+      </c>
+      <c r="B12" s="28" t="n">
+        <f aca="false">-Assumptions!C45</f>
+        <v>-225</v>
+      </c>
+      <c r="C12" s="28" t="n">
+        <f aca="false">-Assumptions!D45</f>
+        <v>-243</v>
+      </c>
+      <c r="D12" s="28" t="n">
+        <f aca="false">-Assumptions!E45</f>
+        <v>-262</v>
+      </c>
+      <c r="E12" s="28" t="n">
+        <f aca="false">-Assumptions!F45</f>
+        <v>-283</v>
+      </c>
+      <c r="F12" s="28" t="n">
+        <f aca="false">-Assumptions!G45</f>
+        <v>-306</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="B13" s="24" t="n">
-        <f aca="false">B6*Assumptions!C45</f>
-        <v>9742.29312</v>
-      </c>
-      <c r="C13" s="24" t="n">
-        <f aca="false">C6*Assumptions!D45</f>
-        <v>10511.2383984</v>
-      </c>
-      <c r="D13" s="24" t="n">
-        <f aca="false">D6*Assumptions!E45</f>
-        <v>11106.2141568</v>
-      </c>
-      <c r="E13" s="24" t="n">
-        <f aca="false">E6*Assumptions!F45</f>
-        <v>11483.8254381312</v>
-      </c>
-      <c r="F13" s="24" t="n">
-        <f aca="false">F6*Assumptions!G45</f>
-        <v>11610.880528085</v>
+        <v>184</v>
+      </c>
+      <c r="B13" s="28" t="n">
+        <f aca="false">B6*Assumptions!C47</f>
+        <v>10259.56399104</v>
+      </c>
+      <c r="C13" s="28" t="n">
+        <f aca="false">C6*Assumptions!D47</f>
+        <v>11463.1289136</v>
+      </c>
+      <c r="D13" s="28" t="n">
+        <f aca="false">D6*Assumptions!E47</f>
+        <v>12528.68778</v>
+      </c>
+      <c r="E13" s="28" t="n">
+        <f aca="false">E6*Assumptions!F47</f>
+        <v>13372.089192</v>
+      </c>
+      <c r="F13" s="28" t="n">
+        <f aca="false">F6*Assumptions!G47</f>
+        <v>13902.666624</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="B14" s="24" t="n">
-        <f aca="false">-(B13-Assumptions!$B$52)</f>
-        <v>2897.70688</v>
+        <v>185</v>
+      </c>
+      <c r="B14" s="28" t="n">
+        <f aca="false">-(B13-Assumptions!$B$54)</f>
+        <v>2380.43600896</v>
       </c>
       <c r="C14" s="6" t="n">
         <f aca="false">-(C13-B13)</f>
-        <v>-768.945278399999</v>
+        <v>-1203.56492256</v>
       </c>
       <c r="D14" s="6" t="n">
         <f aca="false">-(D13-C13)</f>
-        <v>-594.975758400002</v>
+        <v>-1065.5588664</v>
       </c>
       <c r="E14" s="6" t="n">
         <f aca="false">-(E13-D13)</f>
-        <v>-377.611281331201</v>
+        <v>-843.401411999999</v>
       </c>
       <c r="F14" s="6" t="n">
         <f aca="false">-(F13-E13)</f>
-        <v>-127.055089953794</v>
+        <v>-530.577432</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">B10+B11+B12+B14</f>
-        <v>3289.5732238</v>
+        <v>2504.6299595616</v>
       </c>
       <c r="C15" s="19" t="n">
         <f aca="false">C10+C11+C12+C14</f>
-        <v>177.314084022002</v>
+        <v>-584.908175322001</v>
       </c>
       <c r="D15" s="19" t="n">
         <f aca="false">D10+D11+D12+D14</f>
-        <v>636.981046943039</v>
+        <v>-96.6374546434988</v>
       </c>
       <c r="E15" s="19" t="n">
         <f aca="false">E10+E11+E12+E14</f>
-        <v>1119.56191807622</v>
+        <v>383.368546390001</v>
       </c>
       <c r="F15" s="19" t="n">
         <f aca="false">F10+F11+F12+F14</f>
-        <v>1541.01942227705</v>
+        <v>883.63313604</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B16" s="9" t="n">
-        <f aca="false">Assumptions!C48</f>
+        <f aca="false">Assumptions!C50</f>
         <v>0.214188789049045</v>
       </c>
       <c r="C16" s="9" t="n">
-        <f aca="false">Assumptions!D48</f>
-        <v>0.190968667422146</v>
+        <f aca="false">Assumptions!D50</f>
+        <v>0.194434700110878</v>
       </c>
       <c r="D16" s="9" t="n">
-        <f aca="false">Assumptions!E48</f>
-        <v>0.173553576201971</v>
+        <f aca="false">Assumptions!E50</f>
+        <v>0.179619133407252</v>
       </c>
       <c r="E16" s="9" t="n">
-        <f aca="false">Assumptions!F48</f>
-        <v>0.153816472819106</v>
+        <f aca="false">Assumptions!F50</f>
+        <v>0.162828157809809</v>
       </c>
       <c r="F16" s="9" t="n">
-        <f aca="false">Assumptions!G48</f>
-        <v>0.138723393761621</v>
+        <f aca="false">Assumptions!G50</f>
+        <v>0.149988</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="B17" s="28" t="n">
-        <f aca="false">Assumptions!C49</f>
+        <v>118</v>
+      </c>
+      <c r="B17" s="38" t="n">
+        <f aca="false">Assumptions!C51</f>
         <v>0.82359515177471</v>
       </c>
-      <c r="C17" s="28" t="n">
-        <f aca="false">Assumptions!D49</f>
-        <v>0.691533853327463</v>
-      </c>
-      <c r="D17" s="28" t="n">
-        <f aca="false">Assumptions!E49</f>
-        <v>0.589264834048317</v>
-      </c>
-      <c r="E17" s="28" t="n">
-        <f aca="false">Assumptions!F49</f>
-        <v>0.510709326768904</v>
-      </c>
-      <c r="F17" s="28" t="n">
-        <f aca="false">Assumptions!G49</f>
-        <v>0.448492873305996</v>
+      <c r="C17" s="38" t="n">
+        <f aca="false">Assumptions!D51</f>
+        <v>0.689527147610713</v>
+      </c>
+      <c r="D17" s="38" t="n">
+        <f aca="false">Assumptions!E51</f>
+        <v>0.584533709299085</v>
+      </c>
+      <c r="E17" s="38" t="n">
+        <f aca="false">Assumptions!F51</f>
+        <v>0.502682795710809</v>
+      </c>
+      <c r="F17" s="38" t="n">
+        <f aca="false">Assumptions!G51</f>
+        <v>0.437120035783686</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="B18" s="19" t="n">
         <f aca="false">B15*B17</f>
-        <v>2709.27655852958</v>
+        <v>2062.80109168462</v>
       </c>
       <c r="C18" s="19" t="n">
         <f aca="false">C15*C17</f>
-        <v>122.618691772964</v>
+        <v>-403.310065743966</v>
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">D15*D17</f>
-        <v>375.350530918813</v>
+        <v>-56.4878498199864</v>
       </c>
       <c r="E18" s="19" t="n">
         <f aca="false">E15*E17</f>
-        <v>571.770713456811</v>
+        <v>192.712772686915</v>
       </c>
       <c r="F18" s="19" t="n">
         <f aca="false">F15*F17</f>
-        <v>691.136228517381</v>
+        <v>386.253748045455</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="B20" s="19" t="n">
         <f aca="false">SUM(B18:F18)</f>
-        <v>4470.15272319555</v>
+        <v>2181.96969685304</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="B21" s="12" t="n">
         <f aca="false">F10/(F13+0.05*F6)</f>
-        <v>0.139166666666667</v>
+        <v>0.103101643519637</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="B22" s="12" t="n">
         <f aca="false">Assumptions!$B$26/B21</f>
-        <v>0.359281437125749</v>
+        <v>0.484958321643796</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B23" s="6" t="n">
         <f aca="false">F10*(1+Assumptions!$B$26)*(1-B22)</f>
-        <v>1148.83395588752</v>
+        <v>819.210758562</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="B24" s="6" t="n">
         <f aca="false">B23/(Assumptions!$B$25-Assumptions!$B$26)</f>
-        <v>12948.4897632993</v>
+        <v>8193.09075651078</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="B25" s="6" t="n">
         <f aca="false">B24*F17</f>
-        <v>5807.30537891538</v>
+        <v>3581.36412466498</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="B26" s="19" t="n">
         <f aca="false">B20+B25</f>
-        <v>10277.4581021109</v>
+        <v>5763.33382151802</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B27" s="12" t="n">
         <f aca="false">B25/B26</f>
-        <v>0.565052693109261</v>
+        <v>0.621404942967831</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="B28" s="24" t="n">
+        <v>196</v>
+      </c>
+      <c r="B28" s="28" t="n">
         <f aca="false">-Assumptions!$B$28</f>
         <v>-10200</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="B29" s="24" t="n">
+        <v>197</v>
+      </c>
+      <c r="B29" s="28" t="n">
         <f aca="false">-Assumptions!$B$29</f>
         <v>-0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>125</v>
+        <v>198</v>
       </c>
       <c r="B30" s="19" t="n">
         <f aca="false">B26-Assumptions!$B$28-Assumptions!$B$29</f>
-        <v>77.4581021109334</v>
+        <v>-4436.66617848198</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="B31" s="11" t="n">
+        <v>199</v>
+      </c>
+      <c r="B31" s="19" t="n">
+        <f aca="false">MAX(B30,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B32" s="39" t="n">
         <f aca="false">B30/Assumptions!$B$6</f>
-        <v>0.0233762361074855</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B32" s="20" t="n">
-        <f aca="false">B31/Assumptions!$B$5-1</f>
-        <v>-0.989325919585623</v>
+        <v>-1.33895039113863</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="B33" s="11" t="n">
+        <f aca="false">MAX(B31/Assumptions!$B$6,0.01)</f>
+        <v>0.01</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="s">
-        <v>179</v>
+      <c r="A34" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B34" s="20" t="n">
+        <f aca="false">B33/Assumptions!$B$5-1</f>
+        <v>-0.995433789954338</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -6057,7 +6498,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6071,73 +6512,73 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="B6" s="27" t="n">
+        <v>178</v>
+      </c>
+      <c r="B6" s="35" t="n">
         <v>8673.4</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="35" t="n">
         <v>13778.2</v>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="35" t="n">
         <v>10819</v>
       </c>
-      <c r="E6" s="23" t="n">
-        <f aca="false">Segments!E6</f>
-        <v>8698.476</v>
-      </c>
-      <c r="F6" s="23" t="n">
-        <f aca="false">Segments!F6</f>
-        <v>9916.26264</v>
-      </c>
-      <c r="G6" s="23" t="n">
-        <f aca="false">Segments!G6</f>
-        <v>11106.2141568</v>
-      </c>
-      <c r="H6" s="23" t="n">
-        <f aca="false">Segments!H6</f>
-        <v>12216.83557248</v>
-      </c>
-      <c r="I6" s="23" t="n">
-        <f aca="false">Segments!I6</f>
-        <v>13194.1824182784</v>
+      <c r="E6" s="27" t="n">
+        <f aca="false">Segments!E11</f>
+        <v>9160.324992</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <f aca="false">Segments!F11</f>
+        <v>10814.27256</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <f aca="false">Segments!G11</f>
+        <v>12528.68778</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <f aca="false">Segments!H11</f>
+        <v>14225.6268</v>
+      </c>
+      <c r="I6" s="27" t="n">
+        <f aca="false">Segments!I11</f>
+        <v>15798.4848</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>2661.03638064516</v>
@@ -6148,30 +6589,30 @@
       <c r="D7" s="17" t="n">
         <v>2871.29429032258</v>
       </c>
-      <c r="E7" s="24" t="n">
-        <f aca="false">Segments!E9</f>
-        <v>652.3857</v>
-      </c>
-      <c r="F7" s="24" t="n">
-        <f aca="false">Segments!F9</f>
-        <v>1388.2767696</v>
-      </c>
-      <c r="G7" s="24" t="n">
-        <f aca="false">Segments!G9</f>
-        <v>1776.994265088</v>
-      </c>
-      <c r="H7" s="24" t="n">
-        <f aca="false">Segments!H9</f>
-        <v>2137.946225184</v>
-      </c>
-      <c r="I7" s="24" t="n">
-        <f aca="false">Segments!I9</f>
-        <v>2374.95283529011</v>
+      <c r="E7" s="28" t="n">
+        <f aca="false">Segments!E15</f>
+        <v>416</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <f aca="false">Segments!F15</f>
+        <v>1071</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <f aca="false">Segments!G15</f>
+        <v>1541</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <f aca="false">Segments!H15</f>
+        <v>1894.4</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <f aca="false">Segments!I15</f>
+        <v>2160</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="B8" s="17" t="n">
         <v>-60.7138</v>
@@ -6182,64 +6623,64 @@
       <c r="D8" s="17" t="n">
         <v>-75.733</v>
       </c>
-      <c r="E8" s="24" t="n">
-        <f aca="false">-Segments!E11</f>
-        <v>-113.080188</v>
-      </c>
-      <c r="F8" s="24" t="n">
-        <f aca="false">-Segments!F11</f>
-        <v>-128.91141432</v>
-      </c>
-      <c r="G8" s="24" t="n">
-        <f aca="false">-Segments!G11</f>
-        <v>-144.3807840384</v>
-      </c>
-      <c r="H8" s="24" t="n">
-        <f aca="false">-Segments!H11</f>
-        <v>-158.81886244224</v>
-      </c>
-      <c r="I8" s="24" t="n">
-        <f aca="false">-Segments!I11</f>
-        <v>-171.524371437619</v>
+      <c r="E8" s="28" t="n">
+        <f aca="false">-Segments!E17</f>
+        <v>-119.084224896</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <f aca="false">-Segments!F17</f>
+        <v>-140.58554328</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <f aca="false">-Segments!G17</f>
+        <v>-162.87294114</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <f aca="false">-Segments!H17</f>
+        <v>-184.9331484</v>
+      </c>
+      <c r="I8" s="28" t="n">
+        <f aca="false">-Segments!I17</f>
+        <v>-205.3803024</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="B9" s="27" t="n">
+        <v>161</v>
+      </c>
+      <c r="B9" s="35" t="n">
         <v>2600.32258064516</v>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="35" t="n">
         <v>3400</v>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="35" t="n">
         <v>2795.56129032258</v>
       </c>
-      <c r="E9" s="23" t="n">
-        <f aca="false">Segments!E12</f>
-        <v>539.305512</v>
-      </c>
-      <c r="F9" s="23" t="n">
-        <f aca="false">Segments!F12</f>
-        <v>1259.36535528</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <f aca="false">Segments!G12</f>
-        <v>1632.6134810496</v>
-      </c>
-      <c r="H9" s="23" t="n">
-        <f aca="false">Segments!H12</f>
-        <v>1979.12736274176</v>
-      </c>
-      <c r="I9" s="23" t="n">
-        <f aca="false">Segments!I12</f>
-        <v>2203.42846385249</v>
+      <c r="E9" s="27" t="n">
+        <f aca="false">Segments!E18</f>
+        <v>296.915775104</v>
+      </c>
+      <c r="F9" s="27" t="n">
+        <f aca="false">Segments!F18</f>
+        <v>930.41445672</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <f aca="false">Segments!G18</f>
+        <v>1378.12705886</v>
+      </c>
+      <c r="H9" s="27" t="n">
+        <f aca="false">Segments!H18</f>
+        <v>1709.4668516</v>
+      </c>
+      <c r="I9" s="27" t="n">
+        <f aca="false">Segments!I18</f>
+        <v>1954.6196976</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="B10" s="17" t="n">
         <v>-990</v>
@@ -6250,30 +6691,30 @@
       <c r="D10" s="17" t="n">
         <v>-2150</v>
       </c>
-      <c r="E10" s="24" t="n">
-        <f aca="false">-Assumptions!C46*Assumptions!$B$28</f>
+      <c r="E10" s="28" t="n">
+        <f aca="false">-Assumptions!C48*Assumptions!$B$28</f>
         <v>-2244</v>
       </c>
-      <c r="F10" s="24" t="n">
-        <f aca="false">-Assumptions!D46*'Balance Sheet'!D11</f>
-        <v>-1806.6166072</v>
-      </c>
-      <c r="G10" s="24" t="n">
-        <f aca="false">-Assumptions!E46*'Balance Sheet'!E11</f>
-        <v>-1920.1202455344</v>
-      </c>
-      <c r="H10" s="24" t="n">
-        <f aca="false">-Assumptions!F46*'Balance Sheet'!F11</f>
-        <v>-1897.53135929199</v>
-      </c>
-      <c r="I10" s="24" t="n">
-        <f aca="false">-Assumptions!G46*'Balance Sheet'!G11</f>
-        <v>-1802.26177215008</v>
+      <c r="F10" s="28" t="n">
+        <f aca="false">-Assumptions!D48*'Balance Sheet'!D11</f>
+        <v>-1974.512798208</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <f aca="false">-Assumptions!E48*'Balance Sheet'!E11</f>
+        <v>-2261.18871668448</v>
+      </c>
+      <c r="H10" s="28" t="n">
+        <f aca="false">-Assumptions!F48*'Balance Sheet'!F11</f>
+        <v>-2397.42540154194</v>
+      </c>
+      <c r="I10" s="28" t="n">
+        <f aca="false">-Assumptions!G48*'Balance Sheet'!G11</f>
+        <v>-2464.47149680733</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="B11" s="19" t="n">
         <v>1610.32258064516</v>
@@ -6286,53 +6727,53 @@
       </c>
       <c r="E11" s="19" t="n">
         <f aca="false">E9+E10</f>
-        <v>-1704.694488</v>
+        <v>-1947.084224896</v>
       </c>
       <c r="F11" s="19" t="n">
         <f aca="false">F9+F10</f>
-        <v>-547.25125192</v>
+        <v>-1044.098341488</v>
       </c>
       <c r="G11" s="19" t="n">
         <f aca="false">G9+G10</f>
-        <v>-287.5067644848</v>
+        <v>-883.06165782448</v>
       </c>
       <c r="H11" s="19" t="n">
         <f aca="false">H9+H10</f>
-        <v>81.5960034497662</v>
+        <v>-687.958549941937</v>
       </c>
       <c r="I11" s="19" t="n">
         <f aca="false">I9+I10</f>
-        <v>401.166691702412</v>
+        <v>-509.851799207334</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="E12" s="6" t="n">
         <f aca="false">SUM($E$11:E11)</f>
-        <v>-1704.694488</v>
+        <v>-1947.084224896</v>
       </c>
       <c r="F12" s="6" t="n">
         <f aca="false">SUM($E$11:F11)</f>
-        <v>-2251.94573992</v>
+        <v>-2991.182566384</v>
       </c>
       <c r="G12" s="6" t="n">
         <f aca="false">SUM($E$11:G11)</f>
-        <v>-2539.4525044048</v>
+        <v>-3874.24422420848</v>
       </c>
       <c r="H12" s="6" t="n">
         <f aca="false">SUM($E$11:H11)</f>
-        <v>-2457.85650095503</v>
+        <v>-4562.20277415042</v>
       </c>
       <c r="I12" s="6" t="n">
         <f aca="false">SUM($E$11:I11)</f>
-        <v>-2056.68980925262</v>
+        <v>-5072.05457335775</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="B13" s="17" t="n">
         <v>-362.322580645161</v>
@@ -6343,101 +6784,101 @@
       <c r="D13" s="17" t="n">
         <v>-145.251290322581</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="28" t="n">
         <f aca="false">-Assumptions!$B$7*MAX(0,E12)</f>
         <v>-0</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="28" t="n">
         <f aca="false">-(Assumptions!$B$7*MAX(0,F12)-Assumptions!$B$7*MAX(0,C12))</f>
         <v>-0</v>
       </c>
-      <c r="G13" s="24" t="n">
+      <c r="G13" s="28" t="n">
         <f aca="false">-(Assumptions!$B$7*MAX(0,G12)-Assumptions!$B$7*MAX(0,D12))</f>
         <v>-0</v>
       </c>
-      <c r="H13" s="24" t="n">
+      <c r="H13" s="28" t="n">
         <f aca="false">-(Assumptions!$B$7*MAX(0,H12)-Assumptions!$B$7*MAX(0,E12))</f>
         <v>-0</v>
       </c>
-      <c r="I13" s="24" t="n">
+      <c r="I13" s="28" t="n">
         <f aca="false">-(Assumptions!$B$7*MAX(0,I12)-Assumptions!$B$7*MAX(0,F12))</f>
         <v>-0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="B14" s="27" t="n">
+        <v>209</v>
+      </c>
+      <c r="B14" s="35" t="n">
         <v>1248</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="35" t="n">
         <v>1327.8</v>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D14" s="35" t="n">
         <v>500.31</v>
       </c>
       <c r="E14" s="19" t="n">
         <f aca="false">E11+E13</f>
-        <v>-1704.694488</v>
+        <v>-1947.084224896</v>
       </c>
       <c r="F14" s="19" t="n">
         <f aca="false">F11+F13</f>
-        <v>-547.25125192</v>
+        <v>-1044.098341488</v>
       </c>
       <c r="G14" s="19" t="n">
         <f aca="false">G11+G13</f>
-        <v>-287.5067644848</v>
+        <v>-883.06165782448</v>
       </c>
       <c r="H14" s="19" t="n">
         <f aca="false">H11+H13</f>
-        <v>81.5960034497662</v>
+        <v>-687.958549941937</v>
       </c>
       <c r="I14" s="19" t="n">
         <f aca="false">I11+I13</f>
-        <v>401.166691702412</v>
+        <v>-509.851799207334</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B15" s="29" t="n">
+        <v>210</v>
+      </c>
+      <c r="B15" s="39" t="n">
         <f aca="false">B14/Assumptions!$B$6</f>
         <v>0.376636424945712</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="39" t="n">
         <f aca="false">C14/Assumptions!$B$6</f>
         <v>0.400719427117721</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="39" t="n">
         <f aca="false">D14/Assumptions!$B$6</f>
         <v>0.150989559106241</v>
       </c>
       <c r="E15" s="8" t="n">
         <f aca="false">E14/Assumptions!$B$6</f>
-        <v>-0.514463171141811</v>
+        <v>-0.587614456356588</v>
       </c>
       <c r="F15" s="8" t="n">
         <f aca="false">F14/Assumptions!$B$6</f>
-        <v>-0.165156053742159</v>
+        <v>-0.315100534158483</v>
       </c>
       <c r="G15" s="8" t="n">
         <f aca="false">G14/Assumptions!$B$6</f>
-        <v>-0.0867672435282562</v>
+        <v>-0.266500950167985</v>
       </c>
       <c r="H15" s="8" t="n">
         <f aca="false">H14/Assumptions!$B$6</f>
-        <v>0.0246250216579951</v>
+        <v>-0.20762039163539</v>
       </c>
       <c r="I15" s="8" t="n">
         <f aca="false">I14/Assumptions!$B$6</f>
-        <v>0.121068901097832</v>
+        <v>-0.153869197841017</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/engine/elec_study/ELEC_Valuation_Model_05082026_public.xlsx
+++ b/engine/elec_study/ELEC_Valuation_Model_05082026_public.xlsx
@@ -3417,7 +3417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3596,8 +3596,19 @@
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Terminal value share of DCF enterprise value</t>
+        </is>
+      </c>
+      <c r="B14" s="9">
+        <f>DCF!B27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Read: meaningfully overvalued — the price capitalises devaluation-era earnings; the swing factors are working-capital collection, margin normalisation, and the easing path.</t>
         </is>

--- a/engine/elec_study/ELEC_Valuation_Model_05082026_public.xlsx
+++ b/engine/elec_study/ELEC_Valuation_Model_05082026_public.xlsx
@@ -1432,7 +1432,7 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>No dividends modelled — the company has never paid one and the balance sheet argues against a first.</t>
+          <t>No dividends modelled — none in the disclosed record and the balance sheet argues against a first.</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2238,19 +2238,19 @@
         <v>0.129988</v>
       </c>
       <c r="B9" s="39" t="n">
-        <v>-0.87</v>
+        <v>-1.31</v>
       </c>
       <c r="C9" s="39" t="n">
-        <v>-0.92</v>
+        <v>-1.4</v>
       </c>
       <c r="D9" s="39" t="n">
-        <v>-0.98</v>
+        <v>-1.51</v>
       </c>
       <c r="E9" s="39" t="n">
-        <v>-1.07</v>
+        <v>-1.66</v>
       </c>
       <c r="F9" s="39" t="n">
-        <v>-1.2</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="10">
@@ -2258,19 +2258,19 @@
         <v>0.139988</v>
       </c>
       <c r="B10" s="39" t="n">
-        <v>-1.04</v>
+        <v>-1.48</v>
       </c>
       <c r="C10" s="39" t="n">
-        <v>-1.1</v>
+        <v>-1.56</v>
       </c>
       <c r="D10" s="39" t="n">
-        <v>-1.17</v>
+        <v>-1.68</v>
       </c>
       <c r="E10" s="39" t="n">
-        <v>-1.27</v>
+        <v>-1.82</v>
       </c>
       <c r="F10" s="39" t="n">
-        <v>-1.39</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="11">
@@ -2278,19 +2278,19 @@
         <v>0.149988</v>
       </c>
       <c r="B11" s="39" t="n">
-        <v>-1.19</v>
+        <v>-1.61</v>
       </c>
       <c r="C11" s="39" t="n">
-        <v>-1.25</v>
+        <v>-1.7</v>
       </c>
       <c r="D11" s="39" t="n">
-        <v>-1.32</v>
+        <v>-1.81</v>
       </c>
       <c r="E11" s="39" t="n">
-        <v>-1.42</v>
+        <v>-1.95</v>
       </c>
       <c r="F11" s="39" t="n">
-        <v>-1.54</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="12">
@@ -2298,19 +2298,19 @@
         <v>0.159988</v>
       </c>
       <c r="B12" s="39" t="n">
-        <v>-1.31</v>
+        <v>-1.72</v>
       </c>
       <c r="C12" s="39" t="n">
-        <v>-1.37</v>
+        <v>-1.81</v>
       </c>
       <c r="D12" s="39" t="n">
-        <v>-1.44</v>
+        <v>-1.92</v>
       </c>
       <c r="E12" s="39" t="n">
-        <v>-1.54</v>
+        <v>-2.05</v>
       </c>
       <c r="F12" s="39" t="n">
-        <v>-1.66</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="13">
@@ -2318,19 +2318,19 @@
         <v>0.169988</v>
       </c>
       <c r="B13" s="39" t="n">
-        <v>-1.41</v>
+        <v>-1.82</v>
       </c>
       <c r="C13" s="39" t="n">
-        <v>-1.47</v>
+        <v>-1.9</v>
       </c>
       <c r="D13" s="39" t="n">
-        <v>-1.55</v>
+        <v>-2</v>
       </c>
       <c r="E13" s="39" t="n">
-        <v>-1.64</v>
+        <v>-2.13</v>
       </c>
       <c r="F13" s="39" t="n">
-        <v>-1.75</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="15">
@@ -2367,19 +2367,19 @@
         <v>0.1952611846539747</v>
       </c>
       <c r="B17" s="39" t="n">
-        <v>-0.91</v>
+        <v>-1.46</v>
       </c>
       <c r="C17" s="39" t="n">
-        <v>-1.11</v>
+        <v>-1.63</v>
       </c>
       <c r="D17" s="39" t="n">
-        <v>-1.27</v>
+        <v>-1.77</v>
       </c>
       <c r="E17" s="39" t="n">
-        <v>-1.39</v>
+        <v>-1.88</v>
       </c>
       <c r="F17" s="39" t="n">
-        <v>-1.5</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="18">
@@ -2387,19 +2387,19 @@
         <v>0.2052611846539747</v>
       </c>
       <c r="B18" s="39" t="n">
-        <v>-0.95</v>
+        <v>-1.49</v>
       </c>
       <c r="C18" s="39" t="n">
-        <v>-1.14</v>
+        <v>-1.65</v>
       </c>
       <c r="D18" s="39" t="n">
-        <v>-1.29</v>
+        <v>-1.79</v>
       </c>
       <c r="E18" s="39" t="n">
-        <v>-1.42</v>
+        <v>-1.9</v>
       </c>
       <c r="F18" s="39" t="n">
-        <v>-1.52</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="19">
@@ -2407,19 +2407,19 @@
         <v>0.2152611846539747</v>
       </c>
       <c r="B19" s="39" t="n">
-        <v>-0.98</v>
+        <v>-1.51</v>
       </c>
       <c r="C19" s="39" t="n">
-        <v>-1.17</v>
+        <v>-1.68</v>
       </c>
       <c r="D19" s="39" t="n">
-        <v>-1.32</v>
+        <v>-1.81</v>
       </c>
       <c r="E19" s="39" t="n">
-        <v>-1.44</v>
+        <v>-1.92</v>
       </c>
       <c r="F19" s="39" t="n">
-        <v>-1.55</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="20">
@@ -2427,19 +2427,19 @@
         <v>0.2252611846539747</v>
       </c>
       <c r="B20" s="39" t="n">
-        <v>-1.02</v>
+        <v>-1.54</v>
       </c>
       <c r="C20" s="39" t="n">
-        <v>-1.2</v>
+        <v>-1.7</v>
       </c>
       <c r="D20" s="39" t="n">
-        <v>-1.35</v>
+        <v>-1.83</v>
       </c>
       <c r="E20" s="39" t="n">
-        <v>-1.47</v>
+        <v>-1.93</v>
       </c>
       <c r="F20" s="39" t="n">
-        <v>-1.57</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="21">
@@ -2447,19 +2447,19 @@
         <v>0.2352611846539747</v>
       </c>
       <c r="B21" s="39" t="n">
-        <v>-1.05</v>
+        <v>-1.56</v>
       </c>
       <c r="C21" s="39" t="n">
-        <v>-1.23</v>
+        <v>-1.72</v>
       </c>
       <c r="D21" s="39" t="n">
-        <v>-1.37</v>
+        <v>-1.85</v>
       </c>
       <c r="E21" s="39" t="n">
-        <v>-1.49</v>
+        <v>-1.95</v>
       </c>
       <c r="F21" s="39" t="n">
-        <v>-1.59</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="23">
@@ -2496,19 +2496,19 @@
         <v>-0.3</v>
       </c>
       <c r="B25" s="39" t="n">
-        <v>-2.72</v>
+        <v>-3.26</v>
       </c>
       <c r="C25" s="39" t="n">
-        <v>-2.5</v>
+        <v>-3.02</v>
       </c>
       <c r="D25" s="39" t="n">
+        <v>-2.77</v>
+      </c>
+      <c r="E25" s="39" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="F25" s="39" t="n">
         <v>-2.29</v>
-      </c>
-      <c r="E25" s="39" t="n">
-        <v>-2.07</v>
-      </c>
-      <c r="F25" s="39" t="n">
-        <v>-1.85</v>
       </c>
     </row>
     <row r="26">
@@ -2516,19 +2516,19 @@
         <v>-0.15</v>
       </c>
       <c r="B26" s="39" t="n">
-        <v>-2.24</v>
+        <v>-2.77</v>
       </c>
       <c r="C26" s="39" t="n">
-        <v>-2.02</v>
+        <v>-2.53</v>
       </c>
       <c r="D26" s="39" t="n">
-        <v>-1.8</v>
+        <v>-2.29</v>
       </c>
       <c r="E26" s="39" t="n">
-        <v>-1.59</v>
+        <v>-2.05</v>
       </c>
       <c r="F26" s="39" t="n">
-        <v>-1.37</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="27">
@@ -2536,19 +2536,19 @@
         <v>0</v>
       </c>
       <c r="B27" s="39" t="n">
-        <v>-1.76</v>
+        <v>-2.29</v>
       </c>
       <c r="C27" s="39" t="n">
-        <v>-1.54</v>
+        <v>-2.05</v>
       </c>
       <c r="D27" s="39" t="n">
-        <v>-1.32</v>
+        <v>-1.81</v>
       </c>
       <c r="E27" s="39" t="n">
-        <v>-1.1</v>
+        <v>-1.57</v>
       </c>
       <c r="F27" s="39" t="n">
-        <v>-0.89</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="28">
@@ -2556,19 +2556,19 @@
         <v>0.15</v>
       </c>
       <c r="B28" s="39" t="n">
-        <v>-1.27</v>
+        <v>-1.81</v>
       </c>
       <c r="C28" s="39" t="n">
-        <v>-1.06</v>
+        <v>-1.57</v>
       </c>
       <c r="D28" s="39" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="E28" s="39" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="F28" s="39" t="n">
         <v>-0.84</v>
-      </c>
-      <c r="E28" s="39" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="F28" s="39" t="n">
-        <v>-0.4</v>
       </c>
     </row>
     <row r="29">
@@ -2576,172 +2576,281 @@
         <v>0.3</v>
       </c>
       <c r="B29" s="39" t="n">
-        <v>-0.79</v>
+        <v>-1.33</v>
       </c>
       <c r="C29" s="39" t="n">
-        <v>-0.57</v>
+        <v>-1.08</v>
       </c>
       <c r="D29" s="39" t="n">
-        <v>-0.35</v>
+        <v>-0.84</v>
       </c>
       <c r="E29" s="39" t="n">
-        <v>-0.14</v>
+        <v>-0.6</v>
       </c>
       <c r="F29" s="39" t="n">
-        <v>0.08</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Beta grid (Ke / WACCs / DCF)</t>
+          <t>Terminal-ROIC grid (drives RR = g/ROIC and the inverted g-gradient)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>Terminal ROIC</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>RR for g=5%</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Terminal value</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>DCF (EGP/sh, unfloored)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="B33" s="12" t="n">
+        <v>0.6493506493506493</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>5513</v>
+      </c>
+      <c r="D33" s="39" t="n">
+        <v>-2.02</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>6474</v>
+      </c>
+      <c r="D34" s="39" t="n">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="n">
+        <v>0.09170814583433977</v>
+      </c>
+      <c r="B35" s="12" t="n">
+        <v>0.5452078389014566</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>7150</v>
+      </c>
+      <c r="D35" s="39" t="n">
+        <v>-1.81</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B36" s="12" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>9171</v>
+      </c>
+      <c r="D36" s="39" t="n">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="B37" s="12" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>10481</v>
+      </c>
+      <c r="D37" s="39" t="n">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Challenged net-debt reading (unverified aggregator 10,386): DCF unfloored</t>
+        </is>
+      </c>
+      <c r="E39" s="39" t="n">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Beta grid (Ke / WACCs / DCF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Ke</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>WACC explicit</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>WACC terminal</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>DCF (EGP/sh)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="39" t="n">
+    <row r="43">
+      <c r="A43" s="39" t="n">
         <v>0.6</v>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B43" s="12" t="n">
         <v>0.24556</v>
       </c>
-      <c r="C33" s="12" t="n">
+      <c r="C43" s="12" t="n">
         <v>0.2012355297306375</v>
       </c>
-      <c r="D33" s="12" t="n">
+      <c r="D43" s="12" t="n">
         <v>0.1347</v>
       </c>
-      <c r="E33" s="39" t="n">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="39" t="n">
+      <c r="E43" s="39" t="n">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="39" t="n">
         <v>0.78</v>
       </c>
-      <c r="B34" s="12" t="n">
+      <c r="B44" s="12" t="n">
         <v>0.262498</v>
       </c>
-      <c r="C34" s="12" t="n">
+      <c r="C44" s="12" t="n">
         <v>0.2081712931542658</v>
       </c>
-      <c r="D34" s="12" t="n">
+      <c r="D44" s="12" t="n">
         <v>0.14226</v>
       </c>
-      <c r="E34" s="39" t="n">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="39" t="n">
+      <c r="E44" s="39" t="n">
+        <v>-1.71</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="39" t="n">
         <v>0.8</v>
       </c>
-      <c r="B35" s="12" t="n">
+      <c r="B45" s="12" t="n">
         <v>0.26438</v>
       </c>
-      <c r="C35" s="12" t="n">
+      <c r="C45" s="12" t="n">
         <v>0.2089419335346689</v>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="D45" s="12" t="n">
         <v>0.1431</v>
       </c>
-      <c r="E35" s="39" t="n">
-        <v>-1.22</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="39" t="n">
+      <c r="E45" s="39" t="n">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="39" t="n">
         <v>0.964</v>
       </c>
-      <c r="B36" s="12" t="n">
+      <c r="B46" s="12" t="n">
         <v>0.2798124</v>
       </c>
-      <c r="C36" s="12" t="n">
+      <c r="C46" s="12" t="n">
         <v>0.2152611846539747</v>
       </c>
-      <c r="D36" s="12" t="n">
+      <c r="D46" s="12" t="n">
         <v>0.149988</v>
       </c>
-      <c r="E36" s="39" t="n">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="39" t="n">
+      <c r="E46" s="39" t="n">
+        <v>-1.81</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="B37" s="12" t="n">
+      <c r="B47" s="12" t="n">
         <v>0.2832</v>
       </c>
-      <c r="C37" s="12" t="n">
+      <c r="C47" s="12" t="n">
         <v>0.2166483373387004</v>
       </c>
-      <c r="D37" s="12" t="n">
+      <c r="D47" s="12" t="n">
         <v>0.1515</v>
       </c>
-      <c r="E37" s="39" t="n">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="39" t="n">
+      <c r="E47" s="39" t="n">
+        <v>-1.83</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="39" t="n">
         <v>1.15</v>
       </c>
-      <c r="B38" s="12" t="n">
+      <c r="B48" s="12" t="n">
         <v>0.297315</v>
       </c>
-      <c r="C38" s="12" t="n">
+      <c r="C48" s="12" t="n">
         <v>0.222428140191724</v>
       </c>
-      <c r="D38" s="12" t="n">
+      <c r="D48" s="12" t="n">
         <v>0.1578</v>
       </c>
-      <c r="E38" s="39" t="n">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="39" t="n">
+      <c r="E48" s="39" t="n">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="39" t="n">
         <v>1.3</v>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B49" s="12" t="n">
         <v>0.31143</v>
       </c>
-      <c r="C39" s="12" t="n">
+      <c r="C49" s="12" t="n">
         <v>0.2282079430447475</v>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="D49" s="12" t="n">
         <v>0.1641</v>
       </c>
-      <c r="E39" s="39" t="n">
-        <v>-1.49</v>
+      <c r="E49" s="39" t="n">
+        <v>-1.95</v>
       </c>
     </row>
   </sheetData>
@@ -3272,17 +3381,17 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>EGP 196bn</t>
+          <t>EGP 196bn (21-Jul; ~205bn 27-Jul)</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>10.4x</t>
+          <t>11.3x computed</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>~6.0x</t>
+          <t>~7.1x computed</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -3292,7 +3401,7 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>FY25 rev EGP 281bn, NP 17.3bn; W&amp;C segment +66% — the demand proof</t>
+          <t>FY25 rev 281bn, NP 17.3bn, EBITDA 30.7bn, net bank debt 19.8bn (filed); W&amp;C grew low-teens FY25 (+66% is FY2024)</t>
         </is>
       </c>
     </row>
@@ -3304,27 +3413,27 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>SAR 18.0bn</t>
+          <t>SAR 15.4bn (30-Jul)</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>18.0x</t>
+          <t>14.3x</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>15.0x</t>
+          <t>~12.5x derived</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>0.27x</t>
+          <t>~0.5x</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Same industry, clean balance sheet, different market</t>
+          <t>Same industry, clean balance sheet, different market; BS inputs unverified</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3594,7 @@
         <v/>
       </c>
       <c r="D6" s="7" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="E6" s="9">
         <f>Assumptions!B35</f>
@@ -3520,14 +3629,14 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="C8" s="8">
         <f>'Relative &amp; Normalized'!C7</f>
         <v/>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="E8" s="9">
         <f>Assumptions!B37</f>
@@ -3548,7 +3657,7 @@
         <v/>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="E9" s="9">
         <f>Assumptions!B38</f>
@@ -4184,7 +4293,7 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>SWDY ~6.0x; discount for leverage/concentration</t>
+          <t>SWDY ~7.1x COMPUTED from its FY25 filing (prior 6.0x aggregator print did not reproduce); discount for leverage/concentration</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4308,7 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>SWDY 10.4x trailing; deep discount</t>
+          <t>SWDY 11.3x COMPUTED (prior 10.4x did not reproduce); ~42% discount held deliberately deep</t>
         </is>
       </c>
     </row>
@@ -4346,23 +4455,23 @@
         </is>
       </c>
       <c r="C42" s="23" t="n">
-        <v>12600</v>
+        <v>14000</v>
       </c>
       <c r="D42" s="23" t="n">
-        <v>12600</v>
+        <v>14000</v>
       </c>
       <c r="E42" s="23" t="n">
-        <v>12600</v>
+        <v>14000</v>
       </c>
       <c r="F42" s="23" t="n">
-        <v>12600</v>
+        <v>14000</v>
       </c>
       <c r="G42" s="23" t="n">
-        <v>12600</v>
+        <v>14000</v>
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
-          <t>Flat at the 2026 consensus avg — no house commodity view; bull/bear move it</t>
+          <t>Flat at the CURRENT market (~$14.0k LME cash 3-4 Aug-26); the -10% sensitivity (=12.6k) is the mean-reversion case</t>
         </is>
       </c>
     </row>

--- a/engine/elec_study/ELEC_Valuation_Model_05082026_public.xlsx
+++ b/engine/elec_study/ELEC_Valuation_Model_05082026_public.xlsx
@@ -695,7 +695,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Currency. EGP million unless stated. Spot EGP 2.19 (5 Aug 2026 close). Sheets: Summary · Fundamental</t>
+          <t>Currency. EGP million unless stated. Spot EGP 2.08 (2026-09-03 close). Sheets: Summary · Fundamental</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>0.6135</v>
+        <v>0.7286</v>
       </c>
     </row>
     <row r="7">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B7" s="43" t="inlineStr">
         <is>
-          <t>37% vs 18% · 2.1:1</t>
+          <t>50% vs 11% · 4.4:1</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="B8" s="43" t="inlineStr">
         <is>
-          <t>2.29 (+4.7%)</t>
+          <t>2.29 (+10.2%)</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="B10" s="43" t="inlineStr">
         <is>
-          <t>60% / 39%</t>
+          <t>80% / 24%</t>
         </is>
       </c>
     </row>
@@ -2024,13 +2024,13 @@
     </row>
     <row r="23">
       <c r="A23" s="39" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="B23" s="12" t="n">
-        <v>1</v>
+        <v>0.40075</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>1</v>
+        <v>0.6178</v>
       </c>
     </row>
     <row r="24">
@@ -2258,13 +2258,13 @@
         <v>0.139988</v>
       </c>
       <c r="B10" s="39" t="n">
-        <v>-1.48</v>
+        <v>-1.47</v>
       </c>
       <c r="C10" s="39" t="n">
         <v>-1.56</v>
       </c>
       <c r="D10" s="39" t="n">
-        <v>-1.68</v>
+        <v>-1.67</v>
       </c>
       <c r="E10" s="39" t="n">
         <v>-1.82</v>
@@ -2287,10 +2287,10 @@
         <v>-1.81</v>
       </c>
       <c r="E11" s="39" t="n">
-        <v>-1.95</v>
+        <v>-1.94</v>
       </c>
       <c r="F11" s="39" t="n">
-        <v>-2.13</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="12">
@@ -2304,10 +2304,10 @@
         <v>-1.81</v>
       </c>
       <c r="D12" s="39" t="n">
-        <v>-1.92</v>
+        <v>-1.91</v>
       </c>
       <c r="E12" s="39" t="n">
-        <v>-2.05</v>
+        <v>-2.04</v>
       </c>
       <c r="F12" s="39" t="n">
         <v>-2.21</v>
@@ -2327,7 +2327,7 @@
         <v>-2</v>
       </c>
       <c r="E13" s="39" t="n">
-        <v>-2.13</v>
+        <v>-2.12</v>
       </c>
       <c r="F13" s="39" t="n">
         <v>-2.28</v>
@@ -2364,19 +2364,19 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>0.1952611846539747</v>
+        <v>0.1939056500498176</v>
       </c>
       <c r="B17" s="39" t="n">
-        <v>-1.46</v>
+        <v>-1.45</v>
       </c>
       <c r="C17" s="39" t="n">
         <v>-1.63</v>
       </c>
       <c r="D17" s="39" t="n">
-        <v>-1.77</v>
+        <v>-1.76</v>
       </c>
       <c r="E17" s="39" t="n">
-        <v>-1.88</v>
+        <v>-1.87</v>
       </c>
       <c r="F17" s="39" t="n">
         <v>-1.97</v>
@@ -2384,19 +2384,19 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
-        <v>0.2052611846539747</v>
+        <v>0.2039056500498176</v>
       </c>
       <c r="B18" s="39" t="n">
-        <v>-1.49</v>
+        <v>-1.48</v>
       </c>
       <c r="C18" s="39" t="n">
         <v>-1.65</v>
       </c>
       <c r="D18" s="39" t="n">
-        <v>-1.79</v>
+        <v>-1.78</v>
       </c>
       <c r="E18" s="39" t="n">
-        <v>-1.9</v>
+        <v>-1.89</v>
       </c>
       <c r="F18" s="39" t="n">
         <v>-1.99</v>
@@ -2404,19 +2404,19 @@
     </row>
     <row r="19">
       <c r="A19" s="12" t="n">
-        <v>0.2152611846539747</v>
+        <v>0.2139056500498176</v>
       </c>
       <c r="B19" s="39" t="n">
         <v>-1.51</v>
       </c>
       <c r="C19" s="39" t="n">
-        <v>-1.68</v>
+        <v>-1.67</v>
       </c>
       <c r="D19" s="39" t="n">
         <v>-1.81</v>
       </c>
       <c r="E19" s="39" t="n">
-        <v>-1.92</v>
+        <v>-1.91</v>
       </c>
       <c r="F19" s="39" t="n">
         <v>-2</v>
@@ -2424,7 +2424,7 @@
     </row>
     <row r="20">
       <c r="A20" s="12" t="n">
-        <v>0.2252611846539747</v>
+        <v>0.2239056500498176</v>
       </c>
       <c r="B20" s="39" t="n">
         <v>-1.54</v>
@@ -2444,7 +2444,7 @@
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
-        <v>0.2352611846539747</v>
+        <v>0.2339056500498176</v>
       </c>
       <c r="B21" s="39" t="n">
         <v>-1.56</v>
@@ -2545,10 +2545,10 @@
         <v>-1.81</v>
       </c>
       <c r="E27" s="39" t="n">
-        <v>-1.57</v>
+        <v>-1.56</v>
       </c>
       <c r="F27" s="39" t="n">
-        <v>-1.33</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="28">
@@ -2559,10 +2559,10 @@
         <v>-1.81</v>
       </c>
       <c r="C28" s="39" t="n">
-        <v>-1.57</v>
+        <v>-1.56</v>
       </c>
       <c r="D28" s="39" t="n">
-        <v>-1.33</v>
+        <v>-1.32</v>
       </c>
       <c r="E28" s="39" t="n">
         <v>-1.08</v>
@@ -2576,7 +2576,7 @@
         <v>0.3</v>
       </c>
       <c r="B29" s="39" t="n">
-        <v>-1.33</v>
+        <v>-1.32</v>
       </c>
       <c r="C29" s="39" t="n">
         <v>-1.08</v>
@@ -2585,10 +2585,10 @@
         <v>-0.84</v>
       </c>
       <c r="E29" s="39" t="n">
-        <v>-0.6</v>
+        <v>-0.59</v>
       </c>
       <c r="F29" s="39" t="n">
-        <v>-0.36</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="31">
@@ -2645,7 +2645,7 @@
         <v>6474</v>
       </c>
       <c r="D34" s="39" t="n">
-        <v>-1.9</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="35">
@@ -2742,7 +2742,7 @@
         <v>0.24556</v>
       </c>
       <c r="C43" s="12" t="n">
-        <v>0.2012355297306375</v>
+        <v>0.2003047439516406</v>
       </c>
       <c r="D43" s="12" t="n">
         <v>0.1347</v>
@@ -2759,7 +2759,7 @@
         <v>0.262498</v>
       </c>
       <c r="C44" s="12" t="n">
-        <v>0.2081712931542658</v>
+        <v>0.2070304667474424</v>
       </c>
       <c r="D44" s="12" t="n">
         <v>0.14226</v>
@@ -2776,7 +2776,7 @@
         <v>0.26438</v>
       </c>
       <c r="C45" s="12" t="n">
-        <v>0.2089419335346689</v>
+        <v>0.2077777692803093</v>
       </c>
       <c r="D45" s="12" t="n">
         <v>0.1431</v>
@@ -2793,7 +2793,7 @@
         <v>0.2798124</v>
       </c>
       <c r="C46" s="12" t="n">
-        <v>0.2152611846539747</v>
+        <v>0.2139056500498176</v>
       </c>
       <c r="D46" s="12" t="n">
         <v>0.149988</v>
@@ -2810,13 +2810,13 @@
         <v>0.2832</v>
       </c>
       <c r="C47" s="12" t="n">
-        <v>0.2166483373387004</v>
+        <v>0.215250794608978</v>
       </c>
       <c r="D47" s="12" t="n">
         <v>0.1515</v>
       </c>
       <c r="E47" s="39" t="n">
-        <v>-1.83</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="48">
@@ -2827,7 +2827,7 @@
         <v>0.297315</v>
       </c>
       <c r="C48" s="12" t="n">
-        <v>0.222428140191724</v>
+        <v>0.2208555636054796</v>
       </c>
       <c r="D48" s="12" t="n">
         <v>0.1578</v>
@@ -2844,7 +2844,7 @@
         <v>0.31143</v>
       </c>
       <c r="C49" s="12" t="n">
-        <v>0.2282079430447475</v>
+        <v>0.2264603326019811</v>
       </c>
       <c r="D49" s="12" t="n">
         <v>0.1641</v>
@@ -3594,7 +3594,7 @@
         <v/>
       </c>
       <c r="D6" s="7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="E6" s="9">
         <f>Assumptions!B35</f>
@@ -3955,11 +3955,11 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>5-Aug-2026 close, uploaded EGX history</t>
+          <t>2026-09-03 close, uploaded EGX history</t>
         </is>
       </c>
     </row>

--- a/engine/elec_study/ELEC_Valuation_Model_05082026_public.xlsx
+++ b/engine/elec_study/ELEC_Valuation_Model_05082026_public.xlsx
@@ -2367,19 +2367,19 @@
         <v>0.1939056500498176</v>
       </c>
       <c r="B17" s="39" t="n">
-        <v>-1.45</v>
+        <v>-1.83</v>
       </c>
       <c r="C17" s="39" t="n">
-        <v>-1.63</v>
+        <v>-1.98</v>
       </c>
       <c r="D17" s="39" t="n">
-        <v>-1.76</v>
+        <v>-2.09</v>
       </c>
       <c r="E17" s="39" t="n">
-        <v>-1.87</v>
+        <v>-2.18</v>
       </c>
       <c r="F17" s="39" t="n">
-        <v>-1.97</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="18">
@@ -2387,19 +2387,19 @@
         <v>0.2039056500498176</v>
       </c>
       <c r="B18" s="39" t="n">
-        <v>-1.48</v>
+        <v>-1.85</v>
       </c>
       <c r="C18" s="39" t="n">
-        <v>-1.65</v>
+        <v>-2</v>
       </c>
       <c r="D18" s="39" t="n">
-        <v>-1.78</v>
+        <v>-2.11</v>
       </c>
       <c r="E18" s="39" t="n">
-        <v>-1.89</v>
+        <v>-2.19</v>
       </c>
       <c r="F18" s="39" t="n">
-        <v>-1.99</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="19">
@@ -2407,19 +2407,19 @@
         <v>0.2139056500498176</v>
       </c>
       <c r="B19" s="39" t="n">
-        <v>-1.51</v>
+        <v>-1.87</v>
       </c>
       <c r="C19" s="39" t="n">
-        <v>-1.67</v>
+        <v>-2.02</v>
       </c>
       <c r="D19" s="39" t="n">
-        <v>-1.81</v>
+        <v>-2.12</v>
       </c>
       <c r="E19" s="39" t="n">
-        <v>-1.91</v>
+        <v>-2.21</v>
       </c>
       <c r="F19" s="39" t="n">
-        <v>-2</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="20">
@@ -2427,19 +2427,19 @@
         <v>0.2239056500498176</v>
       </c>
       <c r="B20" s="39" t="n">
-        <v>-1.54</v>
+        <v>-1.89</v>
       </c>
       <c r="C20" s="39" t="n">
-        <v>-1.7</v>
+        <v>-2.03</v>
       </c>
       <c r="D20" s="39" t="n">
-        <v>-1.83</v>
+        <v>-2.14</v>
       </c>
       <c r="E20" s="39" t="n">
-        <v>-1.93</v>
+        <v>-2.22</v>
       </c>
       <c r="F20" s="39" t="n">
-        <v>-2.02</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="21">
@@ -2447,19 +2447,19 @@
         <v>0.2339056500498176</v>
       </c>
       <c r="B21" s="39" t="n">
-        <v>-1.56</v>
+        <v>-1.91</v>
       </c>
       <c r="C21" s="39" t="n">
-        <v>-1.72</v>
+        <v>-2.05</v>
       </c>
       <c r="D21" s="39" t="n">
-        <v>-1.85</v>
+        <v>-2.15</v>
       </c>
       <c r="E21" s="39" t="n">
-        <v>-1.95</v>
+        <v>-2.23</v>
       </c>
       <c r="F21" s="39" t="n">
-        <v>-2.04</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="23">
@@ -2496,19 +2496,19 @@
         <v>-0.3</v>
       </c>
       <c r="B25" s="39" t="n">
-        <v>-3.26</v>
+        <v>0</v>
       </c>
       <c r="C25" s="39" t="n">
-        <v>-3.02</v>
+        <v>0</v>
       </c>
       <c r="D25" s="39" t="n">
-        <v>-2.77</v>
+        <v>0</v>
       </c>
       <c r="E25" s="39" t="n">
-        <v>-2.53</v>
+        <v>0</v>
       </c>
       <c r="F25" s="39" t="n">
-        <v>-2.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2516,19 +2516,19 @@
         <v>-0.15</v>
       </c>
       <c r="B26" s="39" t="n">
-        <v>-2.77</v>
+        <v>0</v>
       </c>
       <c r="C26" s="39" t="n">
-        <v>-2.53</v>
+        <v>0</v>
       </c>
       <c r="D26" s="39" t="n">
-        <v>-2.29</v>
+        <v>-2.7</v>
       </c>
       <c r="E26" s="39" t="n">
-        <v>-2.05</v>
+        <v>-2.4</v>
       </c>
       <c r="F26" s="39" t="n">
-        <v>-1.81</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="27">
@@ -2536,19 +2536,19 @@
         <v>0</v>
       </c>
       <c r="B27" s="39" t="n">
-        <v>-2.29</v>
+        <v>-2.72</v>
       </c>
       <c r="C27" s="39" t="n">
-        <v>-2.05</v>
+        <v>-2.42</v>
       </c>
       <c r="D27" s="39" t="n">
-        <v>-1.81</v>
+        <v>-2.12</v>
       </c>
       <c r="E27" s="39" t="n">
-        <v>-1.56</v>
+        <v>-1.82</v>
       </c>
       <c r="F27" s="39" t="n">
-        <v>-1.32</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="28">
@@ -2556,19 +2556,19 @@
         <v>0.15</v>
       </c>
       <c r="B28" s="39" t="n">
-        <v>-1.81</v>
+        <v>-2.14</v>
       </c>
       <c r="C28" s="39" t="n">
-        <v>-1.56</v>
+        <v>-1.84</v>
       </c>
       <c r="D28" s="39" t="n">
-        <v>-1.32</v>
+        <v>-1.54</v>
       </c>
       <c r="E28" s="39" t="n">
-        <v>-1.08</v>
+        <v>-1.24</v>
       </c>
       <c r="F28" s="39" t="n">
-        <v>-0.84</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="29">
@@ -2576,19 +2576,19 @@
         <v>0.3</v>
       </c>
       <c r="B29" s="39" t="n">
-        <v>-1.32</v>
+        <v>-1.56</v>
       </c>
       <c r="C29" s="39" t="n">
-        <v>-1.08</v>
+        <v>-1.26</v>
       </c>
       <c r="D29" s="39" t="n">
-        <v>-0.84</v>
+        <v>-0.96</v>
       </c>
       <c r="E29" s="39" t="n">
-        <v>-0.59</v>
+        <v>-0.67</v>
       </c>
       <c r="F29" s="39" t="n">
-        <v>-0.35</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="31">
@@ -2625,13 +2625,13 @@
         <v>0.077</v>
       </c>
       <c r="B33" s="12" t="n">
-        <v>0.6493506493506493</v>
+        <v>0.9090909090909099</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>5513</v>
+        <v>1821</v>
       </c>
       <c r="D33" s="39" t="n">
-        <v>-2.02</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="34">
@@ -2639,13 +2639,13 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="B34" s="12" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.8235294117647065</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>6474</v>
+        <v>3534</v>
       </c>
       <c r="D34" s="39" t="n">
-        <v>-1.89</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="35">
@@ -2653,13 +2653,13 @@
         <v>0.09170814583433977</v>
       </c>
       <c r="B35" s="12" t="n">
-        <v>0.5452078389014566</v>
+        <v>0.7632909744620399</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>7150</v>
+        <v>4741</v>
       </c>
       <c r="D35" s="39" t="n">
-        <v>-1.81</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="36">
@@ -2667,13 +2667,13 @@
         <v>0.12</v>
       </c>
       <c r="B36" s="12" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5833333333333339</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>9171</v>
+        <v>8345</v>
       </c>
       <c r="D36" s="39" t="n">
-        <v>-1.54</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="37">
@@ -2681,13 +2681,13 @@
         <v>0.15</v>
       </c>
       <c r="B37" s="12" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.4666666666666671</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>10481</v>
+        <v>10681</v>
       </c>
       <c r="D37" s="39" t="n">
-        <v>-1.37</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="39">
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="E39" s="39" t="n">
-        <v>-1.98</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="41">
@@ -2748,7 +2748,7 @@
         <v>0.1347</v>
       </c>
       <c r="E43" s="39" t="n">
-        <v>-1.59</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="44">
@@ -2765,7 +2765,7 @@
         <v>0.14226</v>
       </c>
       <c r="E44" s="39" t="n">
-        <v>-1.71</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="45">
@@ -2782,7 +2782,7 @@
         <v>0.1431</v>
       </c>
       <c r="E45" s="39" t="n">
-        <v>-1.72</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="46">
@@ -2799,7 +2799,7 @@
         <v>0.149988</v>
       </c>
       <c r="E46" s="39" t="n">
-        <v>-1.81</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="47">
@@ -2816,7 +2816,7 @@
         <v>0.1515</v>
       </c>
       <c r="E47" s="39" t="n">
-        <v>-1.82</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="48">
@@ -2833,7 +2833,7 @@
         <v>0.1578</v>
       </c>
       <c r="E48" s="39" t="n">
-        <v>-1.89</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="49">
@@ -2850,7 +2850,7 @@
         <v>0.1641</v>
       </c>
       <c r="E49" s="39" t="n">
-        <v>-1.95</v>
+        <v>-2.24</v>
       </c>
     </row>
   </sheetData>
@@ -3650,14 +3650,14 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="C9" s="8">
         <f>'Relative &amp; Normalized'!C9</f>
         <v/>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="E9" s="9">
         <f>Assumptions!B38</f>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>CBE's Q4-2028 inflation target 5% + 5.5pp real-rate convention</t>
+          <t>House terminal inflation 7.00% + the 3.5pp real-rate convention (engine/macro_paths/EG.json)</t>
         </is>
       </c>
     </row>
@@ -4230,11 +4230,11 @@
         </is>
       </c>
       <c r="B26" s="18" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000006</v>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>Standing center 5%; grid 3-7% on Sensitivity</t>
+          <t>DERIVED, not typed: zero stated real growth on the house terminal inflation of 7.00% (engine/macro_paths/EG.json)</t>
         </is>
       </c>
     </row>
